--- a/models/RY_Tool_3_Statement_Model.xlsx
+++ b/models/RY_Tool_3_Statement_Model.xlsx
@@ -16,13 +16,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#,##0;(#,##0);\-"/>
     <numFmt numFmtId="165" formatCode="0.0%;(0.0%);\-"/>
-    <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;;(0.00&quot;x&quot;);\-"/>
-    <numFmt numFmtId="167" formatCode="0&quot; days&quot;;(0);\-"/>
+    <numFmt numFmtId="166" formatCode="0.0&quot; yrs&quot;;(0.0);\-"/>
+    <numFmt numFmtId="167" formatCode="0.00&quot;x&quot;;(0.00&quot;x&quot;);\-"/>
+    <numFmt numFmtId="168" formatCode="0&quot; days&quot;;(0);\-"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -84,6 +85,12 @@
       <color rgb="FF404040"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF404040"/>
+      <sz val="12"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -133,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -181,6 +188,10 @@
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -191,6 +202,13 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -558,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:I146"/>
+  <dimension ref="A2:I206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.4" customWidth="1" min="1" max="1"/>
@@ -689,23 +707,23 @@
         </is>
       </c>
       <c r="C10" s="13">
-        <f>C68</f>
+        <f>C84</f>
         <v/>
       </c>
       <c r="D10" s="13">
-        <f>D68</f>
+        <f>D84</f>
         <v/>
       </c>
       <c r="E10" s="13">
-        <f>E68</f>
+        <f>E84</f>
         <v/>
       </c>
       <c r="F10" s="13">
-        <f>F68</f>
+        <f>F84</f>
         <v/>
       </c>
       <c r="G10" s="13">
-        <f>G68</f>
+        <f>G84</f>
         <v/>
       </c>
       <c r="I10" s="12" t="inlineStr">
@@ -1302,7 +1320,7 @@
       <c r="A38" s="18" t="n"/>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>Retained earnings reconciliation</t>
+          <t>Net income → EBITDA − capex bridge (bottom-up)</t>
         </is>
       </c>
       <c r="C38" s="18" t="n"/>
@@ -1316,1957 +1334,1994 @@
     <row r="39">
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Retained earnings, beginning of year</t>
-        </is>
-      </c>
-      <c r="C39" s="10" t="n">
-        <v>670703</v>
+          <t xml:space="preserve">  Net income for the year</t>
+        </is>
+      </c>
+      <c r="C39" s="13">
+        <f>C36</f>
+        <v/>
       </c>
       <c r="D39" s="13">
-        <f>C42</f>
+        <f>D36</f>
         <v/>
       </c>
       <c r="E39" s="13">
-        <f>D42</f>
+        <f>E36</f>
         <v/>
       </c>
       <c r="F39" s="13">
-        <f>E42</f>
+        <f>F36</f>
         <v/>
       </c>
       <c r="G39" s="13">
-        <f>F42</f>
+        <f>G36</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Net income for the year</t>
+          <t xml:space="preserve">  Add: income taxes</t>
         </is>
       </c>
       <c r="C40" s="13">
-        <f>C36</f>
+        <f>C34</f>
         <v/>
       </c>
       <c r="D40" s="13">
-        <f>D36</f>
+        <f>D34</f>
         <v/>
       </c>
       <c r="E40" s="13">
-        <f>E36</f>
+        <f>E34</f>
         <v/>
       </c>
       <c r="F40" s="13">
-        <f>F36</f>
+        <f>F34</f>
         <v/>
       </c>
       <c r="G40" s="13">
-        <f>G36</f>
+        <f>G34</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Dividends</t>
-        </is>
-      </c>
-      <c r="C41" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>170000</v>
-      </c>
-      <c r="F41" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="10" t="n">
-        <v>0</v>
+          <t xml:space="preserve">  Add: bank charges and interest</t>
+        </is>
+      </c>
+      <c r="C41" s="13">
+        <f>C18</f>
+        <v/>
+      </c>
+      <c r="D41" s="13">
+        <f>D18</f>
+        <v/>
+      </c>
+      <c r="E41" s="13">
+        <f>E18</f>
+        <v/>
+      </c>
+      <c r="F41" s="13">
+        <f>F18</f>
+        <v/>
+      </c>
+      <c r="G41" s="13">
+        <f>G18</f>
+        <v/>
+      </c>
+      <c r="I41" s="12" t="inlineStr">
+        <is>
+          <t>Interest is bundled within bank charges &amp; interest.</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="14" t="inlineStr">
         <is>
+          <t xml:space="preserve">  = EBIT</t>
+        </is>
+      </c>
+      <c r="C42" s="15">
+        <f>C36+C34+C18</f>
+        <v/>
+      </c>
+      <c r="D42" s="15">
+        <f>D36+D34+D18</f>
+        <v/>
+      </c>
+      <c r="E42" s="15">
+        <f>E36+E34+E18</f>
+        <v/>
+      </c>
+      <c r="F42" s="15">
+        <f>F36+F34+F18</f>
+        <v/>
+      </c>
+      <c r="G42" s="15">
+        <f>G36+G34+G18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Add: amortization — office equipment</t>
+        </is>
+      </c>
+      <c r="C43" s="13">
+        <f>C19</f>
+        <v/>
+      </c>
+      <c r="D43" s="13">
+        <f>D19</f>
+        <v/>
+      </c>
+      <c r="E43" s="13">
+        <f>E19</f>
+        <v/>
+      </c>
+      <c r="F43" s="13">
+        <f>F19</f>
+        <v/>
+      </c>
+      <c r="G43" s="13">
+        <f>G19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Add: amortization — building and shop equipment</t>
+        </is>
+      </c>
+      <c r="C44" s="13">
+        <f>C82</f>
+        <v/>
+      </c>
+      <c r="D44" s="13">
+        <f>D82</f>
+        <v/>
+      </c>
+      <c r="E44" s="13">
+        <f>E82</f>
+        <v/>
+      </c>
+      <c r="F44" s="13">
+        <f>F82</f>
+        <v/>
+      </c>
+      <c r="G44" s="13">
+        <f>G82</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = EBITDA</t>
+        </is>
+      </c>
+      <c r="C45" s="15">
+        <f>C42+C19+C82</f>
+        <v/>
+      </c>
+      <c r="D45" s="15">
+        <f>D42+D19+D82</f>
+        <v/>
+      </c>
+      <c r="E45" s="15">
+        <f>E42+E19+E82</f>
+        <v/>
+      </c>
+      <c r="F45" s="15">
+        <f>F42+F19+F82</f>
+        <v/>
+      </c>
+      <c r="G45" s="15">
+        <f>G42+G19+G82</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Less: capital expenditures (implied)</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="n"/>
+      <c r="D46" s="13">
+        <f>D128</f>
+        <v/>
+      </c>
+      <c r="E46" s="13">
+        <f>E128</f>
+        <v/>
+      </c>
+      <c r="F46" s="13">
+        <f>F128</f>
+        <v/>
+      </c>
+      <c r="G46" s="13">
+        <f>G128</f>
+        <v/>
+      </c>
+      <c r="I46" s="12" t="inlineStr">
+        <is>
+          <t>From the implied cash flow; requires prior-year PP&amp;E, so FY2021 is n/a.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = EBITDA − capex</t>
+        </is>
+      </c>
+      <c r="C47" s="20" t="n"/>
+      <c r="D47" s="20">
+        <f>D45+D128</f>
+        <v/>
+      </c>
+      <c r="E47" s="20">
+        <f>E45+E128</f>
+        <v/>
+      </c>
+      <c r="F47" s="20">
+        <f>F45+F128</f>
+        <v/>
+      </c>
+      <c r="G47" s="20">
+        <f>G45+G128</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="18" t="n"/>
+      <c r="B49" s="18" t="inlineStr">
+        <is>
+          <t>Retained earnings reconciliation</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="n"/>
+      <c r="D49" s="18" t="n"/>
+      <c r="E49" s="18" t="n"/>
+      <c r="F49" s="18" t="n"/>
+      <c r="G49" s="18" t="n"/>
+      <c r="H49" s="18" t="n"/>
+      <c r="I49" s="18" t="n"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Retained earnings, beginning of year</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="n">
+        <v>670703</v>
+      </c>
+      <c r="D50" s="13">
+        <f>C53</f>
+        <v/>
+      </c>
+      <c r="E50" s="13">
+        <f>D53</f>
+        <v/>
+      </c>
+      <c r="F50" s="13">
+        <f>E53</f>
+        <v/>
+      </c>
+      <c r="G50" s="13">
+        <f>F53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Net income for the year</t>
+        </is>
+      </c>
+      <c r="C51" s="13">
+        <f>C36</f>
+        <v/>
+      </c>
+      <c r="D51" s="13">
+        <f>D36</f>
+        <v/>
+      </c>
+      <c r="E51" s="13">
+        <f>E36</f>
+        <v/>
+      </c>
+      <c r="F51" s="13">
+        <f>F36</f>
+        <v/>
+      </c>
+      <c r="G51" s="13">
+        <f>G36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Dividends</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>170000</v>
+      </c>
+      <c r="F52" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="14" t="inlineStr">
+        <is>
           <t>Retained earnings, end of year</t>
         </is>
       </c>
-      <c r="C42" s="15">
-        <f>C39+C40-C41</f>
-        <v/>
-      </c>
-      <c r="D42" s="15">
-        <f>D39+D40-D41</f>
-        <v/>
-      </c>
-      <c r="E42" s="15">
-        <f>E39+E40-E41</f>
-        <v/>
-      </c>
-      <c r="F42" s="15">
-        <f>F39+F40-F41</f>
-        <v/>
-      </c>
-      <c r="G42" s="15">
-        <f>G39+G40-G41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="18" t="n"/>
-      <c r="B44" s="18" t="inlineStr">
+      <c r="C53" s="15">
+        <f>C50+C51-C52</f>
+        <v/>
+      </c>
+      <c r="D53" s="15">
+        <f>D50+D51-D52</f>
+        <v/>
+      </c>
+      <c r="E53" s="15">
+        <f>E50+E51-E52</f>
+        <v/>
+      </c>
+      <c r="F53" s="15">
+        <f>F50+F51-F52</f>
+        <v/>
+      </c>
+      <c r="G53" s="15">
+        <f>G50+G51-G52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="18" t="n"/>
+      <c r="B55" s="18" t="inlineStr">
         <is>
           <t>Growth &amp; margins</t>
         </is>
       </c>
-      <c r="C44" s="18" t="n"/>
-      <c r="D44" s="18" t="n"/>
-      <c r="E44" s="18" t="n"/>
-      <c r="F44" s="18" t="n"/>
-      <c r="G44" s="18" t="n"/>
-      <c r="H44" s="18" t="n"/>
-      <c r="I44" s="18" t="n"/>
-    </row>
-    <row r="45">
-      <c r="B45" s="16" t="inlineStr">
+      <c r="C55" s="18" t="n"/>
+      <c r="D55" s="18" t="n"/>
+      <c r="E55" s="18" t="n"/>
+      <c r="F55" s="18" t="n"/>
+      <c r="G55" s="18" t="n"/>
+      <c r="H55" s="18" t="n"/>
+      <c r="I55" s="18" t="n"/>
+    </row>
+    <row r="56">
+      <c r="B56" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue y/y %</t>
         </is>
       </c>
-      <c r="C45" s="17">
+      <c r="C56" s="17">
         <f>IFERROR(C9/C9-1,"")</f>
         <v/>
       </c>
-      <c r="D45" s="17">
+      <c r="D56" s="17">
         <f>IFERROR(D9/C9-1,"")</f>
         <v/>
       </c>
-      <c r="E45" s="17">
+      <c r="E56" s="17">
         <f>IFERROR(E9/D9-1,"")</f>
         <v/>
       </c>
-      <c r="F45" s="17">
+      <c r="F56" s="17">
         <f>IFERROR(F9/E9-1,"")</f>
         <v/>
       </c>
-      <c r="G45" s="17">
+      <c r="G56" s="17">
         <f>IFERROR(G9/F9-1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="16" t="inlineStr">
+    <row r="57">
+      <c r="B57" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Gross margin y/y %</t>
         </is>
       </c>
-      <c r="C46" s="17">
+      <c r="C57" s="17">
         <f>IFERROR(C11/C11-1,"")</f>
         <v/>
       </c>
-      <c r="D46" s="17">
+      <c r="D57" s="17">
         <f>IFERROR(D11/C11-1,"")</f>
         <v/>
       </c>
-      <c r="E46" s="17">
+      <c r="E57" s="17">
         <f>IFERROR(E11/D11-1,"")</f>
         <v/>
       </c>
-      <c r="F46" s="17">
+      <c r="F57" s="17">
         <f>IFERROR(F11/E11-1,"")</f>
         <v/>
       </c>
-      <c r="G46" s="17">
+      <c r="G57" s="17">
         <f>IFERROR(G11/F11-1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="16" t="inlineStr">
+    <row r="58">
+      <c r="B58" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Net income y/y %</t>
         </is>
       </c>
-      <c r="C47" s="17">
+      <c r="C58" s="17">
         <f>IFERROR(C36/C36-1,"")</f>
         <v/>
       </c>
-      <c r="D47" s="17">
+      <c r="D58" s="17">
         <f>IFERROR(D36/C36-1,"")</f>
         <v/>
       </c>
-      <c r="E47" s="17">
+      <c r="E58" s="17">
         <f>IFERROR(E36/D36-1,"")</f>
         <v/>
       </c>
-      <c r="F47" s="17">
+      <c r="F58" s="17">
         <f>IFERROR(F36/E36-1,"")</f>
         <v/>
       </c>
-      <c r="G47" s="17">
+      <c r="G58" s="17">
         <f>IFERROR(G36/F36-1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="16" t="inlineStr">
+    <row r="59">
+      <c r="B59" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  G&amp;A % of revenue</t>
         </is>
       </c>
-      <c r="C48" s="17">
+      <c r="C59" s="17">
         <f>IFERROR(C29/C9,0)</f>
         <v/>
       </c>
-      <c r="D48" s="17">
+      <c r="D59" s="17">
         <f>IFERROR(D29/D9,0)</f>
         <v/>
       </c>
-      <c r="E48" s="17">
+      <c r="E59" s="17">
         <f>IFERROR(E29/E9,0)</f>
         <v/>
       </c>
-      <c r="F48" s="17">
+      <c r="F59" s="17">
         <f>IFERROR(F29/F9,0)</f>
         <v/>
       </c>
-      <c r="G48" s="17">
+      <c r="G59" s="17">
         <f>IFERROR(G29/G9,0)</f>
         <v/>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" s="16" t="inlineStr">
+    <row r="60">
+      <c r="B60" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Net income margin %</t>
         </is>
       </c>
-      <c r="C49" s="17">
+      <c r="C60" s="17">
         <f>IFERROR(C36/C9,0)</f>
         <v/>
       </c>
-      <c r="D49" s="17">
+      <c r="D60" s="17">
         <f>IFERROR(D36/D9,0)</f>
         <v/>
       </c>
-      <c r="E49" s="17">
+      <c r="E60" s="17">
         <f>IFERROR(E36/E9,0)</f>
         <v/>
       </c>
-      <c r="F49" s="17">
+      <c r="F60" s="17">
         <f>IFERROR(F36/F9,0)</f>
         <v/>
       </c>
-      <c r="G49" s="17">
+      <c r="G60" s="17">
         <f>IFERROR(G36/G9,0)</f>
         <v/>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="8" t="n"/>
-      <c r="B51" s="8" t="inlineStr">
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="8" t="n"/>
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>COST OF SALES SCHEDULE</t>
         </is>
       </c>
-      <c r="C51" s="8" t="n"/>
-      <c r="D51" s="8" t="n"/>
-      <c r="E51" s="8" t="n"/>
-      <c r="F51" s="8" t="n"/>
-      <c r="G51" s="8" t="n"/>
-      <c r="H51" s="8" t="n"/>
-      <c r="I51" s="8" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="18" t="n"/>
-      <c r="B52" s="18" t="inlineStr">
+      <c r="C62" s="8" t="n"/>
+      <c r="D62" s="8" t="n"/>
+      <c r="E62" s="8" t="n"/>
+      <c r="F62" s="8" t="n"/>
+      <c r="G62" s="8" t="n"/>
+      <c r="H62" s="8" t="n"/>
+      <c r="I62" s="8" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="18" t="n"/>
+      <c r="B63" s="18" t="inlineStr">
         <is>
           <t>Direct costs</t>
         </is>
       </c>
-      <c r="C52" s="18" t="n"/>
-      <c r="D52" s="18" t="n"/>
-      <c r="E52" s="18" t="n"/>
-      <c r="F52" s="18" t="n"/>
-      <c r="G52" s="18" t="n"/>
-      <c r="H52" s="18" t="n"/>
-      <c r="I52" s="18" t="n"/>
-    </row>
-    <row r="53">
-      <c r="B53" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Direct wages</t>
-        </is>
-      </c>
-      <c r="C53" s="10" t="n">
-        <v>155912</v>
-      </c>
-      <c r="D53" s="10" t="n">
-        <v>207400</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>124776</v>
-      </c>
-      <c r="F53" s="10" t="n">
-        <v>246407</v>
-      </c>
-      <c r="G53" s="10" t="n">
-        <v>331037</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Materials, supplies and miscellaneous</t>
-        </is>
-      </c>
-      <c r="C54" s="10" t="n">
-        <v>196164</v>
-      </c>
-      <c r="D54" s="10" t="n">
-        <v>234466</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>423028</v>
-      </c>
-      <c r="F54" s="10" t="n">
-        <v>320248</v>
-      </c>
-      <c r="G54" s="10" t="n">
-        <v>233181</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Subcontracts</t>
-        </is>
-      </c>
-      <c r="C55" s="10" t="n">
-        <v>123993</v>
-      </c>
-      <c r="D55" s="10" t="n">
-        <v>124289</v>
-      </c>
-      <c r="E55" s="10" t="n">
-        <v>156114</v>
-      </c>
-      <c r="F55" s="10" t="n">
-        <v>208375</v>
-      </c>
-      <c r="G55" s="10" t="n">
-        <v>242821</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="14" t="inlineStr">
-        <is>
-          <t>Total direct costs</t>
-        </is>
-      </c>
-      <c r="C56" s="15">
-        <f>SUM(C53:C55)</f>
-        <v/>
-      </c>
-      <c r="D56" s="15">
-        <f>SUM(D53:D55)</f>
-        <v/>
-      </c>
-      <c r="E56" s="15">
-        <f>SUM(E53:E55)</f>
-        <v/>
-      </c>
-      <c r="F56" s="15">
-        <f>SUM(F53:F55)</f>
-        <v/>
-      </c>
-      <c r="G56" s="15">
-        <f>SUM(G53:G55)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="18" t="n"/>
-      <c r="B57" s="18" t="inlineStr">
-        <is>
-          <t>Indirect costs</t>
-        </is>
-      </c>
-      <c r="C57" s="18" t="n"/>
-      <c r="D57" s="18" t="n"/>
-      <c r="E57" s="18" t="n"/>
-      <c r="F57" s="18" t="n"/>
-      <c r="G57" s="18" t="n"/>
-      <c r="H57" s="18" t="n"/>
-      <c r="I57" s="18" t="n"/>
-    </row>
-    <row r="58">
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Employee group benefits</t>
-        </is>
-      </c>
-      <c r="C58" s="10" t="n">
-        <v>6052</v>
-      </c>
-      <c r="D58" s="10" t="n">
-        <v>5039</v>
-      </c>
-      <c r="E58" s="10" t="n">
-        <v>9316</v>
-      </c>
-      <c r="F58" s="10" t="n">
-        <v>7971</v>
-      </c>
-      <c r="G58" s="10" t="n">
-        <v>18149</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  WSIB</t>
-        </is>
-      </c>
-      <c r="C59" s="10" t="n">
-        <v>1840</v>
-      </c>
-      <c r="D59" s="10" t="n">
-        <v>1078</v>
-      </c>
-      <c r="E59" s="10" t="n">
-        <v>3724</v>
-      </c>
-      <c r="F59" s="10" t="n">
-        <v>2996</v>
-      </c>
-      <c r="G59" s="10" t="n">
-        <v>-47</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Insurance and property tax</t>
-        </is>
-      </c>
-      <c r="C60" s="10" t="n">
-        <v>28591</v>
-      </c>
-      <c r="D60" s="10" t="n">
-        <v>33771</v>
-      </c>
-      <c r="E60" s="10" t="n">
-        <v>29558</v>
-      </c>
-      <c r="F60" s="10" t="n">
-        <v>33572</v>
-      </c>
-      <c r="G60" s="10" t="n">
-        <v>29258</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Utilities</t>
-        </is>
-      </c>
-      <c r="C61" s="10" t="n">
-        <v>21844</v>
-      </c>
-      <c r="D61" s="10" t="n">
-        <v>24879</v>
-      </c>
-      <c r="E61" s="10" t="n">
-        <v>25382</v>
-      </c>
-      <c r="F61" s="10" t="n">
-        <v>25785</v>
-      </c>
-      <c r="G61" s="10" t="n">
-        <v>25115</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Repairs and maintenance — equipment</t>
-        </is>
-      </c>
-      <c r="C62" s="10" t="n">
-        <v>29368</v>
-      </c>
-      <c r="D62" s="10" t="n">
-        <v>47451</v>
-      </c>
-      <c r="E62" s="10" t="n">
-        <v>39527</v>
-      </c>
-      <c r="F62" s="10" t="n">
-        <v>13007</v>
-      </c>
-      <c r="G62" s="10" t="n">
-        <v>21655</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Repairs and maintenance — buildings</t>
-        </is>
-      </c>
-      <c r="C63" s="10" t="n">
-        <v>35600</v>
-      </c>
-      <c r="D63" s="10" t="n">
-        <v>22714</v>
-      </c>
-      <c r="E63" s="10" t="n">
-        <v>34750</v>
-      </c>
-      <c r="F63" s="10" t="n">
-        <v>50649</v>
-      </c>
-      <c r="G63" s="10" t="n">
-        <v>141141</v>
-      </c>
+      <c r="C63" s="18" t="n"/>
+      <c r="D63" s="18" t="n"/>
+      <c r="E63" s="18" t="n"/>
+      <c r="F63" s="18" t="n"/>
+      <c r="G63" s="18" t="n"/>
+      <c r="H63" s="18" t="n"/>
+      <c r="I63" s="18" t="n"/>
     </row>
     <row r="64">
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Freight and duty</t>
+          <t xml:space="preserve">  Direct wages</t>
         </is>
       </c>
       <c r="C64" s="10" t="n">
-        <v>23583</v>
+        <v>155912</v>
       </c>
       <c r="D64" s="10" t="n">
-        <v>14673</v>
+        <v>207400</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>18134</v>
+        <v>124776</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>23910</v>
+        <v>246407</v>
       </c>
       <c r="G64" s="10" t="n">
-        <v>22757</v>
+        <v>331037</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Truck and travel</t>
+          <t xml:space="preserve">  Materials, supplies and miscellaneous</t>
         </is>
       </c>
       <c r="C65" s="10" t="n">
-        <v>4307</v>
+        <v>196164</v>
       </c>
       <c r="D65" s="10" t="n">
-        <v>10175</v>
+        <v>234466</v>
       </c>
       <c r="E65" s="10" t="n">
-        <v>7805</v>
+        <v>423028</v>
       </c>
       <c r="F65" s="10" t="n">
-        <v>11969</v>
+        <v>320248</v>
       </c>
       <c r="G65" s="10" t="n">
-        <v>11486</v>
+        <v>233181</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Amortization — building and shop equipment</t>
+          <t xml:space="preserve">  Subcontracts</t>
         </is>
       </c>
       <c r="C66" s="10" t="n">
-        <v>89055</v>
+        <v>123993</v>
       </c>
       <c r="D66" s="10" t="n">
-        <v>74522</v>
+        <v>124289</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>53208</v>
+        <v>156114</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>45953</v>
+        <v>208375</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>42284</v>
-      </c>
-      <c r="I66" s="12" t="inlineStr">
-        <is>
-          <t>Non-cash; added back in cash flow.</t>
-        </is>
+        <v>242821</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>Total indirect costs</t>
+          <t>Total direct costs</t>
         </is>
       </c>
       <c r="C67" s="15">
-        <f>SUM(C58:C66)</f>
+        <f>SUM(C64:C66)</f>
         <v/>
       </c>
       <c r="D67" s="15">
-        <f>SUM(D58:D66)</f>
+        <f>SUM(D64:D66)</f>
         <v/>
       </c>
       <c r="E67" s="15">
-        <f>SUM(E58:E66)</f>
+        <f>SUM(E64:E66)</f>
         <v/>
       </c>
       <c r="F67" s="15">
-        <f>SUM(F58:F66)</f>
+        <f>SUM(F64:F66)</f>
         <v/>
       </c>
       <c r="G67" s="15">
-        <f>SUM(G58:G66)</f>
+        <f>SUM(G64:G66)</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="B68" s="19" t="inlineStr">
-        <is>
-          <t>Total cost of sales</t>
-        </is>
-      </c>
-      <c r="C68" s="20">
-        <f>C56+C67</f>
-        <v/>
-      </c>
-      <c r="D68" s="20">
-        <f>D56+D67</f>
-        <v/>
-      </c>
-      <c r="E68" s="20">
-        <f>E56+E67</f>
-        <v/>
-      </c>
-      <c r="F68" s="20">
-        <f>F56+F67</f>
-        <v/>
-      </c>
-      <c r="G68" s="20">
-        <f>G56+G67</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70" ht="18" customHeight="1">
-      <c r="A70" s="8" t="n"/>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>BALANCE SHEET</t>
-        </is>
-      </c>
-      <c r="C70" s="8" t="n"/>
-      <c r="D70" s="8" t="n"/>
-      <c r="E70" s="8" t="n"/>
-      <c r="F70" s="8" t="n"/>
-      <c r="G70" s="8" t="n"/>
-      <c r="H70" s="8" t="n"/>
-      <c r="I70" s="8" t="n"/>
+      <c r="A68" s="18" t="n"/>
+      <c r="B68" s="18" t="inlineStr">
+        <is>
+          <t>Direct costs as % of revenue</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="n"/>
+      <c r="D68" s="18" t="n"/>
+      <c r="E68" s="18" t="n"/>
+      <c r="F68" s="18" t="n"/>
+      <c r="G68" s="18" t="n"/>
+      <c r="H68" s="18" t="n"/>
+      <c r="I68" s="18" t="n"/>
+    </row>
+    <row r="69">
+      <c r="B69" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Direct wages % of revenue</t>
+        </is>
+      </c>
+      <c r="C69" s="17">
+        <f>IFERROR(C64/C9,0)</f>
+        <v/>
+      </c>
+      <c r="D69" s="17">
+        <f>IFERROR(D64/D9,0)</f>
+        <v/>
+      </c>
+      <c r="E69" s="17">
+        <f>IFERROR(E64/E9,0)</f>
+        <v/>
+      </c>
+      <c r="F69" s="17">
+        <f>IFERROR(F64/F9,0)</f>
+        <v/>
+      </c>
+      <c r="G69" s="17">
+        <f>IFERROR(G64/G9,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Materials, supplies and miscellaneous % of revenue</t>
+        </is>
+      </c>
+      <c r="C70" s="17">
+        <f>IFERROR(C65/C9,0)</f>
+        <v/>
+      </c>
+      <c r="D70" s="17">
+        <f>IFERROR(D65/D9,0)</f>
+        <v/>
+      </c>
+      <c r="E70" s="17">
+        <f>IFERROR(E65/E9,0)</f>
+        <v/>
+      </c>
+      <c r="F70" s="17">
+        <f>IFERROR(F65/F9,0)</f>
+        <v/>
+      </c>
+      <c r="G70" s="17">
+        <f>IFERROR(G65/G9,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" s="18" t="n"/>
-      <c r="B71" s="18" t="inlineStr">
-        <is>
-          <t>Assets — current</t>
-        </is>
-      </c>
-      <c r="C71" s="18" t="n"/>
-      <c r="D71" s="18" t="n"/>
-      <c r="E71" s="18" t="n"/>
-      <c r="F71" s="18" t="n"/>
-      <c r="G71" s="18" t="n"/>
-      <c r="H71" s="18" t="n"/>
-      <c r="I71" s="18" t="n"/>
+      <c r="B71" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Subcontracts % of revenue</t>
+        </is>
+      </c>
+      <c r="C71" s="17">
+        <f>IFERROR(C66/C9,0)</f>
+        <v/>
+      </c>
+      <c r="D71" s="17">
+        <f>IFERROR(D66/D9,0)</f>
+        <v/>
+      </c>
+      <c r="E71" s="17">
+        <f>IFERROR(E66/E9,0)</f>
+        <v/>
+      </c>
+      <c r="F71" s="17">
+        <f>IFERROR(F66/F9,0)</f>
+        <v/>
+      </c>
+      <c r="G71" s="17">
+        <f>IFERROR(G66/G9,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
-      <c r="B72" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Cash in bank</t>
-        </is>
-      </c>
-      <c r="C72" s="10" t="n">
-        <v>301695</v>
-      </c>
-      <c r="D72" s="10" t="n">
-        <v>331894</v>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>323927</v>
-      </c>
-      <c r="F72" s="10" t="n">
-        <v>451664</v>
-      </c>
-      <c r="G72" s="10" t="n">
-        <v>700989</v>
+      <c r="B72" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Total direct costs % of revenue</t>
+        </is>
+      </c>
+      <c r="C72" s="22">
+        <f>IFERROR(C67/C9,0)</f>
+        <v/>
+      </c>
+      <c r="D72" s="22">
+        <f>IFERROR(D67/D9,0)</f>
+        <v/>
+      </c>
+      <c r="E72" s="22">
+        <f>IFERROR(E67/E9,0)</f>
+        <v/>
+      </c>
+      <c r="F72" s="22">
+        <f>IFERROR(F67/F9,0)</f>
+        <v/>
+      </c>
+      <c r="G72" s="22">
+        <f>IFERROR(G67/G9,0)</f>
+        <v/>
       </c>
     </row>
     <row r="73">
-      <c r="B73" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Accounts receivable</t>
-        </is>
-      </c>
-      <c r="C73" s="10" t="n">
-        <v>174456</v>
-      </c>
-      <c r="D73" s="10" t="n">
-        <v>102521</v>
-      </c>
-      <c r="E73" s="10" t="n">
-        <v>172686</v>
-      </c>
-      <c r="F73" s="10" t="n">
-        <v>283263</v>
-      </c>
-      <c r="G73" s="10" t="n">
-        <v>249660</v>
-      </c>
+      <c r="A73" s="18" t="n"/>
+      <c r="B73" s="18" t="inlineStr">
+        <is>
+          <t>Indirect costs</t>
+        </is>
+      </c>
+      <c r="C73" s="18" t="n"/>
+      <c r="D73" s="18" t="n"/>
+      <c r="E73" s="18" t="n"/>
+      <c r="F73" s="18" t="n"/>
+      <c r="G73" s="18" t="n"/>
+      <c r="H73" s="18" t="n"/>
+      <c r="I73" s="18" t="n"/>
     </row>
     <row r="74">
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Government sales tax recoverable</t>
+          <t xml:space="preserve">  Employee group benefits</t>
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>10746</v>
+        <v>6052</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>8957</v>
+        <v>5039</v>
       </c>
       <c r="E74" s="10" t="n">
-        <v>11269</v>
+        <v>9316</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>4041</v>
+        <v>7971</v>
       </c>
       <c r="G74" s="10" t="n">
-        <v>10200</v>
+        <v>18149</v>
       </c>
     </row>
     <row r="75">
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Due from director</t>
+          <t xml:space="preserve">  WSIB</t>
         </is>
       </c>
       <c r="C75" s="10" t="n">
-        <v>121461</v>
+        <v>1840</v>
       </c>
       <c r="D75" s="10" t="n">
-        <v>243508</v>
+        <v>1078</v>
       </c>
       <c r="E75" s="10" t="n">
-        <v>0</v>
+        <v>3724</v>
       </c>
       <c r="F75" s="10" t="n">
-        <v>0</v>
+        <v>2996</v>
       </c>
       <c r="G75" s="10" t="n">
-        <v>6193</v>
+        <v>-47</v>
       </c>
     </row>
     <row r="76">
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Due from KEL Tooling, non-interest bearing</t>
+          <t xml:space="preserve">  Insurance and property tax</t>
         </is>
       </c>
       <c r="C76" s="10" t="n">
-        <v>0</v>
+        <v>28591</v>
       </c>
       <c r="D76" s="10" t="n">
-        <v>0</v>
+        <v>33771</v>
       </c>
       <c r="E76" s="10" t="n">
-        <v>23308</v>
+        <v>29558</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>16108</v>
+        <v>33572</v>
       </c>
       <c r="G76" s="10" t="n">
-        <v>8908</v>
+        <v>29258</v>
       </c>
     </row>
     <row r="77">
-      <c r="B77" s="14" t="inlineStr">
-        <is>
-          <t>Total current assets</t>
-        </is>
-      </c>
-      <c r="C77" s="15">
-        <f>SUM(C72:C76)</f>
-        <v/>
-      </c>
-      <c r="D77" s="15">
-        <f>SUM(D72:D76)</f>
-        <v/>
-      </c>
-      <c r="E77" s="15">
-        <f>SUM(E72:E76)</f>
-        <v/>
-      </c>
-      <c r="F77" s="15">
-        <f>SUM(F72:F76)</f>
-        <v/>
-      </c>
-      <c r="G77" s="15">
-        <f>SUM(G72:G76)</f>
-        <v/>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Utilities</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="n">
+        <v>21844</v>
+      </c>
+      <c r="D77" s="10" t="n">
+        <v>24879</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>25382</v>
+      </c>
+      <c r="F77" s="10" t="n">
+        <v>25785</v>
+      </c>
+      <c r="G77" s="10" t="n">
+        <v>25115</v>
       </c>
     </row>
     <row r="78">
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>Due from Related Group of Companies</t>
+          <t xml:space="preserve">  Repairs and maintenance — equipment</t>
         </is>
       </c>
       <c r="C78" s="10" t="n">
-        <v>24277</v>
+        <v>29368</v>
       </c>
       <c r="D78" s="10" t="n">
-        <v>24277</v>
+        <v>47451</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>12780</v>
+        <v>39527</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>16132</v>
+        <v>13007</v>
       </c>
       <c r="G78" s="10" t="n">
-        <v>18139</v>
+        <v>21655</v>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>Land, buildings and equipment, net</t>
+          <t xml:space="preserve">  Repairs and maintenance — buildings</t>
         </is>
       </c>
       <c r="C79" s="10" t="n">
-        <v>570987</v>
+        <v>35600</v>
       </c>
       <c r="D79" s="10" t="n">
-        <v>513774</v>
+        <v>22714</v>
       </c>
       <c r="E79" s="10" t="n">
-        <v>441755</v>
+        <v>34750</v>
       </c>
       <c r="F79" s="10" t="n">
-        <v>403824</v>
+        <v>50649</v>
       </c>
       <c r="G79" s="10" t="n">
-        <v>502314</v>
-      </c>
-      <c r="I79" s="12" t="inlineStr">
-        <is>
-          <t>Net of accumulated amortization.</t>
-        </is>
+        <v>141141</v>
       </c>
     </row>
     <row r="80">
-      <c r="B80" s="21" t="inlineStr">
-        <is>
-          <t>TOTAL ASSETS</t>
-        </is>
-      </c>
-      <c r="C80" s="22">
-        <f>C77+C78+C79</f>
-        <v/>
-      </c>
-      <c r="D80" s="22">
-        <f>D77+D78+D79</f>
-        <v/>
-      </c>
-      <c r="E80" s="22">
-        <f>E77+E78+E79</f>
-        <v/>
-      </c>
-      <c r="F80" s="22">
-        <f>F77+F78+F79</f>
-        <v/>
-      </c>
-      <c r="G80" s="22">
-        <f>G77+G78+G79</f>
-        <v/>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Freight and duty</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="n">
+        <v>23583</v>
+      </c>
+      <c r="D80" s="10" t="n">
+        <v>14673</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>18134</v>
+      </c>
+      <c r="F80" s="10" t="n">
+        <v>23910</v>
+      </c>
+      <c r="G80" s="10" t="n">
+        <v>22757</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Truck and travel</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="n">
+        <v>4307</v>
+      </c>
+      <c r="D81" s="10" t="n">
+        <v>10175</v>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>7805</v>
+      </c>
+      <c r="F81" s="10" t="n">
+        <v>11969</v>
+      </c>
+      <c r="G81" s="10" t="n">
+        <v>11486</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="18" t="n"/>
-      <c r="B82" s="18" t="inlineStr">
-        <is>
-          <t>Liabilities — current</t>
-        </is>
-      </c>
-      <c r="C82" s="18" t="n"/>
-      <c r="D82" s="18" t="n"/>
-      <c r="E82" s="18" t="n"/>
-      <c r="F82" s="18" t="n"/>
-      <c r="G82" s="18" t="n"/>
-      <c r="H82" s="18" t="n"/>
-      <c r="I82" s="18" t="n"/>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Amortization — building and shop equipment</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="n">
+        <v>89055</v>
+      </c>
+      <c r="D82" s="10" t="n">
+        <v>74522</v>
+      </c>
+      <c r="E82" s="10" t="n">
+        <v>53208</v>
+      </c>
+      <c r="F82" s="10" t="n">
+        <v>45953</v>
+      </c>
+      <c r="G82" s="10" t="n">
+        <v>42284</v>
+      </c>
+      <c r="I82" s="12" t="inlineStr">
+        <is>
+          <t>Non-cash; added back in cash flow.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="B83" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Bank loan</t>
-        </is>
-      </c>
-      <c r="C83" s="10" t="n">
-        <v>25000</v>
-      </c>
-      <c r="D83" s="10" t="n">
-        <v>11500</v>
-      </c>
-      <c r="E83" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" s="10" t="n">
-        <v>155242</v>
+      <c r="B83" s="14" t="inlineStr">
+        <is>
+          <t>Total indirect costs</t>
+        </is>
+      </c>
+      <c r="C83" s="15">
+        <f>SUM(C74:C82)</f>
+        <v/>
+      </c>
+      <c r="D83" s="15">
+        <f>SUM(D74:D82)</f>
+        <v/>
+      </c>
+      <c r="E83" s="15">
+        <f>SUM(E74:E82)</f>
+        <v/>
+      </c>
+      <c r="F83" s="15">
+        <f>SUM(F74:F82)</f>
+        <v/>
+      </c>
+      <c r="G83" s="15">
+        <f>SUM(G74:G82)</f>
+        <v/>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="C84" s="10" t="n">
-        <v>246579</v>
-      </c>
-      <c r="D84" s="10" t="n">
-        <v>269806</v>
-      </c>
-      <c r="E84" s="10" t="n">
-        <v>157001</v>
-      </c>
-      <c r="F84" s="10" t="n">
-        <v>148733</v>
-      </c>
-      <c r="G84" s="10" t="n">
-        <v>152022</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="B85" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Payroll deductions payable</t>
-        </is>
-      </c>
-      <c r="C85" s="10" t="n">
-        <v>2687</v>
-      </c>
-      <c r="D85" s="10" t="n">
-        <v>26638</v>
-      </c>
-      <c r="E85" s="10" t="n">
-        <v>6158</v>
-      </c>
-      <c r="F85" s="10" t="n">
-        <v>6157</v>
-      </c>
-      <c r="G85" s="10" t="n">
-        <v>10936</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Income tax payable</t>
-        </is>
-      </c>
-      <c r="C86" s="10" t="n">
-        <v>37030</v>
-      </c>
-      <c r="D86" s="10" t="n">
-        <v>10179</v>
-      </c>
-      <c r="E86" s="10" t="n">
-        <v>16792</v>
-      </c>
-      <c r="F86" s="10" t="n">
-        <v>30644</v>
-      </c>
-      <c r="G86" s="10" t="n">
-        <v>629</v>
-      </c>
+      <c r="B84" s="19" t="inlineStr">
+        <is>
+          <t>Total cost of sales</t>
+        </is>
+      </c>
+      <c r="C84" s="20">
+        <f>C67+C83</f>
+        <v/>
+      </c>
+      <c r="D84" s="20">
+        <f>D67+D83</f>
+        <v/>
+      </c>
+      <c r="E84" s="20">
+        <f>E67+E83</f>
+        <v/>
+      </c>
+      <c r="F84" s="20">
+        <f>F67+F83</f>
+        <v/>
+      </c>
+      <c r="G84" s="20">
+        <f>G67+G83</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="A86" s="8" t="n"/>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>BALANCE SHEET</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="n"/>
+      <c r="D86" s="8" t="n"/>
+      <c r="E86" s="8" t="n"/>
+      <c r="F86" s="8" t="n"/>
+      <c r="G86" s="8" t="n"/>
+      <c r="H86" s="8" t="n"/>
+      <c r="I86" s="8" t="n"/>
     </row>
     <row r="87">
-      <c r="B87" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Due to KEL Tooling, non-interest bearing</t>
-        </is>
-      </c>
-      <c r="C87" s="10" t="n">
-        <v>2239</v>
-      </c>
-      <c r="D87" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="A87" s="18" t="n"/>
+      <c r="B87" s="18" t="inlineStr">
+        <is>
+          <t>Assets — current</t>
+        </is>
+      </c>
+      <c r="C87" s="18" t="n"/>
+      <c r="D87" s="18" t="n"/>
+      <c r="E87" s="18" t="n"/>
+      <c r="F87" s="18" t="n"/>
+      <c r="G87" s="18" t="n"/>
+      <c r="H87" s="18" t="n"/>
+      <c r="I87" s="18" t="n"/>
     </row>
     <row r="88">
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Due to director</t>
+          <t xml:space="preserve">  Cash in bank</t>
         </is>
       </c>
       <c r="C88" s="10" t="n">
-        <v>0</v>
+        <v>301695</v>
       </c>
       <c r="D88" s="10" t="n">
-        <v>0</v>
+        <v>331894</v>
       </c>
       <c r="E88" s="10" t="n">
-        <v>6616</v>
+        <v>323927</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>6616</v>
+        <v>451664</v>
       </c>
       <c r="G88" s="10" t="n">
-        <v>0</v>
+        <v>700989</v>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="14" t="inlineStr">
-        <is>
-          <t>Total current liabilities</t>
-        </is>
-      </c>
-      <c r="C89" s="15">
-        <f>SUM(C83:C88)</f>
-        <v/>
-      </c>
-      <c r="D89" s="15">
-        <f>SUM(D83:D88)</f>
-        <v/>
-      </c>
-      <c r="E89" s="15">
-        <f>SUM(E83:E88)</f>
-        <v/>
-      </c>
-      <c r="F89" s="15">
-        <f>SUM(F83:F88)</f>
-        <v/>
-      </c>
-      <c r="G89" s="15">
-        <f>SUM(G83:G88)</f>
-        <v/>
+      <c r="B89" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Accounts receivable</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="n">
+        <v>174456</v>
+      </c>
+      <c r="D89" s="10" t="n">
+        <v>102521</v>
+      </c>
+      <c r="E89" s="10" t="n">
+        <v>172686</v>
+      </c>
+      <c r="F89" s="10" t="n">
+        <v>283263</v>
+      </c>
+      <c r="G89" s="10" t="n">
+        <v>249660</v>
       </c>
     </row>
     <row r="90">
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>Future income tax liability</t>
+          <t xml:space="preserve">  Government sales tax recoverable</t>
         </is>
       </c>
       <c r="C90" s="10" t="n">
-        <v>16039</v>
+        <v>10746</v>
       </c>
       <c r="D90" s="10" t="n">
-        <v>10090</v>
+        <v>8957</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>4211</v>
+        <v>11269</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>849</v>
+        <v>4041</v>
       </c>
       <c r="G90" s="10" t="n">
+        <v>10200</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Due from director</t>
+        </is>
+      </c>
+      <c r="C91" s="10" t="n">
+        <v>121461</v>
+      </c>
+      <c r="D91" s="10" t="n">
+        <v>243508</v>
+      </c>
+      <c r="E91" s="10" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="91">
-      <c r="B91" s="14" t="inlineStr">
-        <is>
-          <t>Total liabilities</t>
-        </is>
-      </c>
-      <c r="C91" s="15">
-        <f>C89+C90</f>
-        <v/>
-      </c>
-      <c r="D91" s="15">
-        <f>D89+D90</f>
-        <v/>
-      </c>
-      <c r="E91" s="15">
-        <f>E89+E90</f>
-        <v/>
-      </c>
-      <c r="F91" s="15">
-        <f>F89+F90</f>
-        <v/>
-      </c>
-      <c r="G91" s="15">
-        <f>G89+G90</f>
-        <v/>
+      <c r="F91" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="10" t="n">
+        <v>6193</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="18" t="n"/>
-      <c r="B92" s="18" t="inlineStr">
-        <is>
-          <t>Shareholders' equity</t>
-        </is>
-      </c>
-      <c r="C92" s="18" t="n"/>
-      <c r="D92" s="18" t="n"/>
-      <c r="E92" s="18" t="n"/>
-      <c r="F92" s="18" t="n"/>
-      <c r="G92" s="18" t="n"/>
-      <c r="H92" s="18" t="n"/>
-      <c r="I92" s="18" t="n"/>
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Due from KEL Tooling, non-interest bearing</t>
+        </is>
+      </c>
+      <c r="C92" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>23308</v>
+      </c>
+      <c r="F92" s="10" t="n">
+        <v>16108</v>
+      </c>
+      <c r="G92" s="10" t="n">
+        <v>8908</v>
+      </c>
     </row>
     <row r="93">
-      <c r="B93" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Share capital</t>
-        </is>
-      </c>
-      <c r="C93" s="10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D93" s="10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E93" s="10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F93" s="10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G93" s="10" t="n">
-        <v>1000</v>
+      <c r="B93" s="14" t="inlineStr">
+        <is>
+          <t>Total current assets</t>
+        </is>
+      </c>
+      <c r="C93" s="15">
+        <f>SUM(C88:C92)</f>
+        <v/>
+      </c>
+      <c r="D93" s="15">
+        <f>SUM(D88:D92)</f>
+        <v/>
+      </c>
+      <c r="E93" s="15">
+        <f>SUM(E88:E92)</f>
+        <v/>
+      </c>
+      <c r="F93" s="15">
+        <f>SUM(F88:F92)</f>
+        <v/>
+      </c>
+      <c r="G93" s="15">
+        <f>SUM(G88:G92)</f>
+        <v/>
       </c>
     </row>
     <row r="94">
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Retained earnings</t>
-        </is>
-      </c>
-      <c r="C94" s="13">
-        <f>C42</f>
-        <v/>
-      </c>
-      <c r="D94" s="13">
-        <f>D42</f>
-        <v/>
-      </c>
-      <c r="E94" s="13">
-        <f>E42</f>
-        <v/>
-      </c>
-      <c r="F94" s="13">
-        <f>F42</f>
-        <v/>
-      </c>
-      <c r="G94" s="13">
-        <f>G42</f>
-        <v/>
-      </c>
-      <c r="I94" s="12" t="inlineStr">
-        <is>
-          <t>Links to retained earnings, end of year (Income Statement).</t>
-        </is>
+          <t>Due from Related Group of Companies</t>
+        </is>
+      </c>
+      <c r="C94" s="10" t="n">
+        <v>24277</v>
+      </c>
+      <c r="D94" s="10" t="n">
+        <v>24277</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>12780</v>
+      </c>
+      <c r="F94" s="10" t="n">
+        <v>16132</v>
+      </c>
+      <c r="G94" s="10" t="n">
+        <v>18139</v>
       </c>
     </row>
     <row r="95">
-      <c r="B95" s="14" t="inlineStr">
-        <is>
-          <t>Total shareholders' equity</t>
-        </is>
-      </c>
-      <c r="C95" s="15">
-        <f>C93+C94</f>
-        <v/>
-      </c>
-      <c r="D95" s="15">
-        <f>D93+D94</f>
-        <v/>
-      </c>
-      <c r="E95" s="15">
-        <f>E93+E94</f>
-        <v/>
-      </c>
-      <c r="F95" s="15">
-        <f>F93+F94</f>
-        <v/>
-      </c>
-      <c r="G95" s="15">
-        <f>G93+G94</f>
-        <v/>
+      <c r="B95" s="9" t="inlineStr">
+        <is>
+          <t>Land, buildings and equipment, net</t>
+        </is>
+      </c>
+      <c r="C95" s="10" t="n">
+        <v>570987</v>
+      </c>
+      <c r="D95" s="10" t="n">
+        <v>513774</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>441755</v>
+      </c>
+      <c r="F95" s="10" t="n">
+        <v>403824</v>
+      </c>
+      <c r="G95" s="10" t="n">
+        <v>502314</v>
+      </c>
+      <c r="I95" s="12" t="inlineStr">
+        <is>
+          <t>Net of accumulated amortization.</t>
+        </is>
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="21" t="inlineStr">
-        <is>
-          <t>TOTAL LIABILITIES AND EQUITY</t>
-        </is>
-      </c>
-      <c r="C96" s="22">
-        <f>C91+C95</f>
-        <v/>
-      </c>
-      <c r="D96" s="22">
-        <f>D91+D95</f>
-        <v/>
-      </c>
-      <c r="E96" s="22">
-        <f>E91+E95</f>
-        <v/>
-      </c>
-      <c r="F96" s="22">
-        <f>F91+F95</f>
-        <v/>
-      </c>
-      <c r="G96" s="22">
-        <f>G91+G95</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97">
-      <c r="B97" s="9" t="inlineStr">
-        <is>
-          <t>Balance check (Total assets − Total liabilities &amp; equity)</t>
-        </is>
-      </c>
-      <c r="C97" s="13">
-        <f>C80-C96</f>
-        <v/>
-      </c>
-      <c r="D97" s="13">
-        <f>D80-D96</f>
-        <v/>
-      </c>
-      <c r="E97" s="13">
-        <f>E80-E96</f>
-        <v/>
-      </c>
-      <c r="F97" s="13">
-        <f>F80-F96</f>
-        <v/>
-      </c>
-      <c r="G97" s="13">
-        <f>G80-G96</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99" ht="18" customHeight="1">
-      <c r="A99" s="8" t="n"/>
-      <c r="B99" s="8" t="inlineStr">
-        <is>
-          <t>CASH FLOW STATEMENT (implied from balance sheet &amp; income statement)</t>
-        </is>
-      </c>
-      <c r="C99" s="8" t="n"/>
-      <c r="D99" s="8" t="n"/>
-      <c r="E99" s="8" t="n"/>
-      <c r="F99" s="8" t="n"/>
-      <c r="G99" s="8" t="n"/>
-      <c r="H99" s="8" t="n"/>
-      <c r="I99" s="8" t="n"/>
+      <c r="B96" s="23" t="inlineStr">
+        <is>
+          <t>TOTAL ASSETS</t>
+        </is>
+      </c>
+      <c r="C96" s="24">
+        <f>C93+C94+C95</f>
+        <v/>
+      </c>
+      <c r="D96" s="24">
+        <f>D93+D94+D95</f>
+        <v/>
+      </c>
+      <c r="E96" s="24">
+        <f>E93+E94+E95</f>
+        <v/>
+      </c>
+      <c r="F96" s="24">
+        <f>F93+F94+F95</f>
+        <v/>
+      </c>
+      <c r="G96" s="24">
+        <f>G93+G94+G95</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="18" t="n"/>
+      <c r="B98" s="18" t="inlineStr">
+        <is>
+          <t>Liabilities — current</t>
+        </is>
+      </c>
+      <c r="C98" s="18" t="n"/>
+      <c r="D98" s="18" t="n"/>
+      <c r="E98" s="18" t="n"/>
+      <c r="F98" s="18" t="n"/>
+      <c r="G98" s="18" t="n"/>
+      <c r="H98" s="18" t="n"/>
+      <c r="I98" s="18" t="n"/>
+    </row>
+    <row r="99">
+      <c r="B99" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Bank loan</t>
+        </is>
+      </c>
+      <c r="C99" s="10" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D99" s="10" t="n">
+        <v>11500</v>
+      </c>
+      <c r="E99" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="10" t="n">
+        <v>155242</v>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="18" t="n"/>
-      <c r="B100" s="18" t="inlineStr">
-        <is>
-          <t>Operating activities</t>
-        </is>
-      </c>
-      <c r="C100" s="18" t="n"/>
-      <c r="D100" s="18" t="n"/>
-      <c r="E100" s="18" t="n"/>
-      <c r="F100" s="18" t="n"/>
-      <c r="G100" s="18" t="n"/>
-      <c r="H100" s="18" t="n"/>
-      <c r="I100" s="18" t="n"/>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="C100" s="10" t="n">
+        <v>246579</v>
+      </c>
+      <c r="D100" s="10" t="n">
+        <v>269806</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>157001</v>
+      </c>
+      <c r="F100" s="10" t="n">
+        <v>148733</v>
+      </c>
+      <c r="G100" s="10" t="n">
+        <v>152022</v>
+      </c>
     </row>
     <row r="101">
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Net income for the year</t>
-        </is>
-      </c>
-      <c r="C101" s="13" t="n"/>
-      <c r="D101" s="13">
-        <f>D36</f>
-        <v/>
-      </c>
-      <c r="E101" s="13">
-        <f>E36</f>
-        <v/>
-      </c>
-      <c r="F101" s="13">
-        <f>F36</f>
-        <v/>
-      </c>
-      <c r="G101" s="13">
-        <f>G36</f>
-        <v/>
+          <t xml:space="preserve">  Payroll deductions payable</t>
+        </is>
+      </c>
+      <c r="C101" s="10" t="n">
+        <v>2687</v>
+      </c>
+      <c r="D101" s="10" t="n">
+        <v>26638</v>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>6158</v>
+      </c>
+      <c r="F101" s="10" t="n">
+        <v>6157</v>
+      </c>
+      <c r="G101" s="10" t="n">
+        <v>10936</v>
       </c>
     </row>
     <row r="102">
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Add: amortization — office equipment</t>
-        </is>
-      </c>
-      <c r="C102" s="13" t="n"/>
-      <c r="D102" s="13">
-        <f>D19</f>
-        <v/>
-      </c>
-      <c r="E102" s="13">
-        <f>E19</f>
-        <v/>
-      </c>
-      <c r="F102" s="13">
-        <f>F19</f>
-        <v/>
-      </c>
-      <c r="G102" s="13">
-        <f>G19</f>
-        <v/>
+          <t xml:space="preserve">  Income tax payable</t>
+        </is>
+      </c>
+      <c r="C102" s="10" t="n">
+        <v>37030</v>
+      </c>
+      <c r="D102" s="10" t="n">
+        <v>10179</v>
+      </c>
+      <c r="E102" s="10" t="n">
+        <v>16792</v>
+      </c>
+      <c r="F102" s="10" t="n">
+        <v>30644</v>
+      </c>
+      <c r="G102" s="10" t="n">
+        <v>629</v>
       </c>
     </row>
     <row r="103">
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Add: amortization — building and shop equipment</t>
-        </is>
-      </c>
-      <c r="C103" s="13" t="n"/>
-      <c r="D103" s="13">
-        <f>D66</f>
-        <v/>
-      </c>
-      <c r="E103" s="13">
-        <f>E66</f>
-        <v/>
-      </c>
-      <c r="F103" s="13">
-        <f>F66</f>
-        <v/>
-      </c>
-      <c r="G103" s="13">
-        <f>G66</f>
-        <v/>
+          <t xml:space="preserve">  Due to KEL Tooling, non-interest bearing</t>
+        </is>
+      </c>
+      <c r="C103" s="10" t="n">
+        <v>2239</v>
+      </c>
+      <c r="D103" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Increase / (decrease) in future income tax liability</t>
-        </is>
-      </c>
-      <c r="C104" s="13" t="n"/>
-      <c r="D104" s="13">
-        <f>D90-C90</f>
-        <v/>
-      </c>
-      <c r="E104" s="13">
-        <f>E90-D90</f>
-        <v/>
-      </c>
-      <c r="F104" s="13">
-        <f>F90-E90</f>
-        <v/>
-      </c>
-      <c r="G104" s="13">
-        <f>G90-F90</f>
-        <v/>
+          <t xml:space="preserve">  Due to director</t>
+        </is>
+      </c>
+      <c r="C104" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>6616</v>
+      </c>
+      <c r="F104" s="10" t="n">
+        <v>6616</v>
+      </c>
+      <c r="G104" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="B105" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (Increase) / decrease in accounts receivable</t>
-        </is>
-      </c>
-      <c r="C105" s="13" t="n"/>
-      <c r="D105" s="13">
-        <f>-(D73-C73)</f>
-        <v/>
-      </c>
-      <c r="E105" s="13">
-        <f>-(E73-D73)</f>
-        <v/>
-      </c>
-      <c r="F105" s="13">
-        <f>-(F73-E73)</f>
-        <v/>
-      </c>
-      <c r="G105" s="13">
-        <f>-(G73-F73)</f>
+      <c r="B105" s="14" t="inlineStr">
+        <is>
+          <t>Total current liabilities</t>
+        </is>
+      </c>
+      <c r="C105" s="15">
+        <f>SUM(C99:C104)</f>
+        <v/>
+      </c>
+      <c r="D105" s="15">
+        <f>SUM(D99:D104)</f>
+        <v/>
+      </c>
+      <c r="E105" s="15">
+        <f>SUM(E99:E104)</f>
+        <v/>
+      </c>
+      <c r="F105" s="15">
+        <f>SUM(F99:F104)</f>
+        <v/>
+      </c>
+      <c r="G105" s="15">
+        <f>SUM(G99:G104)</f>
         <v/>
       </c>
     </row>
     <row r="106">
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (Increase) / decrease in government sales tax recoverable</t>
-        </is>
-      </c>
-      <c r="C106" s="13" t="n"/>
-      <c r="D106" s="13">
-        <f>-(D74-C74)</f>
-        <v/>
-      </c>
-      <c r="E106" s="13">
-        <f>-(E74-D74)</f>
-        <v/>
-      </c>
-      <c r="F106" s="13">
-        <f>-(F74-E74)</f>
-        <v/>
-      </c>
-      <c r="G106" s="13">
-        <f>-(G74-F74)</f>
-        <v/>
+          <t>Future income tax liability</t>
+        </is>
+      </c>
+      <c r="C106" s="10" t="n">
+        <v>16039</v>
+      </c>
+      <c r="D106" s="10" t="n">
+        <v>10090</v>
+      </c>
+      <c r="E106" s="10" t="n">
+        <v>4211</v>
+      </c>
+      <c r="F106" s="10" t="n">
+        <v>849</v>
+      </c>
+      <c r="G106" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="B107" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Increase / (decrease) in accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="C107" s="13" t="n"/>
-      <c r="D107" s="13">
-        <f>D84-C84</f>
-        <v/>
-      </c>
-      <c r="E107" s="13">
-        <f>E84-D84</f>
-        <v/>
-      </c>
-      <c r="F107" s="13">
-        <f>F84-E84</f>
-        <v/>
-      </c>
-      <c r="G107" s="13">
-        <f>G84-F84</f>
+      <c r="B107" s="14" t="inlineStr">
+        <is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="C107" s="15">
+        <f>C105+C106</f>
+        <v/>
+      </c>
+      <c r="D107" s="15">
+        <f>D105+D106</f>
+        <v/>
+      </c>
+      <c r="E107" s="15">
+        <f>E105+E106</f>
+        <v/>
+      </c>
+      <c r="F107" s="15">
+        <f>F105+F106</f>
+        <v/>
+      </c>
+      <c r="G107" s="15">
+        <f>G105+G106</f>
         <v/>
       </c>
     </row>
     <row r="108">
-      <c r="B108" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Increase / (decrease) in payroll deductions payable</t>
-        </is>
-      </c>
-      <c r="C108" s="13" t="n"/>
-      <c r="D108" s="13">
-        <f>D85-C85</f>
-        <v/>
-      </c>
-      <c r="E108" s="13">
-        <f>E85-D85</f>
-        <v/>
-      </c>
-      <c r="F108" s="13">
-        <f>F85-E85</f>
-        <v/>
-      </c>
-      <c r="G108" s="13">
-        <f>G85-F85</f>
-        <v/>
-      </c>
+      <c r="A108" s="18" t="n"/>
+      <c r="B108" s="18" t="inlineStr">
+        <is>
+          <t>Shareholders' equity</t>
+        </is>
+      </c>
+      <c r="C108" s="18" t="n"/>
+      <c r="D108" s="18" t="n"/>
+      <c r="E108" s="18" t="n"/>
+      <c r="F108" s="18" t="n"/>
+      <c r="G108" s="18" t="n"/>
+      <c r="H108" s="18" t="n"/>
+      <c r="I108" s="18" t="n"/>
     </row>
     <row r="109">
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Increase / (decrease) in income tax payable</t>
-        </is>
-      </c>
-      <c r="C109" s="13" t="n"/>
-      <c r="D109" s="13">
-        <f>D86-C86</f>
-        <v/>
-      </c>
-      <c r="E109" s="13">
-        <f>E86-D86</f>
-        <v/>
-      </c>
-      <c r="F109" s="13">
-        <f>F86-E86</f>
-        <v/>
-      </c>
-      <c r="G109" s="13">
-        <f>G86-F86</f>
-        <v/>
+          <t xml:space="preserve">  Share capital</t>
+        </is>
+      </c>
+      <c r="C109" s="10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D109" s="10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E109" s="10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F109" s="10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G109" s="10" t="n">
+        <v>1000</v>
       </c>
     </row>
     <row r="110">
-      <c r="B110" s="14" t="inlineStr">
-        <is>
-          <t>Net cash from operating activities</t>
-        </is>
-      </c>
-      <c r="C110" s="15" t="n"/>
-      <c r="D110" s="15">
-        <f>SUM(D101:D109)</f>
-        <v/>
-      </c>
-      <c r="E110" s="15">
-        <f>SUM(E101:E109)</f>
-        <v/>
-      </c>
-      <c r="F110" s="15">
-        <f>SUM(F101:F109)</f>
-        <v/>
-      </c>
-      <c r="G110" s="15">
-        <f>SUM(G101:G109)</f>
-        <v/>
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Retained earnings</t>
+        </is>
+      </c>
+      <c r="C110" s="13">
+        <f>C53</f>
+        <v/>
+      </c>
+      <c r="D110" s="13">
+        <f>D53</f>
+        <v/>
+      </c>
+      <c r="E110" s="13">
+        <f>E53</f>
+        <v/>
+      </c>
+      <c r="F110" s="13">
+        <f>F53</f>
+        <v/>
+      </c>
+      <c r="G110" s="13">
+        <f>G53</f>
+        <v/>
+      </c>
+      <c r="I110" s="12" t="inlineStr">
+        <is>
+          <t>Links to retained earnings, end of year (Income Statement).</t>
+        </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="18" t="n"/>
-      <c r="B111" s="18" t="inlineStr">
-        <is>
-          <t>Investing activities</t>
-        </is>
-      </c>
-      <c r="C111" s="18" t="n"/>
-      <c r="D111" s="18" t="n"/>
-      <c r="E111" s="18" t="n"/>
-      <c r="F111" s="18" t="n"/>
-      <c r="G111" s="18" t="n"/>
-      <c r="H111" s="18" t="n"/>
-      <c r="I111" s="18" t="n"/>
+      <c r="B111" s="14" t="inlineStr">
+        <is>
+          <t>Total shareholders' equity</t>
+        </is>
+      </c>
+      <c r="C111" s="15">
+        <f>C109+C110</f>
+        <v/>
+      </c>
+      <c r="D111" s="15">
+        <f>D109+D110</f>
+        <v/>
+      </c>
+      <c r="E111" s="15">
+        <f>E109+E110</f>
+        <v/>
+      </c>
+      <c r="F111" s="15">
+        <f>F109+F110</f>
+        <v/>
+      </c>
+      <c r="G111" s="15">
+        <f>G109+G110</f>
+        <v/>
+      </c>
     </row>
     <row r="112">
-      <c r="B112" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Purchase of land, buildings and equipment (implied)</t>
-        </is>
-      </c>
-      <c r="C112" s="13" t="n"/>
-      <c r="D112" s="13">
-        <f>-((D79-C79)+D19+D66)</f>
-        <v/>
-      </c>
-      <c r="E112" s="13">
-        <f>-((E79-D79)+E19+E66)</f>
-        <v/>
-      </c>
-      <c r="F112" s="13">
-        <f>-((F79-E79)+F19+F66)</f>
-        <v/>
-      </c>
-      <c r="G112" s="13">
-        <f>-((G79-F79)+G19+G66)</f>
-        <v/>
-      </c>
-      <c r="I112" s="12" t="inlineStr">
-        <is>
-          <t>Implied capex = Δ net PP&amp;E + total amortization (office + building/shop).</t>
-        </is>
+      <c r="B112" s="23" t="inlineStr">
+        <is>
+          <t>TOTAL LIABILITIES AND EQUITY</t>
+        </is>
+      </c>
+      <c r="C112" s="24">
+        <f>C107+C111</f>
+        <v/>
+      </c>
+      <c r="D112" s="24">
+        <f>D107+D111</f>
+        <v/>
+      </c>
+      <c r="E112" s="24">
+        <f>E107+E111</f>
+        <v/>
+      </c>
+      <c r="F112" s="24">
+        <f>F107+F111</f>
+        <v/>
+      </c>
+      <c r="G112" s="24">
+        <f>G107+G111</f>
+        <v/>
       </c>
     </row>
     <row r="113">
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (Increase) / decrease in due from Related Group of Companies</t>
-        </is>
-      </c>
-      <c r="C113" s="13" t="n"/>
+          <t>Balance check (Total assets − Total liabilities &amp; equity)</t>
+        </is>
+      </c>
+      <c r="C113" s="13">
+        <f>C96-C112</f>
+        <v/>
+      </c>
       <c r="D113" s="13">
-        <f>-(D78-C78)</f>
+        <f>D96-D112</f>
         <v/>
       </c>
       <c r="E113" s="13">
-        <f>-(E78-D78)</f>
+        <f>E96-E112</f>
         <v/>
       </c>
       <c r="F113" s="13">
-        <f>-(F78-E78)</f>
+        <f>F96-F112</f>
         <v/>
       </c>
       <c r="G113" s="13">
-        <f>-(G78-F78)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="114">
-      <c r="B114" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (Increase) / decrease in due from director</t>
-        </is>
-      </c>
-      <c r="C114" s="13" t="n"/>
-      <c r="D114" s="13">
-        <f>-(D75-C75)</f>
-        <v/>
-      </c>
-      <c r="E114" s="13">
-        <f>-(E75-D75)</f>
-        <v/>
-      </c>
-      <c r="F114" s="13">
-        <f>-(F75-E75)</f>
-        <v/>
-      </c>
-      <c r="G114" s="13">
-        <f>-(G75-F75)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="115">
-      <c r="B115" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (Increase) / decrease in due from KEL Tooling</t>
-        </is>
-      </c>
-      <c r="C115" s="13" t="n"/>
-      <c r="D115" s="13">
-        <f>-(D76-C76)</f>
-        <v/>
-      </c>
-      <c r="E115" s="13">
-        <f>-(E76-D76)</f>
-        <v/>
-      </c>
-      <c r="F115" s="13">
-        <f>-(F76-E76)</f>
-        <v/>
-      </c>
-      <c r="G115" s="13">
-        <f>-(G76-F76)</f>
-        <v/>
-      </c>
+        <f>G96-G112</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="A115" s="8" t="n"/>
+      <c r="B115" s="8" t="inlineStr">
+        <is>
+          <t>CASH FLOW STATEMENT (implied from balance sheet &amp; income statement)</t>
+        </is>
+      </c>
+      <c r="C115" s="8" t="n"/>
+      <c r="D115" s="8" t="n"/>
+      <c r="E115" s="8" t="n"/>
+      <c r="F115" s="8" t="n"/>
+      <c r="G115" s="8" t="n"/>
+      <c r="H115" s="8" t="n"/>
+      <c r="I115" s="8" t="n"/>
     </row>
     <row r="116">
-      <c r="B116" s="14" t="inlineStr">
-        <is>
-          <t>Net cash from investing activities</t>
-        </is>
-      </c>
-      <c r="C116" s="15" t="n"/>
-      <c r="D116" s="15">
-        <f>SUM(D112:D115)</f>
-        <v/>
-      </c>
-      <c r="E116" s="15">
-        <f>SUM(E112:E115)</f>
-        <v/>
-      </c>
-      <c r="F116" s="15">
-        <f>SUM(F112:F115)</f>
-        <v/>
-      </c>
-      <c r="G116" s="15">
-        <f>SUM(G112:G115)</f>
-        <v/>
-      </c>
+      <c r="A116" s="18" t="n"/>
+      <c r="B116" s="18" t="inlineStr">
+        <is>
+          <t>Operating activities</t>
+        </is>
+      </c>
+      <c r="C116" s="18" t="n"/>
+      <c r="D116" s="18" t="n"/>
+      <c r="E116" s="18" t="n"/>
+      <c r="F116" s="18" t="n"/>
+      <c r="G116" s="18" t="n"/>
+      <c r="H116" s="18" t="n"/>
+      <c r="I116" s="18" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" s="18" t="n"/>
-      <c r="B117" s="18" t="inlineStr">
-        <is>
-          <t>Financing activities</t>
-        </is>
-      </c>
-      <c r="C117" s="18" t="n"/>
-      <c r="D117" s="18" t="n"/>
-      <c r="E117" s="18" t="n"/>
-      <c r="F117" s="18" t="n"/>
-      <c r="G117" s="18" t="n"/>
-      <c r="H117" s="18" t="n"/>
-      <c r="I117" s="18" t="n"/>
+      <c r="B117" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Net income for the year</t>
+        </is>
+      </c>
+      <c r="C117" s="13" t="n"/>
+      <c r="D117" s="13">
+        <f>D36</f>
+        <v/>
+      </c>
+      <c r="E117" s="13">
+        <f>E36</f>
+        <v/>
+      </c>
+      <c r="F117" s="13">
+        <f>F36</f>
+        <v/>
+      </c>
+      <c r="G117" s="13">
+        <f>G36</f>
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Increase / (decrease) in bank loan</t>
+          <t xml:space="preserve">  Add: amortization — office equipment</t>
         </is>
       </c>
       <c r="C118" s="13" t="n"/>
       <c r="D118" s="13">
-        <f>D83-C83</f>
+        <f>D19</f>
         <v/>
       </c>
       <c r="E118" s="13">
-        <f>E83-D83</f>
+        <f>E19</f>
         <v/>
       </c>
       <c r="F118" s="13">
-        <f>F83-E83</f>
+        <f>F19</f>
         <v/>
       </c>
       <c r="G118" s="13">
-        <f>G83-F83</f>
+        <f>G19</f>
         <v/>
       </c>
     </row>
     <row r="119">
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Increase / (decrease) in due to director</t>
+          <t xml:space="preserve">  Add: amortization — building and shop equipment</t>
         </is>
       </c>
       <c r="C119" s="13" t="n"/>
       <c r="D119" s="13">
-        <f>D88-C88</f>
+        <f>D82</f>
         <v/>
       </c>
       <c r="E119" s="13">
-        <f>E88-D88</f>
+        <f>E82</f>
         <v/>
       </c>
       <c r="F119" s="13">
-        <f>F88-E88</f>
+        <f>F82</f>
         <v/>
       </c>
       <c r="G119" s="13">
-        <f>G88-F88</f>
+        <f>G82</f>
         <v/>
       </c>
     </row>
     <row r="120">
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Increase / (decrease) in due to KEL Tooling</t>
+          <t xml:space="preserve">  Increase / (decrease) in future income tax liability</t>
         </is>
       </c>
       <c r="C120" s="13" t="n"/>
       <c r="D120" s="13">
-        <f>D87-C87</f>
+        <f>D106-C106</f>
         <v/>
       </c>
       <c r="E120" s="13">
-        <f>E87-D87</f>
+        <f>E106-D106</f>
         <v/>
       </c>
       <c r="F120" s="13">
-        <f>F87-E87</f>
+        <f>F106-E106</f>
         <v/>
       </c>
       <c r="G120" s="13">
-        <f>G87-F87</f>
+        <f>G106-F106</f>
         <v/>
       </c>
     </row>
     <row r="121">
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Dividends paid</t>
+          <t xml:space="preserve">  (Increase) / decrease in accounts receivable</t>
         </is>
       </c>
       <c r="C121" s="13" t="n"/>
       <c r="D121" s="13">
-        <f>-D41</f>
+        <f>-(D89-C89)</f>
         <v/>
       </c>
       <c r="E121" s="13">
-        <f>-E41</f>
+        <f>-(E89-D89)</f>
         <v/>
       </c>
       <c r="F121" s="13">
-        <f>-F41</f>
+        <f>-(F89-E89)</f>
         <v/>
       </c>
       <c r="G121" s="13">
-        <f>-G41</f>
+        <f>-(G89-F89)</f>
         <v/>
       </c>
     </row>
     <row r="122">
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Issuance of share capital</t>
+          <t xml:space="preserve">  (Increase) / decrease in government sales tax recoverable</t>
         </is>
       </c>
       <c r="C122" s="13" t="n"/>
       <c r="D122" s="13">
-        <f>D93-C93</f>
+        <f>-(D90-C90)</f>
         <v/>
       </c>
       <c r="E122" s="13">
-        <f>E93-D93</f>
+        <f>-(E90-D90)</f>
         <v/>
       </c>
       <c r="F122" s="13">
-        <f>F93-E93</f>
+        <f>-(F90-E90)</f>
         <v/>
       </c>
       <c r="G122" s="13">
-        <f>G93-F93</f>
+        <f>-(G90-F90)</f>
         <v/>
       </c>
     </row>
     <row r="123">
-      <c r="B123" s="14" t="inlineStr">
-        <is>
-          <t>Net cash from financing activities</t>
-        </is>
-      </c>
-      <c r="C123" s="15" t="n"/>
-      <c r="D123" s="15">
-        <f>SUM(D118:D122)</f>
-        <v/>
-      </c>
-      <c r="E123" s="15">
-        <f>SUM(E118:E122)</f>
-        <v/>
-      </c>
-      <c r="F123" s="15">
-        <f>SUM(F118:F122)</f>
-        <v/>
-      </c>
-      <c r="G123" s="15">
-        <f>SUM(G118:G122)</f>
+      <c r="B123" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Increase / (decrease) in accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="C123" s="13" t="n"/>
+      <c r="D123" s="13">
+        <f>D100-C100</f>
+        <v/>
+      </c>
+      <c r="E123" s="13">
+        <f>E100-D100</f>
+        <v/>
+      </c>
+      <c r="F123" s="13">
+        <f>F100-E100</f>
+        <v/>
+      </c>
+      <c r="G123" s="13">
+        <f>G100-F100</f>
         <v/>
       </c>
     </row>
     <row r="124">
-      <c r="B124" s="19" t="inlineStr">
-        <is>
-          <t>Net change in cash</t>
-        </is>
-      </c>
-      <c r="C124" s="20">
-        <f>C110+C116+C123</f>
-        <v/>
-      </c>
-      <c r="D124" s="20">
-        <f>D110+D116+D123</f>
-        <v/>
-      </c>
-      <c r="E124" s="20">
-        <f>E110+E116+E123</f>
-        <v/>
-      </c>
-      <c r="F124" s="20">
-        <f>F110+F116+F123</f>
-        <v/>
-      </c>
-      <c r="G124" s="20">
-        <f>G110+G116+G123</f>
+      <c r="B124" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Increase / (decrease) in payroll deductions payable</t>
+        </is>
+      </c>
+      <c r="C124" s="13" t="n"/>
+      <c r="D124" s="13">
+        <f>D101-C101</f>
+        <v/>
+      </c>
+      <c r="E124" s="13">
+        <f>E101-D101</f>
+        <v/>
+      </c>
+      <c r="F124" s="13">
+        <f>F101-E101</f>
+        <v/>
+      </c>
+      <c r="G124" s="13">
+        <f>G101-F101</f>
         <v/>
       </c>
     </row>
     <row r="125">
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
+          <t xml:space="preserve">  Increase / (decrease) in income tax payable</t>
         </is>
       </c>
       <c r="C125" s="13" t="n"/>
       <c r="D125" s="13">
-        <f>C72</f>
+        <f>D102-C102</f>
         <v/>
       </c>
       <c r="E125" s="13">
-        <f>D72</f>
+        <f>E102-D102</f>
         <v/>
       </c>
       <c r="F125" s="13">
-        <f>E72</f>
+        <f>F102-E102</f>
         <v/>
       </c>
       <c r="G125" s="13">
-        <f>F72</f>
+        <f>G102-F102</f>
         <v/>
       </c>
     </row>
     <row r="126">
       <c r="B126" s="14" t="inlineStr">
         <is>
-          <t>Cash, end of year</t>
+          <t>Net cash from operating activities</t>
         </is>
       </c>
       <c r="C126" s="15" t="n"/>
       <c r="D126" s="15">
-        <f>D125+D124</f>
+        <f>SUM(D117:D125)</f>
         <v/>
       </c>
       <c r="E126" s="15">
-        <f>E125+E124</f>
+        <f>SUM(E117:E125)</f>
         <v/>
       </c>
       <c r="F126" s="15">
-        <f>F125+F124</f>
+        <f>SUM(F117:F125)</f>
         <v/>
       </c>
       <c r="G126" s="15">
-        <f>G125+G124</f>
+        <f>SUM(G117:G125)</f>
         <v/>
       </c>
     </row>
     <row r="127">
-      <c r="B127" s="9" t="inlineStr">
-        <is>
-          <t>Tie-out check (implied ending cash − balance sheet cash)</t>
-        </is>
-      </c>
-      <c r="C127" s="13">
-        <f>C126-C72</f>
-        <v/>
-      </c>
-      <c r="D127" s="13">
-        <f>D126-D72</f>
-        <v/>
-      </c>
-      <c r="E127" s="13">
-        <f>E126-E72</f>
-        <v/>
-      </c>
-      <c r="F127" s="13">
-        <f>F126-F72</f>
-        <v/>
-      </c>
-      <c r="G127" s="13">
-        <f>G126-G72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="129" ht="18" customHeight="1">
-      <c r="A129" s="8" t="n"/>
-      <c r="B129" s="8" t="inlineStr">
-        <is>
-          <t>RATIO ANALYSIS &amp; FREE CASH FLOW</t>
-        </is>
-      </c>
-      <c r="C129" s="8" t="n"/>
-      <c r="D129" s="8" t="n"/>
-      <c r="E129" s="8" t="n"/>
-      <c r="F129" s="8" t="n"/>
-      <c r="G129" s="8" t="n"/>
-      <c r="H129" s="8" t="n"/>
-      <c r="I129" s="8" t="n"/>
+      <c r="A127" s="18" t="n"/>
+      <c r="B127" s="18" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C127" s="18" t="n"/>
+      <c r="D127" s="18" t="n"/>
+      <c r="E127" s="18" t="n"/>
+      <c r="F127" s="18" t="n"/>
+      <c r="G127" s="18" t="n"/>
+      <c r="H127" s="18" t="n"/>
+      <c r="I127" s="18" t="n"/>
+    </row>
+    <row r="128">
+      <c r="B128" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Purchase of land, buildings and equipment (implied)</t>
+        </is>
+      </c>
+      <c r="C128" s="13" t="n"/>
+      <c r="D128" s="13">
+        <f>-((D95-C95)+D19+D82)</f>
+        <v/>
+      </c>
+      <c r="E128" s="13">
+        <f>-((E95-D95)+E19+E82)</f>
+        <v/>
+      </c>
+      <c r="F128" s="13">
+        <f>-((F95-E95)+F19+F82)</f>
+        <v/>
+      </c>
+      <c r="G128" s="13">
+        <f>-((G95-F95)+G19+G82)</f>
+        <v/>
+      </c>
+      <c r="I128" s="12" t="inlineStr">
+        <is>
+          <t>Implied capex = Δ net PP&amp;E + total amortization. A positive figure here is a cash inflow (net disposals &gt; additions), as in FY2023.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" s="14" t="inlineStr">
+        <is>
+          <t>Net cash from investing activities</t>
+        </is>
+      </c>
+      <c r="C129" s="15" t="n"/>
+      <c r="D129" s="15">
+        <f>SUM(D128:D128)</f>
+        <v/>
+      </c>
+      <c r="E129" s="15">
+        <f>SUM(E128:E128)</f>
+        <v/>
+      </c>
+      <c r="F129" s="15">
+        <f>SUM(F128:F128)</f>
+        <v/>
+      </c>
+      <c r="G129" s="15">
+        <f>SUM(G128:G128)</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="18" t="n"/>
       <c r="B130" s="18" t="inlineStr">
         <is>
-          <t>Cash generation</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C130" s="18" t="n"/>
@@ -3280,407 +3335,1808 @@
     <row r="131">
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Free cash flow (CFO − capex)</t>
-        </is>
-      </c>
-      <c r="C131" s="13">
-        <f>C110+C112</f>
-        <v/>
-      </c>
+          <t xml:space="preserve">  Increase / (decrease) in bank loan</t>
+        </is>
+      </c>
+      <c r="C131" s="13" t="n"/>
       <c r="D131" s="13">
-        <f>D110+D112</f>
+        <f>D99-C99</f>
         <v/>
       </c>
       <c r="E131" s="13">
-        <f>E110+E112</f>
+        <f>E99-D99</f>
         <v/>
       </c>
       <c r="F131" s="13">
-        <f>F110+F112</f>
+        <f>F99-E99</f>
         <v/>
       </c>
       <c r="G131" s="13">
-        <f>G110+G112</f>
+        <f>G99-F99</f>
         <v/>
       </c>
     </row>
     <row r="132">
-      <c r="B132" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  FCF conversion (FCF / net income)</t>
-        </is>
-      </c>
-      <c r="C132" s="23" t="n"/>
-      <c r="D132" s="23">
-        <f>IFERROR((D110+D112)/D36,"")</f>
-        <v/>
-      </c>
-      <c r="E132" s="23">
-        <f>IFERROR((E110+E112)/E36,"")</f>
-        <v/>
-      </c>
-      <c r="F132" s="23">
-        <f>IFERROR((F110+F112)/F36,"")</f>
-        <v/>
-      </c>
-      <c r="G132" s="23">
-        <f>IFERROR((G110+G112)/G36,"")</f>
+      <c r="B132" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Increase / (decrease) in due to director</t>
+        </is>
+      </c>
+      <c r="C132" s="13" t="n"/>
+      <c r="D132" s="13">
+        <f>D104-C104</f>
+        <v/>
+      </c>
+      <c r="E132" s="13">
+        <f>E104-D104</f>
+        <v/>
+      </c>
+      <c r="F132" s="13">
+        <f>F104-E104</f>
+        <v/>
+      </c>
+      <c r="G132" s="13">
+        <f>G104-F104</f>
         <v/>
       </c>
     </row>
     <row r="133">
-      <c r="B133" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Capex % of revenue</t>
-        </is>
-      </c>
-      <c r="C133" s="17" t="n"/>
-      <c r="D133" s="17">
-        <f>IFERROR(-D112/D9,"")</f>
-        <v/>
-      </c>
-      <c r="E133" s="17">
-        <f>IFERROR(-E112/E9,"")</f>
-        <v/>
-      </c>
-      <c r="F133" s="17">
-        <f>IFERROR(-F112/F9,"")</f>
-        <v/>
-      </c>
-      <c r="G133" s="17">
-        <f>IFERROR(-G112/G9,"")</f>
+      <c r="B133" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Increase / (decrease) in due to KEL Tooling</t>
+        </is>
+      </c>
+      <c r="C133" s="13" t="n"/>
+      <c r="D133" s="13">
+        <f>D103-C103</f>
+        <v/>
+      </c>
+      <c r="E133" s="13">
+        <f>E103-D103</f>
+        <v/>
+      </c>
+      <c r="F133" s="13">
+        <f>F103-E103</f>
+        <v/>
+      </c>
+      <c r="G133" s="13">
+        <f>G103-F103</f>
         <v/>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="18" t="n"/>
-      <c r="B134" s="18" t="inlineStr">
-        <is>
-          <t>Profitability &amp; returns (on ending balances)</t>
-        </is>
-      </c>
-      <c r="C134" s="18" t="n"/>
-      <c r="D134" s="18" t="n"/>
-      <c r="E134" s="18" t="n"/>
-      <c r="F134" s="18" t="n"/>
-      <c r="G134" s="18" t="n"/>
-      <c r="H134" s="18" t="n"/>
-      <c r="I134" s="18" t="n"/>
+      <c r="B134" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (Increase) / decrease in due from Related Group of Companies</t>
+        </is>
+      </c>
+      <c r="C134" s="13" t="n"/>
+      <c r="D134" s="13">
+        <f>-(D94-C94)</f>
+        <v/>
+      </c>
+      <c r="E134" s="13">
+        <f>-(E94-D94)</f>
+        <v/>
+      </c>
+      <c r="F134" s="13">
+        <f>-(F94-E94)</f>
+        <v/>
+      </c>
+      <c r="G134" s="13">
+        <f>-(G94-F94)</f>
+        <v/>
+      </c>
+      <c r="I134" s="12" t="inlineStr">
+        <is>
+          <t>Related-party advances — reclassified to financing.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
-      <c r="B135" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Gross margin %</t>
-        </is>
-      </c>
-      <c r="C135" s="17">
-        <f>IFERROR(C11/C9,0)</f>
-        <v/>
-      </c>
-      <c r="D135" s="17">
-        <f>IFERROR(D11/D9,0)</f>
-        <v/>
-      </c>
-      <c r="E135" s="17">
-        <f>IFERROR(E11/E9,0)</f>
-        <v/>
-      </c>
-      <c r="F135" s="17">
-        <f>IFERROR(F11/F9,0)</f>
-        <v/>
-      </c>
-      <c r="G135" s="17">
-        <f>IFERROR(G11/G9,0)</f>
+      <c r="B135" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (Increase) / decrease in due from director</t>
+        </is>
+      </c>
+      <c r="C135" s="13" t="n"/>
+      <c r="D135" s="13">
+        <f>-(D91-C91)</f>
+        <v/>
+      </c>
+      <c r="E135" s="13">
+        <f>-(E91-D91)</f>
+        <v/>
+      </c>
+      <c r="F135" s="13">
+        <f>-(F91-E91)</f>
+        <v/>
+      </c>
+      <c r="G135" s="13">
+        <f>-(G91-F91)</f>
         <v/>
       </c>
     </row>
     <row r="136">
       <c r="B136" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EBIT (NIBT + bank charges &amp; interest)</t>
-        </is>
-      </c>
-      <c r="C136" s="13">
-        <f>C31+C18</f>
-        <v/>
-      </c>
+          <t xml:space="preserve">  (Increase) / decrease in due from KEL Tooling</t>
+        </is>
+      </c>
+      <c r="C136" s="13" t="n"/>
       <c r="D136" s="13">
-        <f>D31+D18</f>
+        <f>-(D92-C92)</f>
         <v/>
       </c>
       <c r="E136" s="13">
-        <f>E31+E18</f>
+        <f>-(E92-D92)</f>
         <v/>
       </c>
       <c r="F136" s="13">
-        <f>F31+F18</f>
+        <f>-(F92-E92)</f>
         <v/>
       </c>
       <c r="G136" s="13">
-        <f>G31+G18</f>
-        <v/>
-      </c>
-      <c r="I136" s="12" t="inlineStr">
-        <is>
-          <t>Interest is bundled in bank charges &amp; interest.</t>
-        </is>
+        <f>-(G92-F92)</f>
+        <v/>
       </c>
     </row>
     <row r="137">
-      <c r="B137" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Operating margin (EBIT %)</t>
-        </is>
-      </c>
-      <c r="C137" s="17">
-        <f>IFERROR((C31+C18)/C9,0)</f>
-        <v/>
-      </c>
-      <c r="D137" s="17">
-        <f>IFERROR((D31+D18)/D9,0)</f>
-        <v/>
-      </c>
-      <c r="E137" s="17">
-        <f>IFERROR((E31+E18)/E9,0)</f>
-        <v/>
-      </c>
-      <c r="F137" s="17">
-        <f>IFERROR((F31+F18)/F9,0)</f>
-        <v/>
-      </c>
-      <c r="G137" s="17">
-        <f>IFERROR((G31+G18)/G9,0)</f>
+      <c r="B137" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Dividends paid</t>
+        </is>
+      </c>
+      <c r="C137" s="13" t="n"/>
+      <c r="D137" s="13">
+        <f>-D52</f>
+        <v/>
+      </c>
+      <c r="E137" s="13">
+        <f>-E52</f>
+        <v/>
+      </c>
+      <c r="F137" s="13">
+        <f>-F52</f>
+        <v/>
+      </c>
+      <c r="G137" s="13">
+        <f>-G52</f>
         <v/>
       </c>
     </row>
     <row r="138">
-      <c r="B138" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Return on assets (NI / total assets)</t>
-        </is>
-      </c>
-      <c r="C138" s="17">
-        <f>IFERROR(C36/C80,0)</f>
-        <v/>
-      </c>
-      <c r="D138" s="17">
-        <f>IFERROR(D36/D80,0)</f>
-        <v/>
-      </c>
-      <c r="E138" s="17">
-        <f>IFERROR(E36/E80,0)</f>
-        <v/>
-      </c>
-      <c r="F138" s="17">
-        <f>IFERROR(F36/F80,0)</f>
-        <v/>
-      </c>
-      <c r="G138" s="17">
-        <f>IFERROR(G36/G80,0)</f>
+      <c r="B138" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Issuance of share capital</t>
+        </is>
+      </c>
+      <c r="C138" s="13" t="n"/>
+      <c r="D138" s="13">
+        <f>D109-C109</f>
+        <v/>
+      </c>
+      <c r="E138" s="13">
+        <f>E109-D109</f>
+        <v/>
+      </c>
+      <c r="F138" s="13">
+        <f>F109-E109</f>
+        <v/>
+      </c>
+      <c r="G138" s="13">
+        <f>G109-F109</f>
         <v/>
       </c>
     </row>
     <row r="139">
-      <c r="B139" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Return on equity (NI / total equity)</t>
-        </is>
-      </c>
-      <c r="C139" s="17">
-        <f>IFERROR(C36/C95,0)</f>
-        <v/>
-      </c>
-      <c r="D139" s="17">
-        <f>IFERROR(D36/D95,0)</f>
-        <v/>
-      </c>
-      <c r="E139" s="17">
-        <f>IFERROR(E36/E95,0)</f>
-        <v/>
-      </c>
-      <c r="F139" s="17">
-        <f>IFERROR(F36/F95,0)</f>
-        <v/>
-      </c>
-      <c r="G139" s="17">
-        <f>IFERROR(G36/G95,0)</f>
+      <c r="B139" s="14" t="inlineStr">
+        <is>
+          <t>Net cash from financing activities</t>
+        </is>
+      </c>
+      <c r="C139" s="15" t="n"/>
+      <c r="D139" s="15">
+        <f>SUM(D131:D138)</f>
+        <v/>
+      </c>
+      <c r="E139" s="15">
+        <f>SUM(E131:E138)</f>
+        <v/>
+      </c>
+      <c r="F139" s="15">
+        <f>SUM(F131:F138)</f>
+        <v/>
+      </c>
+      <c r="G139" s="15">
+        <f>SUM(G131:G138)</f>
         <v/>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="18" t="n"/>
-      <c r="B140" s="18" t="inlineStr">
-        <is>
-          <t>Liquidity &amp; leverage</t>
-        </is>
-      </c>
-      <c r="C140" s="18" t="n"/>
-      <c r="D140" s="18" t="n"/>
-      <c r="E140" s="18" t="n"/>
-      <c r="F140" s="18" t="n"/>
-      <c r="G140" s="18" t="n"/>
-      <c r="H140" s="18" t="n"/>
-      <c r="I140" s="18" t="n"/>
+      <c r="B140" s="19" t="inlineStr">
+        <is>
+          <t>Net change in cash</t>
+        </is>
+      </c>
+      <c r="C140" s="20">
+        <f>C126+C129+C139</f>
+        <v/>
+      </c>
+      <c r="D140" s="20">
+        <f>D126+D129+D139</f>
+        <v/>
+      </c>
+      <c r="E140" s="20">
+        <f>E126+E129+E139</f>
+        <v/>
+      </c>
+      <c r="F140" s="20">
+        <f>F126+F129+F139</f>
+        <v/>
+      </c>
+      <c r="G140" s="20">
+        <f>G126+G129+G139</f>
+        <v/>
+      </c>
     </row>
     <row r="141">
-      <c r="B141" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Current ratio (CA / CL)</t>
-        </is>
-      </c>
-      <c r="C141" s="23">
-        <f>IFERROR(C77/C89,"")</f>
-        <v/>
-      </c>
-      <c r="D141" s="23">
-        <f>IFERROR(D77/D89,"")</f>
-        <v/>
-      </c>
-      <c r="E141" s="23">
-        <f>IFERROR(E77/E89,"")</f>
-        <v/>
-      </c>
-      <c r="F141" s="23">
-        <f>IFERROR(F77/F89,"")</f>
-        <v/>
-      </c>
-      <c r="G141" s="23">
-        <f>IFERROR(G77/G89,"")</f>
+      <c r="B141" s="9" t="inlineStr">
+        <is>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="C141" s="13" t="n"/>
+      <c r="D141" s="13">
+        <f>C88</f>
+        <v/>
+      </c>
+      <c r="E141" s="13">
+        <f>D88</f>
+        <v/>
+      </c>
+      <c r="F141" s="13">
+        <f>E88</f>
+        <v/>
+      </c>
+      <c r="G141" s="13">
+        <f>F88</f>
         <v/>
       </c>
     </row>
     <row r="142">
-      <c r="B142" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Quick ratio ((cash + A/R) / CL)</t>
-        </is>
-      </c>
-      <c r="C142" s="23">
-        <f>IFERROR((C72+C73)/C89,"")</f>
-        <v/>
-      </c>
-      <c r="D142" s="23">
-        <f>IFERROR((D72+D73)/D89,"")</f>
-        <v/>
-      </c>
-      <c r="E142" s="23">
-        <f>IFERROR((E72+E73)/E89,"")</f>
-        <v/>
-      </c>
-      <c r="F142" s="23">
-        <f>IFERROR((F72+F73)/F89,"")</f>
-        <v/>
-      </c>
-      <c r="G142" s="23">
-        <f>IFERROR((G72+G73)/G89,"")</f>
+      <c r="B142" s="14" t="inlineStr">
+        <is>
+          <t>Cash, end of year</t>
+        </is>
+      </c>
+      <c r="C142" s="15" t="n"/>
+      <c r="D142" s="15">
+        <f>D141+D140</f>
+        <v/>
+      </c>
+      <c r="E142" s="15">
+        <f>E141+E140</f>
+        <v/>
+      </c>
+      <c r="F142" s="15">
+        <f>F141+F140</f>
+        <v/>
+      </c>
+      <c r="G142" s="15">
+        <f>G141+G140</f>
         <v/>
       </c>
     </row>
     <row r="143">
       <c r="B143" s="9" t="inlineStr">
         <is>
+          <t>Tie-out check (implied ending cash − balance sheet cash)</t>
+        </is>
+      </c>
+      <c r="C143" s="13">
+        <f>C142-C88</f>
+        <v/>
+      </c>
+      <c r="D143" s="13">
+        <f>D142-D88</f>
+        <v/>
+      </c>
+      <c r="E143" s="13">
+        <f>E142-E88</f>
+        <v/>
+      </c>
+      <c r="F143" s="13">
+        <f>F142-F88</f>
+        <v/>
+      </c>
+      <c r="G143" s="13">
+        <f>G142-G88</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145" ht="18" customHeight="1">
+      <c r="A145" s="8" t="n"/>
+      <c r="B145" s="8" t="inlineStr">
+        <is>
+          <t>AMORTIZATION &amp; PP&amp;E SCHEDULE</t>
+        </is>
+      </c>
+      <c r="C145" s="8" t="n"/>
+      <c r="D145" s="8" t="n"/>
+      <c r="E145" s="8" t="n"/>
+      <c r="F145" s="8" t="n"/>
+      <c r="G145" s="8" t="n"/>
+      <c r="H145" s="8" t="n"/>
+      <c r="I145" s="8" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="18" t="n"/>
+      <c r="B146" s="18" t="inlineStr">
+        <is>
+          <t>Amortization (depreciation) by category</t>
+        </is>
+      </c>
+      <c r="C146" s="18" t="n"/>
+      <c r="D146" s="18" t="n"/>
+      <c r="E146" s="18" t="n"/>
+      <c r="F146" s="18" t="n"/>
+      <c r="G146" s="18" t="n"/>
+      <c r="H146" s="18" t="n"/>
+      <c r="I146" s="18" t="n"/>
+    </row>
+    <row r="147">
+      <c r="B147" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Amortization — office equipment (G&amp;A)</t>
+        </is>
+      </c>
+      <c r="C147" s="13">
+        <f>C19</f>
+        <v/>
+      </c>
+      <c r="D147" s="13">
+        <f>D19</f>
+        <v/>
+      </c>
+      <c r="E147" s="13">
+        <f>E19</f>
+        <v/>
+      </c>
+      <c r="F147" s="13">
+        <f>F19</f>
+        <v/>
+      </c>
+      <c r="G147" s="13">
+        <f>G19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Amortization — building and shop equipment (COGS)</t>
+        </is>
+      </c>
+      <c r="C148" s="13">
+        <f>C82</f>
+        <v/>
+      </c>
+      <c r="D148" s="13">
+        <f>D82</f>
+        <v/>
+      </c>
+      <c r="E148" s="13">
+        <f>E82</f>
+        <v/>
+      </c>
+      <c r="F148" s="13">
+        <f>F82</f>
+        <v/>
+      </c>
+      <c r="G148" s="13">
+        <f>G82</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" s="14" t="inlineStr">
+        <is>
+          <t>Total amortization (D&amp;A)</t>
+        </is>
+      </c>
+      <c r="C149" s="15">
+        <f>C19+C82</f>
+        <v/>
+      </c>
+      <c r="D149" s="15">
+        <f>D19+D82</f>
+        <v/>
+      </c>
+      <c r="E149" s="15">
+        <f>E19+E82</f>
+        <v/>
+      </c>
+      <c r="F149" s="15">
+        <f>F19+F82</f>
+        <v/>
+      </c>
+      <c r="G149" s="15">
+        <f>G19+G82</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="18" t="n"/>
+      <c r="B150" s="18" t="inlineStr">
+        <is>
+          <t>PP&amp;E rollforward (net book value)</t>
+        </is>
+      </c>
+      <c r="C150" s="18" t="n"/>
+      <c r="D150" s="18" t="n"/>
+      <c r="E150" s="18" t="n"/>
+      <c r="F150" s="18" t="n"/>
+      <c r="G150" s="18" t="n"/>
+      <c r="H150" s="18" t="n"/>
+      <c r="I150" s="18" t="n"/>
+    </row>
+    <row r="151">
+      <c r="B151" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PP&amp;E, beginning of year</t>
+        </is>
+      </c>
+      <c r="C151" s="13" t="n"/>
+      <c r="D151" s="13">
+        <f>C95</f>
+        <v/>
+      </c>
+      <c r="E151" s="13">
+        <f>D95</f>
+        <v/>
+      </c>
+      <c r="F151" s="13">
+        <f>E95</f>
+        <v/>
+      </c>
+      <c r="G151" s="13">
+        <f>F95</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Add: capital expenditures (implied)</t>
+        </is>
+      </c>
+      <c r="C152" s="13" t="n"/>
+      <c r="D152" s="13">
+        <f>-D128</f>
+        <v/>
+      </c>
+      <c r="E152" s="13">
+        <f>-E128</f>
+        <v/>
+      </c>
+      <c r="F152" s="13">
+        <f>-F128</f>
+        <v/>
+      </c>
+      <c r="G152" s="13">
+        <f>-G128</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Less: total amortization</t>
+        </is>
+      </c>
+      <c r="C153" s="13" t="n"/>
+      <c r="D153" s="13">
+        <f>-(D19+D82)</f>
+        <v/>
+      </c>
+      <c r="E153" s="13">
+        <f>-(E19+E82)</f>
+        <v/>
+      </c>
+      <c r="F153" s="13">
+        <f>-(F19+F82)</f>
+        <v/>
+      </c>
+      <c r="G153" s="13">
+        <f>-(G19+G82)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PP&amp;E, end of year</t>
+        </is>
+      </c>
+      <c r="C154" s="15" t="n"/>
+      <c r="D154" s="15">
+        <f>D151+D152+D153</f>
+        <v/>
+      </c>
+      <c r="E154" s="15">
+        <f>E151+E152+E153</f>
+        <v/>
+      </c>
+      <c r="F154" s="15">
+        <f>F151+F152+F153</f>
+        <v/>
+      </c>
+      <c r="G154" s="15">
+        <f>G151+G152+G153</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Check (rollforward − balance sheet PP&amp;E)</t>
+        </is>
+      </c>
+      <c r="C155" s="13" t="n"/>
+      <c r="D155" s="13">
+        <f>D154-D95</f>
+        <v/>
+      </c>
+      <c r="E155" s="13">
+        <f>E154-E95</f>
+        <v/>
+      </c>
+      <c r="F155" s="13">
+        <f>F154-F95</f>
+        <v/>
+      </c>
+      <c r="G155" s="13">
+        <f>G154-G95</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="18" t="n"/>
+      <c r="B156" s="18" t="inlineStr">
+        <is>
+          <t>Implied useful-life analysis</t>
+        </is>
+      </c>
+      <c r="C156" s="18" t="n"/>
+      <c r="D156" s="18" t="n"/>
+      <c r="E156" s="18" t="n"/>
+      <c r="F156" s="18" t="n"/>
+      <c r="G156" s="18" t="n"/>
+      <c r="H156" s="18" t="n"/>
+      <c r="I156" s="18" t="n"/>
+    </row>
+    <row r="157">
+      <c r="B157" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Net PP&amp;E, end of year</t>
+        </is>
+      </c>
+      <c r="C157" s="13">
+        <f>C95</f>
+        <v/>
+      </c>
+      <c r="D157" s="13">
+        <f>D95</f>
+        <v/>
+      </c>
+      <c r="E157" s="13">
+        <f>E95</f>
+        <v/>
+      </c>
+      <c r="F157" s="13">
+        <f>F95</f>
+        <v/>
+      </c>
+      <c r="G157" s="13">
+        <f>G95</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Total amortization (D&amp;A)</t>
+        </is>
+      </c>
+      <c r="C158" s="13">
+        <f>C149</f>
+        <v/>
+      </c>
+      <c r="D158" s="13">
+        <f>D149</f>
+        <v/>
+      </c>
+      <c r="E158" s="13">
+        <f>E149</f>
+        <v/>
+      </c>
+      <c r="F158" s="13">
+        <f>F149</f>
+        <v/>
+      </c>
+      <c r="G158" s="13">
+        <f>G149</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Implied depreciation rate (D&amp;A / beginning net PP&amp;E)</t>
+        </is>
+      </c>
+      <c r="C159" s="17" t="n"/>
+      <c r="D159" s="17">
+        <f>IFERROR(D149/C95,"")</f>
+        <v/>
+      </c>
+      <c r="E159" s="17">
+        <f>IFERROR(E149/D95,"")</f>
+        <v/>
+      </c>
+      <c r="F159" s="17">
+        <f>IFERROR(F149/E95,"")</f>
+        <v/>
+      </c>
+      <c r="G159" s="17">
+        <f>IFERROR(G149/F95,"")</f>
+        <v/>
+      </c>
+      <c r="I159" s="12" t="inlineStr">
+        <is>
+          <t>Annual amortization as a % of opening net book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Implied remaining useful life (net PP&amp;E / D&amp;A)</t>
+        </is>
+      </c>
+      <c r="C160" s="25">
+        <f>IFERROR(C95/C149,"")</f>
+        <v/>
+      </c>
+      <c r="D160" s="25">
+        <f>IFERROR(D95/D149,"")</f>
+        <v/>
+      </c>
+      <c r="E160" s="25">
+        <f>IFERROR(E95/E149,"")</f>
+        <v/>
+      </c>
+      <c r="F160" s="25">
+        <f>IFERROR(F95/F149,"")</f>
+        <v/>
+      </c>
+      <c r="G160" s="25">
+        <f>IFERROR(G95/G149,"")</f>
+        <v/>
+      </c>
+      <c r="I160" s="12" t="inlineStr">
+        <is>
+          <t>Years of amortization remaining at the current run-rate on the net book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Capex intensity (implied capex / D&amp;A)</t>
+        </is>
+      </c>
+      <c r="C161" s="26" t="n"/>
+      <c r="D161" s="26">
+        <f>IFERROR(-D128/D149,"")</f>
+        <v/>
+      </c>
+      <c r="E161" s="26">
+        <f>IFERROR(-E128/E149,"")</f>
+        <v/>
+      </c>
+      <c r="F161" s="26">
+        <f>IFERROR(-F128/F149,"")</f>
+        <v/>
+      </c>
+      <c r="G161" s="26">
+        <f>IFERROR(-G128/G149,"")</f>
+        <v/>
+      </c>
+      <c r="I161" s="12" t="inlineStr">
+        <is>
+          <t>Reinvestment ratio: &gt;1x grows the asset base, &lt;1x shrinks it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Capex % of revenue</t>
+        </is>
+      </c>
+      <c r="C162" s="17" t="n"/>
+      <c r="D162" s="17">
+        <f>IFERROR(-D128/D9,"")</f>
+        <v/>
+      </c>
+      <c r="E162" s="17">
+        <f>IFERROR(-E128/E9,"")</f>
+        <v/>
+      </c>
+      <c r="F162" s="17">
+        <f>IFERROR(-F128/F9,"")</f>
+        <v/>
+      </c>
+      <c r="G162" s="17">
+        <f>IFERROR(-G128/G9,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164" ht="18" customHeight="1">
+      <c r="A164" s="8" t="n"/>
+      <c r="B164" s="8" t="inlineStr">
+        <is>
+          <t>RATIO ANALYSIS &amp; FREE CASH FLOW</t>
+        </is>
+      </c>
+      <c r="C164" s="8" t="n"/>
+      <c r="D164" s="8" t="n"/>
+      <c r="E164" s="8" t="n"/>
+      <c r="F164" s="8" t="n"/>
+      <c r="G164" s="8" t="n"/>
+      <c r="H164" s="8" t="n"/>
+      <c r="I164" s="8" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="18" t="n"/>
+      <c r="B165" s="18" t="inlineStr">
+        <is>
+          <t>Cash generation</t>
+        </is>
+      </c>
+      <c r="C165" s="18" t="n"/>
+      <c r="D165" s="18" t="n"/>
+      <c r="E165" s="18" t="n"/>
+      <c r="F165" s="18" t="n"/>
+      <c r="G165" s="18" t="n"/>
+      <c r="H165" s="18" t="n"/>
+      <c r="I165" s="18" t="n"/>
+    </row>
+    <row r="166">
+      <c r="B166" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Free cash flow (CFO − capex)</t>
+        </is>
+      </c>
+      <c r="C166" s="13">
+        <f>C126+C128</f>
+        <v/>
+      </c>
+      <c r="D166" s="13">
+        <f>D126+D128</f>
+        <v/>
+      </c>
+      <c r="E166" s="13">
+        <f>E126+E128</f>
+        <v/>
+      </c>
+      <c r="F166" s="13">
+        <f>F126+F128</f>
+        <v/>
+      </c>
+      <c r="G166" s="13">
+        <f>G126+G128</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FCF conversion (FCF / net income)</t>
+        </is>
+      </c>
+      <c r="C167" s="26" t="n"/>
+      <c r="D167" s="26">
+        <f>IFERROR((D126+D128)/D36,"")</f>
+        <v/>
+      </c>
+      <c r="E167" s="26">
+        <f>IFERROR((E126+E128)/E36,"")</f>
+        <v/>
+      </c>
+      <c r="F167" s="26">
+        <f>IFERROR((F126+F128)/F36,"")</f>
+        <v/>
+      </c>
+      <c r="G167" s="26">
+        <f>IFERROR((G126+G128)/G36,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Capex % of revenue</t>
+        </is>
+      </c>
+      <c r="C168" s="17" t="n"/>
+      <c r="D168" s="17">
+        <f>IFERROR(-D128/D9,"")</f>
+        <v/>
+      </c>
+      <c r="E168" s="17">
+        <f>IFERROR(-E128/E9,"")</f>
+        <v/>
+      </c>
+      <c r="F168" s="17">
+        <f>IFERROR(-F128/F9,"")</f>
+        <v/>
+      </c>
+      <c r="G168" s="17">
+        <f>IFERROR(-G128/G9,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="18" t="n"/>
+      <c r="B169" s="18" t="inlineStr">
+        <is>
+          <t>Returns</t>
+        </is>
+      </c>
+      <c r="C169" s="18" t="n"/>
+      <c r="D169" s="18" t="n"/>
+      <c r="E169" s="18" t="n"/>
+      <c r="F169" s="18" t="n"/>
+      <c r="G169" s="18" t="n"/>
+      <c r="H169" s="18" t="n"/>
+      <c r="I169" s="18" t="n"/>
+    </row>
+    <row r="170">
+      <c r="B170" s="9" t="inlineStr">
+        <is>
+          <t>Operating earnings (EBIT)</t>
+        </is>
+      </c>
+      <c r="C170" s="13">
+        <f>C31+C18</f>
+        <v/>
+      </c>
+      <c r="D170" s="13">
+        <f>D31+D18</f>
+        <v/>
+      </c>
+      <c r="E170" s="13">
+        <f>E31+E18</f>
+        <v/>
+      </c>
+      <c r="F170" s="13">
+        <f>F31+F18</f>
+        <v/>
+      </c>
+      <c r="G170" s="13">
+        <f>G31+G18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" s="9" t="inlineStr">
+        <is>
+          <t>Normalised tax rate</t>
+        </is>
+      </c>
+      <c r="C171" s="17">
+        <f>C35</f>
+        <v/>
+      </c>
+      <c r="D171" s="17">
+        <f>D35</f>
+        <v/>
+      </c>
+      <c r="E171" s="17">
+        <f>E35</f>
+        <v/>
+      </c>
+      <c r="F171" s="17">
+        <f>F35</f>
+        <v/>
+      </c>
+      <c r="G171" s="17">
+        <f>G35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" s="9" t="inlineStr">
+        <is>
+          <t>NOPAT = EBIT × (1 − tax rate)</t>
+        </is>
+      </c>
+      <c r="C172" s="13">
+        <f>C170*(1-C171)</f>
+        <v/>
+      </c>
+      <c r="D172" s="13">
+        <f>D170*(1-D171)</f>
+        <v/>
+      </c>
+      <c r="E172" s="13">
+        <f>E170*(1-E171)</f>
+        <v/>
+      </c>
+      <c r="F172" s="13">
+        <f>F170*(1-F171)</f>
+        <v/>
+      </c>
+      <c r="G172" s="13">
+        <f>G170*(1-G171)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" s="9" t="inlineStr">
+        <is>
+          <t>Invested capital (Equity + Net debt)</t>
+        </is>
+      </c>
+      <c r="C173" s="13">
+        <f>C174+C175</f>
+        <v/>
+      </c>
+      <c r="D173" s="13">
+        <f>D174+D175</f>
+        <v/>
+      </c>
+      <c r="E173" s="13">
+        <f>E174+E175</f>
+        <v/>
+      </c>
+      <c r="F173" s="13">
+        <f>F174+F175</f>
+        <v/>
+      </c>
+      <c r="G173" s="13">
+        <f>G174+G175</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Total equity</t>
+        </is>
+      </c>
+      <c r="C174" s="13">
+        <f>C111</f>
+        <v/>
+      </c>
+      <c r="D174" s="13">
+        <f>D111</f>
+        <v/>
+      </c>
+      <c r="E174" s="13">
+        <f>E111</f>
+        <v/>
+      </c>
+      <c r="F174" s="13">
+        <f>F111</f>
+        <v/>
+      </c>
+      <c r="G174" s="13">
+        <f>G111</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Net debt (bank loan − cash)</t>
         </is>
       </c>
-      <c r="C143" s="13">
-        <f>C83-C72</f>
-        <v/>
-      </c>
-      <c r="D143" s="13">
-        <f>D83-D72</f>
-        <v/>
-      </c>
-      <c r="E143" s="13">
-        <f>E83-E72</f>
-        <v/>
-      </c>
-      <c r="F143" s="13">
-        <f>F83-F72</f>
-        <v/>
-      </c>
-      <c r="G143" s="13">
-        <f>G83-G72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="144">
-      <c r="B144" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Debt / equity (bank loan / equity)</t>
-        </is>
-      </c>
-      <c r="C144" s="23">
-        <f>IFERROR(C83/C95,0)</f>
-        <v/>
-      </c>
-      <c r="D144" s="23">
-        <f>IFERROR(D83/D95,0)</f>
-        <v/>
-      </c>
-      <c r="E144" s="23">
-        <f>IFERROR(E83/E95,0)</f>
-        <v/>
-      </c>
-      <c r="F144" s="23">
-        <f>IFERROR(F83/F95,0)</f>
-        <v/>
-      </c>
-      <c r="G144" s="23">
-        <f>IFERROR(G83/G95,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="145">
-      <c r="B145" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  DSO (A/R / revenue × 365)</t>
-        </is>
-      </c>
-      <c r="C145" s="24">
-        <f>IFERROR(C73/C9*365,"")</f>
-        <v/>
-      </c>
-      <c r="D145" s="24">
-        <f>IFERROR(D73/D9*365,"")</f>
-        <v/>
-      </c>
-      <c r="E145" s="24">
-        <f>IFERROR(E73/E9*365,"")</f>
-        <v/>
-      </c>
-      <c r="F145" s="24">
-        <f>IFERROR(F73/F9*365,"")</f>
-        <v/>
-      </c>
-      <c r="G145" s="24">
-        <f>IFERROR(G73/G9*365,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="146">
-      <c r="B146" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  DPO (A/P / cost of sales × 365)</t>
-        </is>
-      </c>
-      <c r="C146" s="24">
-        <f>IFERROR(C84/C10*365,"")</f>
-        <v/>
-      </c>
-      <c r="D146" s="24">
-        <f>IFERROR(D84/D10*365,"")</f>
-        <v/>
-      </c>
-      <c r="E146" s="24">
-        <f>IFERROR(E84/E10*365,"")</f>
-        <v/>
-      </c>
-      <c r="F146" s="24">
-        <f>IFERROR(F84/F10*365,"")</f>
-        <v/>
-      </c>
-      <c r="G146" s="24">
-        <f>IFERROR(G84/G10*365,"")</f>
+      <c r="C175" s="13">
+        <f>C99-C88</f>
+        <v/>
+      </c>
+      <c r="D175" s="13">
+        <f>D99-D88</f>
+        <v/>
+      </c>
+      <c r="E175" s="13">
+        <f>E99-E88</f>
+        <v/>
+      </c>
+      <c r="F175" s="13">
+        <f>F99-F88</f>
+        <v/>
+      </c>
+      <c r="G175" s="13">
+        <f>G99-G88</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" s="14" t="inlineStr">
+        <is>
+          <t>ROIC = NOPAT / Invested capital</t>
+        </is>
+      </c>
+      <c r="C176" s="27">
+        <f>IFERROR(C172/C173,0)</f>
+        <v/>
+      </c>
+      <c r="D176" s="27">
+        <f>IFERROR(D172/D173,0)</f>
+        <v/>
+      </c>
+      <c r="E176" s="27">
+        <f>IFERROR(E172/E173,0)</f>
+        <v/>
+      </c>
+      <c r="F176" s="27">
+        <f>IFERROR(F172/F173,0)</f>
+        <v/>
+      </c>
+      <c r="G176" s="27">
+        <f>IFERROR(G172/G173,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Operating margin</t>
+        </is>
+      </c>
+      <c r="C177" s="17">
+        <f>IFERROR(C170/C9,0)</f>
+        <v/>
+      </c>
+      <c r="D177" s="17">
+        <f>IFERROR(D170/D9,0)</f>
+        <v/>
+      </c>
+      <c r="E177" s="17">
+        <f>IFERROR(E170/E9,0)</f>
+        <v/>
+      </c>
+      <c r="F177" s="17">
+        <f>IFERROR(F170/F9,0)</f>
+        <v/>
+      </c>
+      <c r="G177" s="17">
+        <f>IFERROR(G170/G9,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Capital turnover (Sales / IC)</t>
+        </is>
+      </c>
+      <c r="C178" s="26">
+        <f>IFERROR(C9/C173,0)</f>
+        <v/>
+      </c>
+      <c r="D178" s="26">
+        <f>IFERROR(D9/D173,0)</f>
+        <v/>
+      </c>
+      <c r="E178" s="26">
+        <f>IFERROR(E9/E173,0)</f>
+        <v/>
+      </c>
+      <c r="F178" s="26">
+        <f>IFERROR(F9/F173,0)</f>
+        <v/>
+      </c>
+      <c r="G178" s="26">
+        <f>IFERROR(G9/G173,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Tax burden (1 − tax rate)</t>
+        </is>
+      </c>
+      <c r="C179" s="17">
+        <f>1-C171</f>
+        <v/>
+      </c>
+      <c r="D179" s="17">
+        <f>1-D171</f>
+        <v/>
+      </c>
+      <c r="E179" s="17">
+        <f>1-E171</f>
+        <v/>
+      </c>
+      <c r="F179" s="17">
+        <f>1-F171</f>
+        <v/>
+      </c>
+      <c r="G179" s="17">
+        <f>1-G171</f>
+        <v/>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Check: Margin × Turnover × Tax burden</t>
+        </is>
+      </c>
+      <c r="C180" s="17">
+        <f>C177*C178*C179</f>
+        <v/>
+      </c>
+      <c r="D180" s="17">
+        <f>D177*D178*D179</f>
+        <v/>
+      </c>
+      <c r="E180" s="17">
+        <f>E177*E178*E179</f>
+        <v/>
+      </c>
+      <c r="F180" s="17">
+        <f>F177*F178*F179</f>
+        <v/>
+      </c>
+      <c r="G180" s="17">
+        <f>G177*G178*G179</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="18" t="n"/>
+      <c r="B181" s="18" t="inlineStr">
+        <is>
+          <t>RONTA decomposition</t>
+        </is>
+      </c>
+      <c r="C181" s="18" t="n"/>
+      <c r="D181" s="18" t="n"/>
+      <c r="E181" s="18" t="n"/>
+      <c r="F181" s="18" t="n"/>
+      <c r="G181" s="18" t="n"/>
+      <c r="H181" s="18" t="n"/>
+      <c r="I181" s="18" t="n"/>
+    </row>
+    <row r="182">
+      <c r="B182" s="9" t="inlineStr">
+        <is>
+          <t>EBIT before special items</t>
+        </is>
+      </c>
+      <c r="C182" s="13">
+        <f>C170</f>
+        <v/>
+      </c>
+      <c r="D182" s="13">
+        <f>D170</f>
+        <v/>
+      </c>
+      <c r="E182" s="13">
+        <f>E170</f>
+        <v/>
+      </c>
+      <c r="F182" s="13">
+        <f>F170</f>
+        <v/>
+      </c>
+      <c r="G182" s="13">
+        <f>G170</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" s="9" t="inlineStr">
+        <is>
+          <t>NOPAT = EBIT × (1 − tax rate)</t>
+        </is>
+      </c>
+      <c r="C183" s="13">
+        <f>C182*(1-C171)</f>
+        <v/>
+      </c>
+      <c r="D183" s="13">
+        <f>D182*(1-D171)</f>
+        <v/>
+      </c>
+      <c r="E183" s="13">
+        <f>E182*(1-E171)</f>
+        <v/>
+      </c>
+      <c r="F183" s="13">
+        <f>F182*(1-F171)</f>
+        <v/>
+      </c>
+      <c r="G183" s="13">
+        <f>G182*(1-G171)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" s="28" t="inlineStr">
+        <is>
+          <t>Net tangible assets (NTA):</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Total assets</t>
+        </is>
+      </c>
+      <c r="C185" s="13">
+        <f>C96</f>
+        <v/>
+      </c>
+      <c r="D185" s="13">
+        <f>D96</f>
+        <v/>
+      </c>
+      <c r="E185" s="13">
+        <f>E96</f>
+        <v/>
+      </c>
+      <c r="F185" s="13">
+        <f>F96</f>
+        <v/>
+      </c>
+      <c r="G185" s="13">
+        <f>G96</f>
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  − Intangible assets (none)</t>
+        </is>
+      </c>
+      <c r="C186" s="13">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D186" s="13">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E186" s="13">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F186" s="13">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G186" s="13">
+        <f>0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  − Non-interest-bearing current liabilities</t>
+        </is>
+      </c>
+      <c r="C187" s="13">
+        <f>-(C105-C99)</f>
+        <v/>
+      </c>
+      <c r="D187" s="13">
+        <f>-(D105-D99)</f>
+        <v/>
+      </c>
+      <c r="E187" s="13">
+        <f>-(E105-E99)</f>
+        <v/>
+      </c>
+      <c r="F187" s="13">
+        <f>-(F105-F99)</f>
+        <v/>
+      </c>
+      <c r="G187" s="13">
+        <f>-(G105-G99)</f>
+        <v/>
+      </c>
+      <c r="I187" s="12" t="inlineStr">
+        <is>
+          <t>Current liabilities excluding the interest-bearing bank loan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  − Cash</t>
+        </is>
+      </c>
+      <c r="C188" s="13">
+        <f>-C88</f>
+        <v/>
+      </c>
+      <c r="D188" s="13">
+        <f>-D88</f>
+        <v/>
+      </c>
+      <c r="E188" s="13">
+        <f>-E88</f>
+        <v/>
+      </c>
+      <c r="F188" s="13">
+        <f>-F88</f>
+        <v/>
+      </c>
+      <c r="G188" s="13">
+        <f>-G88</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = Net tangible assets</t>
+        </is>
+      </c>
+      <c r="C189" s="15">
+        <f>C185+C186+C187+C188</f>
+        <v/>
+      </c>
+      <c r="D189" s="15">
+        <f>D185+D186+D187+D188</f>
+        <v/>
+      </c>
+      <c r="E189" s="15">
+        <f>E185+E186+E187+E188</f>
+        <v/>
+      </c>
+      <c r="F189" s="15">
+        <f>F185+F186+F187+F188</f>
+        <v/>
+      </c>
+      <c r="G189" s="15">
+        <f>G185+G186+G187+G188</f>
+        <v/>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" s="28" t="inlineStr">
+        <is>
+          <t>RONTA = NOPAT / NTA</t>
+        </is>
+      </c>
+      <c r="C190" s="22">
+        <f>IFERROR(C183/C189,0)</f>
+        <v/>
+      </c>
+      <c r="D190" s="22">
+        <f>IFERROR(D183/D189,0)</f>
+        <v/>
+      </c>
+      <c r="E190" s="22">
+        <f>IFERROR(E183/E189,0)</f>
+        <v/>
+      </c>
+      <c r="F190" s="22">
+        <f>IFERROR(F183/F189,0)</f>
+        <v/>
+      </c>
+      <c r="G190" s="22">
+        <f>IFERROR(G183/G189,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="18" t="n"/>
+      <c r="B191" s="18" t="inlineStr">
+        <is>
+          <t>Return on Equity (ROE)</t>
+        </is>
+      </c>
+      <c r="C191" s="18" t="n"/>
+      <c r="D191" s="18" t="n"/>
+      <c r="E191" s="18" t="n"/>
+      <c r="F191" s="18" t="n"/>
+      <c r="G191" s="18" t="n"/>
+      <c r="H191" s="18" t="n"/>
+      <c r="I191" s="18" t="n"/>
+    </row>
+    <row r="192">
+      <c r="B192" s="9" t="inlineStr">
+        <is>
+          <t>Net income (profit for the year)</t>
+        </is>
+      </c>
+      <c r="C192" s="13">
+        <f>C36</f>
+        <v/>
+      </c>
+      <c r="D192" s="13">
+        <f>D36</f>
+        <v/>
+      </c>
+      <c r="E192" s="13">
+        <f>E36</f>
+        <v/>
+      </c>
+      <c r="F192" s="13">
+        <f>F36</f>
+        <v/>
+      </c>
+      <c r="G192" s="13">
+        <f>G36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" s="9" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+      <c r="C193" s="13">
+        <f>C111</f>
+        <v/>
+      </c>
+      <c r="D193" s="13">
+        <f>D111</f>
+        <v/>
+      </c>
+      <c r="E193" s="13">
+        <f>E111</f>
+        <v/>
+      </c>
+      <c r="F193" s="13">
+        <f>F111</f>
+        <v/>
+      </c>
+      <c r="G193" s="13">
+        <f>G111</f>
+        <v/>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" s="28" t="inlineStr">
+        <is>
+          <t>ROE = Net income / Equity</t>
+        </is>
+      </c>
+      <c r="C194" s="22">
+        <f>IFERROR(C192/C193,0)</f>
+        <v/>
+      </c>
+      <c r="D194" s="22">
+        <f>IFERROR(D192/D193,0)</f>
+        <v/>
+      </c>
+      <c r="E194" s="22">
+        <f>IFERROR(E192/E193,0)</f>
+        <v/>
+      </c>
+      <c r="F194" s="22">
+        <f>IFERROR(F192/F193,0)</f>
+        <v/>
+      </c>
+      <c r="G194" s="22">
+        <f>IFERROR(G192/G193,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" s="9" t="inlineStr">
+        <is>
+          <t>Return on assets (NI / total assets)</t>
+        </is>
+      </c>
+      <c r="C195" s="17">
+        <f>IFERROR(C36/C96,0)</f>
+        <v/>
+      </c>
+      <c r="D195" s="17">
+        <f>IFERROR(D36/D96,0)</f>
+        <v/>
+      </c>
+      <c r="E195" s="17">
+        <f>IFERROR(E36/E96,0)</f>
+        <v/>
+      </c>
+      <c r="F195" s="17">
+        <f>IFERROR(F36/F96,0)</f>
+        <v/>
+      </c>
+      <c r="G195" s="17">
+        <f>IFERROR(G36/G96,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="18" t="n"/>
+      <c r="B196" s="18" t="inlineStr">
+        <is>
+          <t>Leverage</t>
+        </is>
+      </c>
+      <c r="C196" s="18" t="n"/>
+      <c r="D196" s="18" t="n"/>
+      <c r="E196" s="18" t="n"/>
+      <c r="F196" s="18" t="n"/>
+      <c r="G196" s="18" t="n"/>
+      <c r="H196" s="18" t="n"/>
+      <c r="I196" s="18" t="n"/>
+    </row>
+    <row r="197">
+      <c r="B197" s="9" t="inlineStr">
+        <is>
+          <t>Net debt (bank loan − cash)</t>
+        </is>
+      </c>
+      <c r="C197" s="13">
+        <f>C99-C88</f>
+        <v/>
+      </c>
+      <c r="D197" s="13">
+        <f>D99-D88</f>
+        <v/>
+      </c>
+      <c r="E197" s="13">
+        <f>E99-E88</f>
+        <v/>
+      </c>
+      <c r="F197" s="13">
+        <f>F99-F88</f>
+        <v/>
+      </c>
+      <c r="G197" s="13">
+        <f>G99-G88</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" s="9" t="inlineStr">
+        <is>
+          <t>EBITDA (Operating earnings + D&amp;A)</t>
+        </is>
+      </c>
+      <c r="C198" s="13">
+        <f>C170+C19+C82</f>
+        <v/>
+      </c>
+      <c r="D198" s="13">
+        <f>D170+D19+D82</f>
+        <v/>
+      </c>
+      <c r="E198" s="13">
+        <f>E170+E19+E82</f>
+        <v/>
+      </c>
+      <c r="F198" s="13">
+        <f>F170+F19+F82</f>
+        <v/>
+      </c>
+      <c r="G198" s="13">
+        <f>G170+G19+G82</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" s="9" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA  (x)</t>
+        </is>
+      </c>
+      <c r="C199" s="26">
+        <f>IFERROR(C197/C198,"")</f>
+        <v/>
+      </c>
+      <c r="D199" s="26">
+        <f>IFERROR(D197/D198,"")</f>
+        <v/>
+      </c>
+      <c r="E199" s="26">
+        <f>IFERROR(E197/E198,"")</f>
+        <v/>
+      </c>
+      <c r="F199" s="26">
+        <f>IFERROR(F197/F198,"")</f>
+        <v/>
+      </c>
+      <c r="G199" s="26">
+        <f>IFERROR(G197/G198,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" s="9" t="inlineStr">
+        <is>
+          <t>Interest coverage (EBIT / interest expense)</t>
+        </is>
+      </c>
+      <c r="C200" s="26">
+        <f>IFERROR(C170/C18,"")</f>
+        <v/>
+      </c>
+      <c r="D200" s="26">
+        <f>IFERROR(D170/D18,"")</f>
+        <v/>
+      </c>
+      <c r="E200" s="26">
+        <f>IFERROR(E170/E18,"")</f>
+        <v/>
+      </c>
+      <c r="F200" s="26">
+        <f>IFERROR(F170/F18,"")</f>
+        <v/>
+      </c>
+      <c r="G200" s="26">
+        <f>IFERROR(G170/G18,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" s="9" t="inlineStr">
+        <is>
+          <t>Debt / equity (bank loan / equity)</t>
+        </is>
+      </c>
+      <c r="C201" s="26">
+        <f>IFERROR(C99/C111,0)</f>
+        <v/>
+      </c>
+      <c r="D201" s="26">
+        <f>IFERROR(D99/D111,0)</f>
+        <v/>
+      </c>
+      <c r="E201" s="26">
+        <f>IFERROR(E99/E111,0)</f>
+        <v/>
+      </c>
+      <c r="F201" s="26">
+        <f>IFERROR(F99/F111,0)</f>
+        <v/>
+      </c>
+      <c r="G201" s="26">
+        <f>IFERROR(G99/G111,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="18" t="n"/>
+      <c r="B202" s="18" t="inlineStr">
+        <is>
+          <t>Liquidity &amp; working capital</t>
+        </is>
+      </c>
+      <c r="C202" s="18" t="n"/>
+      <c r="D202" s="18" t="n"/>
+      <c r="E202" s="18" t="n"/>
+      <c r="F202" s="18" t="n"/>
+      <c r="G202" s="18" t="n"/>
+      <c r="H202" s="18" t="n"/>
+      <c r="I202" s="18" t="n"/>
+    </row>
+    <row r="203">
+      <c r="B203" s="9" t="inlineStr">
+        <is>
+          <t>Current ratio (CA / CL)</t>
+        </is>
+      </c>
+      <c r="C203" s="26">
+        <f>IFERROR(C93/C105,"")</f>
+        <v/>
+      </c>
+      <c r="D203" s="26">
+        <f>IFERROR(D93/D105,"")</f>
+        <v/>
+      </c>
+      <c r="E203" s="26">
+        <f>IFERROR(E93/E105,"")</f>
+        <v/>
+      </c>
+      <c r="F203" s="26">
+        <f>IFERROR(F93/F105,"")</f>
+        <v/>
+      </c>
+      <c r="G203" s="26">
+        <f>IFERROR(G93/G105,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" s="9" t="inlineStr">
+        <is>
+          <t>Quick ratio ((cash + A/R) / CL)</t>
+        </is>
+      </c>
+      <c r="C204" s="26">
+        <f>IFERROR((C88+C89)/C105,"")</f>
+        <v/>
+      </c>
+      <c r="D204" s="26">
+        <f>IFERROR((D88+D89)/D105,"")</f>
+        <v/>
+      </c>
+      <c r="E204" s="26">
+        <f>IFERROR((E88+E89)/E105,"")</f>
+        <v/>
+      </c>
+      <c r="F204" s="26">
+        <f>IFERROR((F88+F89)/F105,"")</f>
+        <v/>
+      </c>
+      <c r="G204" s="26">
+        <f>IFERROR((G88+G89)/G105,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" s="9" t="inlineStr">
+        <is>
+          <t>DSO (A/R / revenue × 365)</t>
+        </is>
+      </c>
+      <c r="C205" s="29">
+        <f>IFERROR(C89/C9*365,"")</f>
+        <v/>
+      </c>
+      <c r="D205" s="29">
+        <f>IFERROR(D89/D9*365,"")</f>
+        <v/>
+      </c>
+      <c r="E205" s="29">
+        <f>IFERROR(E89/E9*365,"")</f>
+        <v/>
+      </c>
+      <c r="F205" s="29">
+        <f>IFERROR(F89/F9*365,"")</f>
+        <v/>
+      </c>
+      <c r="G205" s="29">
+        <f>IFERROR(G89/G9*365,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" s="9" t="inlineStr">
+        <is>
+          <t>DPO (A/P / cost of sales × 365)</t>
+        </is>
+      </c>
+      <c r="C206" s="29">
+        <f>IFERROR(C100/C10*365,"")</f>
+        <v/>
+      </c>
+      <c r="D206" s="29">
+        <f>IFERROR(D100/D10*365,"")</f>
+        <v/>
+      </c>
+      <c r="E206" s="29">
+        <f>IFERROR(E100/E10*365,"")</f>
+        <v/>
+      </c>
+      <c r="F206" s="29">
+        <f>IFERROR(F100/F10*365,"")</f>
+        <v/>
+      </c>
+      <c r="G206" s="29">
+        <f>IFERROR(G100/G10*365,"")</f>
         <v/>
       </c>
     </row>

--- a/models/RY_Tool_3_Statement_Model.xlsx
+++ b/models/RY_Tool_3_Statement_Model.xlsx
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:I206"/>
+  <dimension ref="A2:I208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.4" customWidth="1" min="1" max="1"/>
@@ -707,23 +707,23 @@
         </is>
       </c>
       <c r="C10" s="13">
-        <f>C84</f>
+        <f>C86</f>
         <v/>
       </c>
       <c r="D10" s="13">
-        <f>D84</f>
+        <f>D86</f>
         <v/>
       </c>
       <c r="E10" s="13">
-        <f>E84</f>
+        <f>E86</f>
         <v/>
       </c>
       <c r="F10" s="13">
-        <f>F84</f>
+        <f>F86</f>
         <v/>
       </c>
       <c r="G10" s="13">
-        <f>G84</f>
+        <f>G86</f>
         <v/>
       </c>
       <c r="I10" s="12" t="inlineStr">
@@ -1478,23 +1478,23 @@
         </is>
       </c>
       <c r="C44" s="13">
-        <f>C82</f>
+        <f>C84</f>
         <v/>
       </c>
       <c r="D44" s="13">
-        <f>D82</f>
+        <f>D84</f>
         <v/>
       </c>
       <c r="E44" s="13">
-        <f>E82</f>
+        <f>E84</f>
         <v/>
       </c>
       <c r="F44" s="13">
-        <f>F82</f>
+        <f>F84</f>
         <v/>
       </c>
       <c r="G44" s="13">
-        <f>G82</f>
+        <f>G84</f>
         <v/>
       </c>
     </row>
@@ -1505,542 +1505,544 @@
         </is>
       </c>
       <c r="C45" s="15">
-        <f>C42+C19+C82</f>
+        <f>C42+C19+C84</f>
         <v/>
       </c>
       <c r="D45" s="15">
-        <f>D42+D19+D82</f>
+        <f>D42+D19+D84</f>
         <v/>
       </c>
       <c r="E45" s="15">
-        <f>E42+E19+E82</f>
+        <f>E42+E19+E84</f>
         <v/>
       </c>
       <c r="F45" s="15">
-        <f>F42+F19+F82</f>
+        <f>F42+F19+F84</f>
         <v/>
       </c>
       <c r="G45" s="15">
-        <f>G42+G19+G82</f>
+        <f>G42+G19+G84</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="9" t="inlineStr">
+      <c r="B46" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EBITDA margin %</t>
+        </is>
+      </c>
+      <c r="C46" s="17">
+        <f>IFERROR(C45/C9,0)</f>
+        <v/>
+      </c>
+      <c r="D46" s="17">
+        <f>IFERROR(D45/D9,0)</f>
+        <v/>
+      </c>
+      <c r="E46" s="17">
+        <f>IFERROR(E45/E9,0)</f>
+        <v/>
+      </c>
+      <c r="F46" s="17">
+        <f>IFERROR(F45/F9,0)</f>
+        <v/>
+      </c>
+      <c r="G46" s="17">
+        <f>IFERROR(G45/G9,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Incremental EBITDA % (ΔEBITDA / ΔRevenue)</t>
+        </is>
+      </c>
+      <c r="C47" s="17" t="n"/>
+      <c r="D47" s="17">
+        <f>IFERROR((D45-C45)/(D9-C9),"")</f>
+        <v/>
+      </c>
+      <c r="E47" s="17">
+        <f>IFERROR((E45-D45)/(E9-D9),"")</f>
+        <v/>
+      </c>
+      <c r="F47" s="17">
+        <f>IFERROR((F45-E45)/(F9-E9),"")</f>
+        <v/>
+      </c>
+      <c r="G47" s="17">
+        <f>IFERROR((G45-F45)/(G9-F9),"")</f>
+        <v/>
+      </c>
+      <c r="I47" s="12" t="inlineStr">
+        <is>
+          <t>Drop-through of incremental revenue to EBITDA; needs a prior year, so FY2021 is n/a.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  Less: capital expenditures (implied)</t>
         </is>
       </c>
-      <c r="C46" s="13" t="n"/>
-      <c r="D46" s="13">
-        <f>D128</f>
-        <v/>
-      </c>
-      <c r="E46" s="13">
-        <f>E128</f>
-        <v/>
-      </c>
-      <c r="F46" s="13">
-        <f>F128</f>
-        <v/>
-      </c>
-      <c r="G46" s="13">
-        <f>G128</f>
-        <v/>
-      </c>
-      <c r="I46" s="12" t="inlineStr">
+      <c r="C48" s="13" t="n"/>
+      <c r="D48" s="13">
+        <f>D130</f>
+        <v/>
+      </c>
+      <c r="E48" s="13">
+        <f>E130</f>
+        <v/>
+      </c>
+      <c r="F48" s="13">
+        <f>F130</f>
+        <v/>
+      </c>
+      <c r="G48" s="13">
+        <f>G130</f>
+        <v/>
+      </c>
+      <c r="I48" s="12" t="inlineStr">
         <is>
           <t>From the implied cash flow; requires prior-year PP&amp;E, so FY2021 is n/a.</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="19" t="inlineStr">
+    <row r="49">
+      <c r="B49" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  = EBITDA − capex</t>
         </is>
       </c>
-      <c r="C47" s="20" t="n"/>
-      <c r="D47" s="20">
-        <f>D45+D128</f>
-        <v/>
-      </c>
-      <c r="E47" s="20">
-        <f>E45+E128</f>
-        <v/>
-      </c>
-      <c r="F47" s="20">
-        <f>F45+F128</f>
-        <v/>
-      </c>
-      <c r="G47" s="20">
-        <f>G45+G128</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="18" t="n"/>
-      <c r="B49" s="18" t="inlineStr">
+      <c r="C49" s="20" t="n"/>
+      <c r="D49" s="20">
+        <f>D45+D130</f>
+        <v/>
+      </c>
+      <c r="E49" s="20">
+        <f>E45+E130</f>
+        <v/>
+      </c>
+      <c r="F49" s="20">
+        <f>F45+F130</f>
+        <v/>
+      </c>
+      <c r="G49" s="20">
+        <f>G45+G130</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="18" t="n"/>
+      <c r="B51" s="18" t="inlineStr">
         <is>
           <t>Retained earnings reconciliation</t>
         </is>
       </c>
-      <c r="C49" s="18" t="n"/>
-      <c r="D49" s="18" t="n"/>
-      <c r="E49" s="18" t="n"/>
-      <c r="F49" s="18" t="n"/>
-      <c r="G49" s="18" t="n"/>
-      <c r="H49" s="18" t="n"/>
-      <c r="I49" s="18" t="n"/>
-    </row>
-    <row r="50">
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Retained earnings, beginning of year</t>
-        </is>
-      </c>
-      <c r="C50" s="10" t="n">
-        <v>670703</v>
-      </c>
-      <c r="D50" s="13">
-        <f>C53</f>
-        <v/>
-      </c>
-      <c r="E50" s="13">
-        <f>D53</f>
-        <v/>
-      </c>
-      <c r="F50" s="13">
-        <f>E53</f>
-        <v/>
-      </c>
-      <c r="G50" s="13">
-        <f>F53</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Net income for the year</t>
-        </is>
-      </c>
-      <c r="C51" s="13">
-        <f>C36</f>
-        <v/>
-      </c>
-      <c r="D51" s="13">
-        <f>D36</f>
-        <v/>
-      </c>
-      <c r="E51" s="13">
-        <f>E36</f>
-        <v/>
-      </c>
-      <c r="F51" s="13">
-        <f>F36</f>
-        <v/>
-      </c>
-      <c r="G51" s="13">
-        <f>G36</f>
-        <v/>
-      </c>
+      <c r="C51" s="18" t="n"/>
+      <c r="D51" s="18" t="n"/>
+      <c r="E51" s="18" t="n"/>
+      <c r="F51" s="18" t="n"/>
+      <c r="G51" s="18" t="n"/>
+      <c r="H51" s="18" t="n"/>
+      <c r="I51" s="18" t="n"/>
     </row>
     <row r="52">
       <c r="B52" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Retained earnings, beginning of year</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="n">
+        <v>670703</v>
+      </c>
+      <c r="D52" s="13">
+        <f>C55</f>
+        <v/>
+      </c>
+      <c r="E52" s="13">
+        <f>D55</f>
+        <v/>
+      </c>
+      <c r="F52" s="13">
+        <f>E55</f>
+        <v/>
+      </c>
+      <c r="G52" s="13">
+        <f>F55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Net income for the year</t>
+        </is>
+      </c>
+      <c r="C53" s="13">
+        <f>C36</f>
+        <v/>
+      </c>
+      <c r="D53" s="13">
+        <f>D36</f>
+        <v/>
+      </c>
+      <c r="E53" s="13">
+        <f>E36</f>
+        <v/>
+      </c>
+      <c r="F53" s="13">
+        <f>F36</f>
+        <v/>
+      </c>
+      <c r="G53" s="13">
+        <f>G36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Dividends</t>
         </is>
       </c>
-      <c r="C52" s="10" t="n">
+      <c r="C54" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D52" s="10" t="n">
+      <c r="D54" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="E52" s="10" t="n">
+      <c r="E54" s="10" t="n">
         <v>170000</v>
       </c>
-      <c r="F52" s="10" t="n">
+      <c r="F54" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="G52" s="10" t="n">
+      <c r="G54" s="10" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="53">
-      <c r="B53" s="14" t="inlineStr">
+    <row r="55">
+      <c r="B55" s="14" t="inlineStr">
         <is>
           <t>Retained earnings, end of year</t>
         </is>
       </c>
-      <c r="C53" s="15">
-        <f>C50+C51-C52</f>
-        <v/>
-      </c>
-      <c r="D53" s="15">
-        <f>D50+D51-D52</f>
-        <v/>
-      </c>
-      <c r="E53" s="15">
-        <f>E50+E51-E52</f>
-        <v/>
-      </c>
-      <c r="F53" s="15">
-        <f>F50+F51-F52</f>
-        <v/>
-      </c>
-      <c r="G53" s="15">
-        <f>G50+G51-G52</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="18" t="n"/>
-      <c r="B55" s="18" t="inlineStr">
+      <c r="C55" s="15">
+        <f>C52+C53-C54</f>
+        <v/>
+      </c>
+      <c r="D55" s="15">
+        <f>D52+D53-D54</f>
+        <v/>
+      </c>
+      <c r="E55" s="15">
+        <f>E52+E53-E54</f>
+        <v/>
+      </c>
+      <c r="F55" s="15">
+        <f>F52+F53-F54</f>
+        <v/>
+      </c>
+      <c r="G55" s="15">
+        <f>G52+G53-G54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="18" t="n"/>
+      <c r="B57" s="18" t="inlineStr">
         <is>
           <t>Growth &amp; margins</t>
         </is>
       </c>
-      <c r="C55" s="18" t="n"/>
-      <c r="D55" s="18" t="n"/>
-      <c r="E55" s="18" t="n"/>
-      <c r="F55" s="18" t="n"/>
-      <c r="G55" s="18" t="n"/>
-      <c r="H55" s="18" t="n"/>
-      <c r="I55" s="18" t="n"/>
-    </row>
-    <row r="56">
-      <c r="B56" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Revenue y/y %</t>
-        </is>
-      </c>
-      <c r="C56" s="17">
-        <f>IFERROR(C9/C9-1,"")</f>
-        <v/>
-      </c>
-      <c r="D56" s="17">
-        <f>IFERROR(D9/C9-1,"")</f>
-        <v/>
-      </c>
-      <c r="E56" s="17">
-        <f>IFERROR(E9/D9-1,"")</f>
-        <v/>
-      </c>
-      <c r="F56" s="17">
-        <f>IFERROR(F9/E9-1,"")</f>
-        <v/>
-      </c>
-      <c r="G56" s="17">
-        <f>IFERROR(G9/F9-1,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Gross margin y/y %</t>
-        </is>
-      </c>
-      <c r="C57" s="17">
-        <f>IFERROR(C11/C11-1,"")</f>
-        <v/>
-      </c>
-      <c r="D57" s="17">
-        <f>IFERROR(D11/C11-1,"")</f>
-        <v/>
-      </c>
-      <c r="E57" s="17">
-        <f>IFERROR(E11/D11-1,"")</f>
-        <v/>
-      </c>
-      <c r="F57" s="17">
-        <f>IFERROR(F11/E11-1,"")</f>
-        <v/>
-      </c>
-      <c r="G57" s="17">
-        <f>IFERROR(G11/F11-1,"")</f>
-        <v/>
-      </c>
+      <c r="C57" s="18" t="n"/>
+      <c r="D57" s="18" t="n"/>
+      <c r="E57" s="18" t="n"/>
+      <c r="F57" s="18" t="n"/>
+      <c r="G57" s="18" t="n"/>
+      <c r="H57" s="18" t="n"/>
+      <c r="I57" s="18" t="n"/>
     </row>
     <row r="58">
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Net income y/y %</t>
+          <t xml:space="preserve">  Revenue y/y %</t>
         </is>
       </c>
       <c r="C58" s="17">
-        <f>IFERROR(C36/C36-1,"")</f>
+        <f>IFERROR(C9/C9-1,"")</f>
         <v/>
       </c>
       <c r="D58" s="17">
-        <f>IFERROR(D36/C36-1,"")</f>
+        <f>IFERROR(D9/C9-1,"")</f>
         <v/>
       </c>
       <c r="E58" s="17">
-        <f>IFERROR(E36/D36-1,"")</f>
+        <f>IFERROR(E9/D9-1,"")</f>
         <v/>
       </c>
       <c r="F58" s="17">
-        <f>IFERROR(F36/E36-1,"")</f>
+        <f>IFERROR(F9/E9-1,"")</f>
         <v/>
       </c>
       <c r="G58" s="17">
-        <f>IFERROR(G36/F36-1,"")</f>
+        <f>IFERROR(G9/F9-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  G&amp;A % of revenue</t>
+          <t xml:space="preserve">  Gross margin y/y %</t>
         </is>
       </c>
       <c r="C59" s="17">
-        <f>IFERROR(C29/C9,0)</f>
+        <f>IFERROR(C11/C11-1,"")</f>
         <v/>
       </c>
       <c r="D59" s="17">
-        <f>IFERROR(D29/D9,0)</f>
+        <f>IFERROR(D11/C11-1,"")</f>
         <v/>
       </c>
       <c r="E59" s="17">
-        <f>IFERROR(E29/E9,0)</f>
+        <f>IFERROR(E11/D11-1,"")</f>
         <v/>
       </c>
       <c r="F59" s="17">
-        <f>IFERROR(F29/F9,0)</f>
+        <f>IFERROR(F11/E11-1,"")</f>
         <v/>
       </c>
       <c r="G59" s="17">
-        <f>IFERROR(G29/G9,0)</f>
+        <f>IFERROR(G11/F11-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="16" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Net income y/y %</t>
+        </is>
+      </c>
+      <c r="C60" s="17">
+        <f>IFERROR(C36/C36-1,"")</f>
+        <v/>
+      </c>
+      <c r="D60" s="17">
+        <f>IFERROR(D36/C36-1,"")</f>
+        <v/>
+      </c>
+      <c r="E60" s="17">
+        <f>IFERROR(E36/D36-1,"")</f>
+        <v/>
+      </c>
+      <c r="F60" s="17">
+        <f>IFERROR(F36/E36-1,"")</f>
+        <v/>
+      </c>
+      <c r="G60" s="17">
+        <f>IFERROR(G36/F36-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  G&amp;A % of revenue</t>
+        </is>
+      </c>
+      <c r="C61" s="17">
+        <f>IFERROR(C29/C9,0)</f>
+        <v/>
+      </c>
+      <c r="D61" s="17">
+        <f>IFERROR(D29/D9,0)</f>
+        <v/>
+      </c>
+      <c r="E61" s="17">
+        <f>IFERROR(E29/E9,0)</f>
+        <v/>
+      </c>
+      <c r="F61" s="17">
+        <f>IFERROR(F29/F9,0)</f>
+        <v/>
+      </c>
+      <c r="G61" s="17">
+        <f>IFERROR(G29/G9,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="16" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Net income margin %</t>
         </is>
       </c>
-      <c r="C60" s="17">
+      <c r="C62" s="17">
         <f>IFERROR(C36/C9,0)</f>
         <v/>
       </c>
-      <c r="D60" s="17">
+      <c r="D62" s="17">
         <f>IFERROR(D36/D9,0)</f>
         <v/>
       </c>
-      <c r="E60" s="17">
+      <c r="E62" s="17">
         <f>IFERROR(E36/E9,0)</f>
         <v/>
       </c>
-      <c r="F60" s="17">
+      <c r="F62" s="17">
         <f>IFERROR(F36/F9,0)</f>
         <v/>
       </c>
-      <c r="G60" s="17">
+      <c r="G62" s="17">
         <f>IFERROR(G36/G9,0)</f>
         <v/>
       </c>
     </row>
-    <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="8" t="n"/>
-      <c r="B62" s="8" t="inlineStr">
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="8" t="n"/>
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>COST OF SALES SCHEDULE</t>
         </is>
       </c>
-      <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="n"/>
-      <c r="E62" s="8" t="n"/>
-      <c r="F62" s="8" t="n"/>
-      <c r="G62" s="8" t="n"/>
-      <c r="H62" s="8" t="n"/>
-      <c r="I62" s="8" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="18" t="n"/>
-      <c r="B63" s="18" t="inlineStr">
+      <c r="C64" s="8" t="n"/>
+      <c r="D64" s="8" t="n"/>
+      <c r="E64" s="8" t="n"/>
+      <c r="F64" s="8" t="n"/>
+      <c r="G64" s="8" t="n"/>
+      <c r="H64" s="8" t="n"/>
+      <c r="I64" s="8" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="18" t="n"/>
+      <c r="B65" s="18" t="inlineStr">
         <is>
           <t>Direct costs</t>
         </is>
       </c>
-      <c r="C63" s="18" t="n"/>
-      <c r="D63" s="18" t="n"/>
-      <c r="E63" s="18" t="n"/>
-      <c r="F63" s="18" t="n"/>
-      <c r="G63" s="18" t="n"/>
-      <c r="H63" s="18" t="n"/>
-      <c r="I63" s="18" t="n"/>
-    </row>
-    <row r="64">
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Direct wages</t>
-        </is>
-      </c>
-      <c r="C64" s="10" t="n">
-        <v>155912</v>
-      </c>
-      <c r="D64" s="10" t="n">
-        <v>207400</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>124776</v>
-      </c>
-      <c r="F64" s="10" t="n">
-        <v>246407</v>
-      </c>
-      <c r="G64" s="10" t="n">
-        <v>331037</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Materials, supplies and miscellaneous</t>
-        </is>
-      </c>
-      <c r="C65" s="10" t="n">
-        <v>196164</v>
-      </c>
-      <c r="D65" s="10" t="n">
-        <v>234466</v>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>423028</v>
-      </c>
-      <c r="F65" s="10" t="n">
-        <v>320248</v>
-      </c>
-      <c r="G65" s="10" t="n">
-        <v>233181</v>
-      </c>
+      <c r="C65" s="18" t="n"/>
+      <c r="D65" s="18" t="n"/>
+      <c r="E65" s="18" t="n"/>
+      <c r="F65" s="18" t="n"/>
+      <c r="G65" s="18" t="n"/>
+      <c r="H65" s="18" t="n"/>
+      <c r="I65" s="18" t="n"/>
     </row>
     <row r="66">
       <c r="B66" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Direct wages</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="n">
+        <v>155912</v>
+      </c>
+      <c r="D66" s="10" t="n">
+        <v>207400</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>124776</v>
+      </c>
+      <c r="F66" s="10" t="n">
+        <v>246407</v>
+      </c>
+      <c r="G66" s="10" t="n">
+        <v>331037</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Materials, supplies and miscellaneous</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="n">
+        <v>196164</v>
+      </c>
+      <c r="D67" s="10" t="n">
+        <v>234466</v>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>423028</v>
+      </c>
+      <c r="F67" s="10" t="n">
+        <v>320248</v>
+      </c>
+      <c r="G67" s="10" t="n">
+        <v>233181</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Subcontracts</t>
         </is>
       </c>
-      <c r="C66" s="10" t="n">
+      <c r="C68" s="10" t="n">
         <v>123993</v>
       </c>
-      <c r="D66" s="10" t="n">
+      <c r="D68" s="10" t="n">
         <v>124289</v>
       </c>
-      <c r="E66" s="10" t="n">
+      <c r="E68" s="10" t="n">
         <v>156114</v>
       </c>
-      <c r="F66" s="10" t="n">
+      <c r="F68" s="10" t="n">
         <v>208375</v>
       </c>
-      <c r="G66" s="10" t="n">
+      <c r="G68" s="10" t="n">
         <v>242821</v>
       </c>
     </row>
-    <row r="67">
-      <c r="B67" s="14" t="inlineStr">
+    <row r="69">
+      <c r="B69" s="14" t="inlineStr">
         <is>
           <t>Total direct costs</t>
         </is>
       </c>
-      <c r="C67" s="15">
-        <f>SUM(C64:C66)</f>
-        <v/>
-      </c>
-      <c r="D67" s="15">
-        <f>SUM(D64:D66)</f>
-        <v/>
-      </c>
-      <c r="E67" s="15">
-        <f>SUM(E64:E66)</f>
-        <v/>
-      </c>
-      <c r="F67" s="15">
-        <f>SUM(F64:F66)</f>
-        <v/>
-      </c>
-      <c r="G67" s="15">
-        <f>SUM(G64:G66)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="18" t="n"/>
-      <c r="B68" s="18" t="inlineStr">
+      <c r="C69" s="15">
+        <f>SUM(C66:C68)</f>
+        <v/>
+      </c>
+      <c r="D69" s="15">
+        <f>SUM(D66:D68)</f>
+        <v/>
+      </c>
+      <c r="E69" s="15">
+        <f>SUM(E66:E68)</f>
+        <v/>
+      </c>
+      <c r="F69" s="15">
+        <f>SUM(F66:F68)</f>
+        <v/>
+      </c>
+      <c r="G69" s="15">
+        <f>SUM(G66:G68)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="18" t="n"/>
+      <c r="B70" s="18" t="inlineStr">
         <is>
           <t>Direct costs as % of revenue</t>
         </is>
       </c>
-      <c r="C68" s="18" t="n"/>
-      <c r="D68" s="18" t="n"/>
-      <c r="E68" s="18" t="n"/>
-      <c r="F68" s="18" t="n"/>
-      <c r="G68" s="18" t="n"/>
-      <c r="H68" s="18" t="n"/>
-      <c r="I68" s="18" t="n"/>
-    </row>
-    <row r="69">
-      <c r="B69" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Direct wages % of revenue</t>
-        </is>
-      </c>
-      <c r="C69" s="17">
-        <f>IFERROR(C64/C9,0)</f>
-        <v/>
-      </c>
-      <c r="D69" s="17">
-        <f>IFERROR(D64/D9,0)</f>
-        <v/>
-      </c>
-      <c r="E69" s="17">
-        <f>IFERROR(E64/E9,0)</f>
-        <v/>
-      </c>
-      <c r="F69" s="17">
-        <f>IFERROR(F64/F9,0)</f>
-        <v/>
-      </c>
-      <c r="G69" s="17">
-        <f>IFERROR(G64/G9,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Materials, supplies and miscellaneous % of revenue</t>
-        </is>
-      </c>
-      <c r="C70" s="17">
-        <f>IFERROR(C65/C9,0)</f>
-        <v/>
-      </c>
-      <c r="D70" s="17">
-        <f>IFERROR(D65/D9,0)</f>
-        <v/>
-      </c>
-      <c r="E70" s="17">
-        <f>IFERROR(E65/E9,0)</f>
-        <v/>
-      </c>
-      <c r="F70" s="17">
-        <f>IFERROR(F65/F9,0)</f>
-        <v/>
-      </c>
-      <c r="G70" s="17">
-        <f>IFERROR(G65/G9,0)</f>
-        <v/>
-      </c>
+      <c r="C70" s="18" t="n"/>
+      <c r="D70" s="18" t="n"/>
+      <c r="E70" s="18" t="n"/>
+      <c r="F70" s="18" t="n"/>
+      <c r="G70" s="18" t="n"/>
+      <c r="H70" s="18" t="n"/>
+      <c r="I70" s="18" t="n"/>
     </row>
     <row r="71">
       <c r="B71" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Subcontracts % of revenue</t>
+          <t xml:space="preserve">  Direct wages % of revenue</t>
         </is>
       </c>
       <c r="C71" s="17">
@@ -2065,738 +2067,743 @@
       </c>
     </row>
     <row r="72">
-      <c r="B72" s="21" t="inlineStr">
+      <c r="B72" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Materials, supplies and miscellaneous % of revenue</t>
+        </is>
+      </c>
+      <c r="C72" s="17">
+        <f>IFERROR(C67/C9,0)</f>
+        <v/>
+      </c>
+      <c r="D72" s="17">
+        <f>IFERROR(D67/D9,0)</f>
+        <v/>
+      </c>
+      <c r="E72" s="17">
+        <f>IFERROR(E67/E9,0)</f>
+        <v/>
+      </c>
+      <c r="F72" s="17">
+        <f>IFERROR(F67/F9,0)</f>
+        <v/>
+      </c>
+      <c r="G72" s="17">
+        <f>IFERROR(G67/G9,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Subcontracts % of revenue</t>
+        </is>
+      </c>
+      <c r="C73" s="17">
+        <f>IFERROR(C68/C9,0)</f>
+        <v/>
+      </c>
+      <c r="D73" s="17">
+        <f>IFERROR(D68/D9,0)</f>
+        <v/>
+      </c>
+      <c r="E73" s="17">
+        <f>IFERROR(E68/E9,0)</f>
+        <v/>
+      </c>
+      <c r="F73" s="17">
+        <f>IFERROR(F68/F9,0)</f>
+        <v/>
+      </c>
+      <c r="G73" s="17">
+        <f>IFERROR(G68/G9,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  Total direct costs % of revenue</t>
         </is>
       </c>
-      <c r="C72" s="22">
-        <f>IFERROR(C67/C9,0)</f>
-        <v/>
-      </c>
-      <c r="D72" s="22">
-        <f>IFERROR(D67/D9,0)</f>
-        <v/>
-      </c>
-      <c r="E72" s="22">
-        <f>IFERROR(E67/E9,0)</f>
-        <v/>
-      </c>
-      <c r="F72" s="22">
-        <f>IFERROR(F67/F9,0)</f>
-        <v/>
-      </c>
-      <c r="G72" s="22">
-        <f>IFERROR(G67/G9,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="18" t="n"/>
-      <c r="B73" s="18" t="inlineStr">
+      <c r="C74" s="22">
+        <f>IFERROR(C69/C9,0)</f>
+        <v/>
+      </c>
+      <c r="D74" s="22">
+        <f>IFERROR(D69/D9,0)</f>
+        <v/>
+      </c>
+      <c r="E74" s="22">
+        <f>IFERROR(E69/E9,0)</f>
+        <v/>
+      </c>
+      <c r="F74" s="22">
+        <f>IFERROR(F69/F9,0)</f>
+        <v/>
+      </c>
+      <c r="G74" s="22">
+        <f>IFERROR(G69/G9,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="18" t="n"/>
+      <c r="B75" s="18" t="inlineStr">
         <is>
           <t>Indirect costs</t>
         </is>
       </c>
-      <c r="C73" s="18" t="n"/>
-      <c r="D73" s="18" t="n"/>
-      <c r="E73" s="18" t="n"/>
-      <c r="F73" s="18" t="n"/>
-      <c r="G73" s="18" t="n"/>
-      <c r="H73" s="18" t="n"/>
-      <c r="I73" s="18" t="n"/>
-    </row>
-    <row r="74">
-      <c r="B74" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Employee group benefits</t>
-        </is>
-      </c>
-      <c r="C74" s="10" t="n">
-        <v>6052</v>
-      </c>
-      <c r="D74" s="10" t="n">
-        <v>5039</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>9316</v>
-      </c>
-      <c r="F74" s="10" t="n">
-        <v>7971</v>
-      </c>
-      <c r="G74" s="10" t="n">
-        <v>18149</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  WSIB</t>
-        </is>
-      </c>
-      <c r="C75" s="10" t="n">
-        <v>1840</v>
-      </c>
-      <c r="D75" s="10" t="n">
-        <v>1078</v>
-      </c>
-      <c r="E75" s="10" t="n">
-        <v>3724</v>
-      </c>
-      <c r="F75" s="10" t="n">
-        <v>2996</v>
-      </c>
-      <c r="G75" s="10" t="n">
-        <v>-47</v>
-      </c>
+      <c r="C75" s="18" t="n"/>
+      <c r="D75" s="18" t="n"/>
+      <c r="E75" s="18" t="n"/>
+      <c r="F75" s="18" t="n"/>
+      <c r="G75" s="18" t="n"/>
+      <c r="H75" s="18" t="n"/>
+      <c r="I75" s="18" t="n"/>
     </row>
     <row r="76">
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Insurance and property tax</t>
+          <t xml:space="preserve">  Employee group benefits</t>
         </is>
       </c>
       <c r="C76" s="10" t="n">
-        <v>28591</v>
+        <v>6052</v>
       </c>
       <c r="D76" s="10" t="n">
-        <v>33771</v>
+        <v>5039</v>
       </c>
       <c r="E76" s="10" t="n">
-        <v>29558</v>
+        <v>9316</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>33572</v>
+        <v>7971</v>
       </c>
       <c r="G76" s="10" t="n">
-        <v>29258</v>
+        <v>18149</v>
       </c>
     </row>
     <row r="77">
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Utilities</t>
+          <t xml:space="preserve">  WSIB</t>
         </is>
       </c>
       <c r="C77" s="10" t="n">
-        <v>21844</v>
+        <v>1840</v>
       </c>
       <c r="D77" s="10" t="n">
-        <v>24879</v>
+        <v>1078</v>
       </c>
       <c r="E77" s="10" t="n">
-        <v>25382</v>
+        <v>3724</v>
       </c>
       <c r="F77" s="10" t="n">
-        <v>25785</v>
+        <v>2996</v>
       </c>
       <c r="G77" s="10" t="n">
-        <v>25115</v>
+        <v>-47</v>
       </c>
     </row>
     <row r="78">
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Repairs and maintenance — equipment</t>
+          <t xml:space="preserve">  Insurance and property tax</t>
         </is>
       </c>
       <c r="C78" s="10" t="n">
-        <v>29368</v>
+        <v>28591</v>
       </c>
       <c r="D78" s="10" t="n">
-        <v>47451</v>
+        <v>33771</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>39527</v>
+        <v>29558</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>13007</v>
+        <v>33572</v>
       </c>
       <c r="G78" s="10" t="n">
-        <v>21655</v>
+        <v>29258</v>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Repairs and maintenance — buildings</t>
+          <t xml:space="preserve">  Utilities</t>
         </is>
       </c>
       <c r="C79" s="10" t="n">
-        <v>35600</v>
+        <v>21844</v>
       </c>
       <c r="D79" s="10" t="n">
-        <v>22714</v>
+        <v>24879</v>
       </c>
       <c r="E79" s="10" t="n">
-        <v>34750</v>
+        <v>25382</v>
       </c>
       <c r="F79" s="10" t="n">
-        <v>50649</v>
+        <v>25785</v>
       </c>
       <c r="G79" s="10" t="n">
-        <v>141141</v>
+        <v>25115</v>
       </c>
     </row>
     <row r="80">
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Freight and duty</t>
+          <t xml:space="preserve">  Repairs and maintenance — equipment</t>
         </is>
       </c>
       <c r="C80" s="10" t="n">
-        <v>23583</v>
+        <v>29368</v>
       </c>
       <c r="D80" s="10" t="n">
-        <v>14673</v>
+        <v>47451</v>
       </c>
       <c r="E80" s="10" t="n">
-        <v>18134</v>
+        <v>39527</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>23910</v>
+        <v>13007</v>
       </c>
       <c r="G80" s="10" t="n">
-        <v>22757</v>
+        <v>21655</v>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Truck and travel</t>
+          <t xml:space="preserve">  Repairs and maintenance — buildings</t>
         </is>
       </c>
       <c r="C81" s="10" t="n">
-        <v>4307</v>
+        <v>35600</v>
       </c>
       <c r="D81" s="10" t="n">
-        <v>10175</v>
+        <v>22714</v>
       </c>
       <c r="E81" s="10" t="n">
-        <v>7805</v>
+        <v>34750</v>
       </c>
       <c r="F81" s="10" t="n">
-        <v>11969</v>
+        <v>50649</v>
       </c>
       <c r="G81" s="10" t="n">
-        <v>11486</v>
+        <v>141141</v>
       </c>
     </row>
     <row r="82">
       <c r="B82" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Freight and duty</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="n">
+        <v>23583</v>
+      </c>
+      <c r="D82" s="10" t="n">
+        <v>14673</v>
+      </c>
+      <c r="E82" s="10" t="n">
+        <v>18134</v>
+      </c>
+      <c r="F82" s="10" t="n">
+        <v>23910</v>
+      </c>
+      <c r="G82" s="10" t="n">
+        <v>22757</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Truck and travel</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="n">
+        <v>4307</v>
+      </c>
+      <c r="D83" s="10" t="n">
+        <v>10175</v>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>7805</v>
+      </c>
+      <c r="F83" s="10" t="n">
+        <v>11969</v>
+      </c>
+      <c r="G83" s="10" t="n">
+        <v>11486</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Amortization — building and shop equipment</t>
         </is>
       </c>
-      <c r="C82" s="10" t="n">
+      <c r="C84" s="10" t="n">
         <v>89055</v>
       </c>
-      <c r="D82" s="10" t="n">
+      <c r="D84" s="10" t="n">
         <v>74522</v>
       </c>
-      <c r="E82" s="10" t="n">
+      <c r="E84" s="10" t="n">
         <v>53208</v>
       </c>
-      <c r="F82" s="10" t="n">
+      <c r="F84" s="10" t="n">
         <v>45953</v>
       </c>
-      <c r="G82" s="10" t="n">
+      <c r="G84" s="10" t="n">
         <v>42284</v>
       </c>
-      <c r="I82" s="12" t="inlineStr">
+      <c r="I84" s="12" t="inlineStr">
         <is>
           <t>Non-cash; added back in cash flow.</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="B83" s="14" t="inlineStr">
+    <row r="85">
+      <c r="B85" s="14" t="inlineStr">
         <is>
           <t>Total indirect costs</t>
         </is>
       </c>
-      <c r="C83" s="15">
-        <f>SUM(C74:C82)</f>
-        <v/>
-      </c>
-      <c r="D83" s="15">
-        <f>SUM(D74:D82)</f>
-        <v/>
-      </c>
-      <c r="E83" s="15">
-        <f>SUM(E74:E82)</f>
-        <v/>
-      </c>
-      <c r="F83" s="15">
-        <f>SUM(F74:F82)</f>
-        <v/>
-      </c>
-      <c r="G83" s="15">
-        <f>SUM(G74:G82)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" s="19" t="inlineStr">
+      <c r="C85" s="15">
+        <f>SUM(C76:C84)</f>
+        <v/>
+      </c>
+      <c r="D85" s="15">
+        <f>SUM(D76:D84)</f>
+        <v/>
+      </c>
+      <c r="E85" s="15">
+        <f>SUM(E76:E84)</f>
+        <v/>
+      </c>
+      <c r="F85" s="15">
+        <f>SUM(F76:F84)</f>
+        <v/>
+      </c>
+      <c r="G85" s="15">
+        <f>SUM(G76:G84)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="19" t="inlineStr">
         <is>
           <t>Total cost of sales</t>
         </is>
       </c>
-      <c r="C84" s="20">
-        <f>C67+C83</f>
-        <v/>
-      </c>
-      <c r="D84" s="20">
-        <f>D67+D83</f>
-        <v/>
-      </c>
-      <c r="E84" s="20">
-        <f>E67+E83</f>
-        <v/>
-      </c>
-      <c r="F84" s="20">
-        <f>F67+F83</f>
-        <v/>
-      </c>
-      <c r="G84" s="20">
-        <f>G67+G83</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="8" t="n"/>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="C86" s="20">
+        <f>C69+C85</f>
+        <v/>
+      </c>
+      <c r="D86" s="20">
+        <f>D69+D85</f>
+        <v/>
+      </c>
+      <c r="E86" s="20">
+        <f>E69+E85</f>
+        <v/>
+      </c>
+      <c r="F86" s="20">
+        <f>F69+F85</f>
+        <v/>
+      </c>
+      <c r="G86" s="20">
+        <f>G69+G85</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="A88" s="8" t="n"/>
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>BALANCE SHEET</t>
         </is>
       </c>
-      <c r="C86" s="8" t="n"/>
-      <c r="D86" s="8" t="n"/>
-      <c r="E86" s="8" t="n"/>
-      <c r="F86" s="8" t="n"/>
-      <c r="G86" s="8" t="n"/>
-      <c r="H86" s="8" t="n"/>
-      <c r="I86" s="8" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="18" t="n"/>
-      <c r="B87" s="18" t="inlineStr">
+      <c r="C88" s="8" t="n"/>
+      <c r="D88" s="8" t="n"/>
+      <c r="E88" s="8" t="n"/>
+      <c r="F88" s="8" t="n"/>
+      <c r="G88" s="8" t="n"/>
+      <c r="H88" s="8" t="n"/>
+      <c r="I88" s="8" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="18" t="n"/>
+      <c r="B89" s="18" t="inlineStr">
         <is>
           <t>Assets — current</t>
         </is>
       </c>
-      <c r="C87" s="18" t="n"/>
-      <c r="D87" s="18" t="n"/>
-      <c r="E87" s="18" t="n"/>
-      <c r="F87" s="18" t="n"/>
-      <c r="G87" s="18" t="n"/>
-      <c r="H87" s="18" t="n"/>
-      <c r="I87" s="18" t="n"/>
-    </row>
-    <row r="88">
-      <c r="B88" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Cash in bank</t>
-        </is>
-      </c>
-      <c r="C88" s="10" t="n">
-        <v>301695</v>
-      </c>
-      <c r="D88" s="10" t="n">
-        <v>331894</v>
-      </c>
-      <c r="E88" s="10" t="n">
-        <v>323927</v>
-      </c>
-      <c r="F88" s="10" t="n">
-        <v>451664</v>
-      </c>
-      <c r="G88" s="10" t="n">
-        <v>700989</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="B89" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Accounts receivable</t>
-        </is>
-      </c>
-      <c r="C89" s="10" t="n">
-        <v>174456</v>
-      </c>
-      <c r="D89" s="10" t="n">
-        <v>102521</v>
-      </c>
-      <c r="E89" s="10" t="n">
-        <v>172686</v>
-      </c>
-      <c r="F89" s="10" t="n">
-        <v>283263</v>
-      </c>
-      <c r="G89" s="10" t="n">
-        <v>249660</v>
-      </c>
+      <c r="C89" s="18" t="n"/>
+      <c r="D89" s="18" t="n"/>
+      <c r="E89" s="18" t="n"/>
+      <c r="F89" s="18" t="n"/>
+      <c r="G89" s="18" t="n"/>
+      <c r="H89" s="18" t="n"/>
+      <c r="I89" s="18" t="n"/>
     </row>
     <row r="90">
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Government sales tax recoverable</t>
+          <t xml:space="preserve">  Cash in bank</t>
         </is>
       </c>
       <c r="C90" s="10" t="n">
-        <v>10746</v>
+        <v>301695</v>
       </c>
       <c r="D90" s="10" t="n">
-        <v>8957</v>
+        <v>331894</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>11269</v>
+        <v>323927</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>4041</v>
+        <v>451664</v>
       </c>
       <c r="G90" s="10" t="n">
-        <v>10200</v>
+        <v>700989</v>
       </c>
     </row>
     <row r="91">
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Due from director</t>
+          <t xml:space="preserve">  Accounts receivable</t>
         </is>
       </c>
       <c r="C91" s="10" t="n">
-        <v>121461</v>
+        <v>174456</v>
       </c>
       <c r="D91" s="10" t="n">
-        <v>243508</v>
+        <v>102521</v>
       </c>
       <c r="E91" s="10" t="n">
-        <v>0</v>
+        <v>172686</v>
       </c>
       <c r="F91" s="10" t="n">
-        <v>0</v>
+        <v>283263</v>
       </c>
       <c r="G91" s="10" t="n">
-        <v>6193</v>
+        <v>249660</v>
       </c>
     </row>
     <row r="92">
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Due from KEL Tooling, non-interest bearing</t>
+          <t xml:space="preserve">  Government sales tax recoverable</t>
         </is>
       </c>
       <c r="C92" s="10" t="n">
+        <v>10746</v>
+      </c>
+      <c r="D92" s="10" t="n">
+        <v>8957</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>11269</v>
+      </c>
+      <c r="F92" s="10" t="n">
+        <v>4041</v>
+      </c>
+      <c r="G92" s="10" t="n">
+        <v>10200</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Due from director</t>
+        </is>
+      </c>
+      <c r="C93" s="10" t="n">
+        <v>121461</v>
+      </c>
+      <c r="D93" s="10" t="n">
+        <v>243508</v>
+      </c>
+      <c r="E93" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D92" s="10" t="n">
+      <c r="F93" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="E92" s="10" t="n">
-        <v>23308</v>
-      </c>
-      <c r="F92" s="10" t="n">
-        <v>16108</v>
-      </c>
-      <c r="G92" s="10" t="n">
-        <v>8908</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="B93" s="14" t="inlineStr">
-        <is>
-          <t>Total current assets</t>
-        </is>
-      </c>
-      <c r="C93" s="15">
-        <f>SUM(C88:C92)</f>
-        <v/>
-      </c>
-      <c r="D93" s="15">
-        <f>SUM(D88:D92)</f>
-        <v/>
-      </c>
-      <c r="E93" s="15">
-        <f>SUM(E88:E92)</f>
-        <v/>
-      </c>
-      <c r="F93" s="15">
-        <f>SUM(F88:F92)</f>
-        <v/>
-      </c>
-      <c r="G93" s="15">
-        <f>SUM(G88:G92)</f>
-        <v/>
+      <c r="G93" s="10" t="n">
+        <v>6193</v>
       </c>
     </row>
     <row r="94">
       <c r="B94" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Due from KEL Tooling, non-interest bearing</t>
+        </is>
+      </c>
+      <c r="C94" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>23308</v>
+      </c>
+      <c r="F94" s="10" t="n">
+        <v>16108</v>
+      </c>
+      <c r="G94" s="10" t="n">
+        <v>8908</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="14" t="inlineStr">
+        <is>
+          <t>Total current assets</t>
+        </is>
+      </c>
+      <c r="C95" s="15">
+        <f>SUM(C90:C94)</f>
+        <v/>
+      </c>
+      <c r="D95" s="15">
+        <f>SUM(D90:D94)</f>
+        <v/>
+      </c>
+      <c r="E95" s="15">
+        <f>SUM(E90:E94)</f>
+        <v/>
+      </c>
+      <c r="F95" s="15">
+        <f>SUM(F90:F94)</f>
+        <v/>
+      </c>
+      <c r="G95" s="15">
+        <f>SUM(G90:G94)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="9" t="inlineStr">
+        <is>
           <t>Due from Related Group of Companies</t>
         </is>
       </c>
-      <c r="C94" s="10" t="n">
+      <c r="C96" s="10" t="n">
         <v>24277</v>
       </c>
-      <c r="D94" s="10" t="n">
+      <c r="D96" s="10" t="n">
         <v>24277</v>
       </c>
-      <c r="E94" s="10" t="n">
+      <c r="E96" s="10" t="n">
         <v>12780</v>
       </c>
-      <c r="F94" s="10" t="n">
+      <c r="F96" s="10" t="n">
         <v>16132</v>
       </c>
-      <c r="G94" s="10" t="n">
+      <c r="G96" s="10" t="n">
         <v>18139</v>
       </c>
     </row>
-    <row r="95">
-      <c r="B95" s="9" t="inlineStr">
+    <row r="97">
+      <c r="B97" s="9" t="inlineStr">
         <is>
           <t>Land, buildings and equipment, net</t>
         </is>
       </c>
-      <c r="C95" s="10" t="n">
+      <c r="C97" s="10" t="n">
         <v>570987</v>
       </c>
-      <c r="D95" s="10" t="n">
+      <c r="D97" s="10" t="n">
         <v>513774</v>
       </c>
-      <c r="E95" s="10" t="n">
+      <c r="E97" s="10" t="n">
         <v>441755</v>
       </c>
-      <c r="F95" s="10" t="n">
+      <c r="F97" s="10" t="n">
         <v>403824</v>
       </c>
-      <c r="G95" s="10" t="n">
+      <c r="G97" s="10" t="n">
         <v>502314</v>
       </c>
-      <c r="I95" s="12" t="inlineStr">
+      <c r="I97" s="12" t="inlineStr">
         <is>
           <t>Net of accumulated amortization.</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="B96" s="23" t="inlineStr">
+    <row r="98">
+      <c r="B98" s="23" t="inlineStr">
         <is>
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="C96" s="24">
-        <f>C93+C94+C95</f>
-        <v/>
-      </c>
-      <c r="D96" s="24">
-        <f>D93+D94+D95</f>
-        <v/>
-      </c>
-      <c r="E96" s="24">
-        <f>E93+E94+E95</f>
-        <v/>
-      </c>
-      <c r="F96" s="24">
-        <f>F93+F94+F95</f>
-        <v/>
-      </c>
-      <c r="G96" s="24">
-        <f>G93+G94+G95</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="18" t="n"/>
-      <c r="B98" s="18" t="inlineStr">
+      <c r="C98" s="24">
+        <f>C95+C96+C97</f>
+        <v/>
+      </c>
+      <c r="D98" s="24">
+        <f>D95+D96+D97</f>
+        <v/>
+      </c>
+      <c r="E98" s="24">
+        <f>E95+E96+E97</f>
+        <v/>
+      </c>
+      <c r="F98" s="24">
+        <f>F95+F96+F97</f>
+        <v/>
+      </c>
+      <c r="G98" s="24">
+        <f>G95+G96+G97</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="18" t="n"/>
+      <c r="B100" s="18" t="inlineStr">
         <is>
           <t>Liabilities — current</t>
         </is>
       </c>
-      <c r="C98" s="18" t="n"/>
-      <c r="D98" s="18" t="n"/>
-      <c r="E98" s="18" t="n"/>
-      <c r="F98" s="18" t="n"/>
-      <c r="G98" s="18" t="n"/>
-      <c r="H98" s="18" t="n"/>
-      <c r="I98" s="18" t="n"/>
-    </row>
-    <row r="99">
-      <c r="B99" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Bank loan</t>
-        </is>
-      </c>
-      <c r="C99" s="10" t="n">
-        <v>25000</v>
-      </c>
-      <c r="D99" s="10" t="n">
-        <v>11500</v>
-      </c>
-      <c r="E99" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" s="10" t="n">
-        <v>155242</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="B100" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="C100" s="10" t="n">
-        <v>246579</v>
-      </c>
-      <c r="D100" s="10" t="n">
-        <v>269806</v>
-      </c>
-      <c r="E100" s="10" t="n">
-        <v>157001</v>
-      </c>
-      <c r="F100" s="10" t="n">
-        <v>148733</v>
-      </c>
-      <c r="G100" s="10" t="n">
-        <v>152022</v>
-      </c>
+      <c r="C100" s="18" t="n"/>
+      <c r="D100" s="18" t="n"/>
+      <c r="E100" s="18" t="n"/>
+      <c r="F100" s="18" t="n"/>
+      <c r="G100" s="18" t="n"/>
+      <c r="H100" s="18" t="n"/>
+      <c r="I100" s="18" t="n"/>
     </row>
     <row r="101">
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Payroll deductions payable</t>
+          <t xml:space="preserve">  Bank loan</t>
         </is>
       </c>
       <c r="C101" s="10" t="n">
-        <v>2687</v>
+        <v>25000</v>
       </c>
       <c r="D101" s="10" t="n">
-        <v>26638</v>
+        <v>11500</v>
       </c>
       <c r="E101" s="10" t="n">
-        <v>6158</v>
+        <v>0</v>
       </c>
       <c r="F101" s="10" t="n">
-        <v>6157</v>
+        <v>0</v>
       </c>
       <c r="G101" s="10" t="n">
-        <v>10936</v>
+        <v>155242</v>
       </c>
     </row>
     <row r="102">
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Income tax payable</t>
+          <t xml:space="preserve">  Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="C102" s="10" t="n">
-        <v>37030</v>
+        <v>246579</v>
       </c>
       <c r="D102" s="10" t="n">
-        <v>10179</v>
+        <v>269806</v>
       </c>
       <c r="E102" s="10" t="n">
-        <v>16792</v>
+        <v>157001</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>30644</v>
+        <v>148733</v>
       </c>
       <c r="G102" s="10" t="n">
-        <v>629</v>
+        <v>152022</v>
       </c>
     </row>
     <row r="103">
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Due to KEL Tooling, non-interest bearing</t>
+          <t xml:space="preserve">  Payroll deductions payable</t>
         </is>
       </c>
       <c r="C103" s="10" t="n">
-        <v>2239</v>
+        <v>2687</v>
       </c>
       <c r="D103" s="10" t="n">
-        <v>0</v>
+        <v>26638</v>
       </c>
       <c r="E103" s="10" t="n">
-        <v>0</v>
+        <v>6158</v>
       </c>
       <c r="F103" s="10" t="n">
-        <v>0</v>
+        <v>6157</v>
       </c>
       <c r="G103" s="10" t="n">
-        <v>0</v>
+        <v>10936</v>
       </c>
     </row>
     <row r="104">
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Due to director</t>
+          <t xml:space="preserve">  Income tax payable</t>
         </is>
       </c>
       <c r="C104" s="10" t="n">
+        <v>37030</v>
+      </c>
+      <c r="D104" s="10" t="n">
+        <v>10179</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>16792</v>
+      </c>
+      <c r="F104" s="10" t="n">
+        <v>30644</v>
+      </c>
+      <c r="G104" s="10" t="n">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Due to KEL Tooling, non-interest bearing</t>
+        </is>
+      </c>
+      <c r="C105" s="10" t="n">
+        <v>2239</v>
+      </c>
+      <c r="D105" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D104" s="10" t="n">
+      <c r="E105" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="E104" s="10" t="n">
-        <v>6616</v>
-      </c>
-      <c r="F104" s="10" t="n">
-        <v>6616</v>
-      </c>
-      <c r="G104" s="10" t="n">
+      <c r="F105" s="10" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="105">
-      <c r="B105" s="14" t="inlineStr">
-        <is>
-          <t>Total current liabilities</t>
-        </is>
-      </c>
-      <c r="C105" s="15">
-        <f>SUM(C99:C104)</f>
-        <v/>
-      </c>
-      <c r="D105" s="15">
-        <f>SUM(D99:D104)</f>
-        <v/>
-      </c>
-      <c r="E105" s="15">
-        <f>SUM(E99:E104)</f>
-        <v/>
-      </c>
-      <c r="F105" s="15">
-        <f>SUM(F99:F104)</f>
-        <v/>
-      </c>
-      <c r="G105" s="15">
-        <f>SUM(G99:G104)</f>
-        <v/>
+      <c r="G105" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>Future income tax liability</t>
+          <t xml:space="preserve">  Due to director</t>
         </is>
       </c>
       <c r="C106" s="10" t="n">
-        <v>16039</v>
+        <v>0</v>
       </c>
       <c r="D106" s="10" t="n">
-        <v>10090</v>
+        <v>0</v>
       </c>
       <c r="E106" s="10" t="n">
-        <v>4211</v>
+        <v>6616</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>849</v>
+        <v>6616</v>
       </c>
       <c r="G106" s="10" t="n">
         <v>0</v>
@@ -2805,406 +2812,407 @@
     <row r="107">
       <c r="B107" s="14" t="inlineStr">
         <is>
+          <t>Total current liabilities</t>
+        </is>
+      </c>
+      <c r="C107" s="15">
+        <f>SUM(C101:C106)</f>
+        <v/>
+      </c>
+      <c r="D107" s="15">
+        <f>SUM(D101:D106)</f>
+        <v/>
+      </c>
+      <c r="E107" s="15">
+        <f>SUM(E101:E106)</f>
+        <v/>
+      </c>
+      <c r="F107" s="15">
+        <f>SUM(F101:F106)</f>
+        <v/>
+      </c>
+      <c r="G107" s="15">
+        <f>SUM(G101:G106)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>Future income tax liability</t>
+        </is>
+      </c>
+      <c r="C108" s="10" t="n">
+        <v>16039</v>
+      </c>
+      <c r="D108" s="10" t="n">
+        <v>10090</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>4211</v>
+      </c>
+      <c r="F108" s="10" t="n">
+        <v>849</v>
+      </c>
+      <c r="G108" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" s="14" t="inlineStr">
+        <is>
           <t>Total liabilities</t>
         </is>
       </c>
-      <c r="C107" s="15">
-        <f>C105+C106</f>
-        <v/>
-      </c>
-      <c r="D107" s="15">
-        <f>D105+D106</f>
-        <v/>
-      </c>
-      <c r="E107" s="15">
-        <f>E105+E106</f>
-        <v/>
-      </c>
-      <c r="F107" s="15">
-        <f>F105+F106</f>
-        <v/>
-      </c>
-      <c r="G107" s="15">
-        <f>G105+G106</f>
-        <v/>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="18" t="n"/>
-      <c r="B108" s="18" t="inlineStr">
+      <c r="C109" s="15">
+        <f>C107+C108</f>
+        <v/>
+      </c>
+      <c r="D109" s="15">
+        <f>D107+D108</f>
+        <v/>
+      </c>
+      <c r="E109" s="15">
+        <f>E107+E108</f>
+        <v/>
+      </c>
+      <c r="F109" s="15">
+        <f>F107+F108</f>
+        <v/>
+      </c>
+      <c r="G109" s="15">
+        <f>G107+G108</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="18" t="n"/>
+      <c r="B110" s="18" t="inlineStr">
         <is>
           <t>Shareholders' equity</t>
         </is>
       </c>
-      <c r="C108" s="18" t="n"/>
-      <c r="D108" s="18" t="n"/>
-      <c r="E108" s="18" t="n"/>
-      <c r="F108" s="18" t="n"/>
-      <c r="G108" s="18" t="n"/>
-      <c r="H108" s="18" t="n"/>
-      <c r="I108" s="18" t="n"/>
-    </row>
-    <row r="109">
-      <c r="B109" s="9" t="inlineStr">
+      <c r="C110" s="18" t="n"/>
+      <c r="D110" s="18" t="n"/>
+      <c r="E110" s="18" t="n"/>
+      <c r="F110" s="18" t="n"/>
+      <c r="G110" s="18" t="n"/>
+      <c r="H110" s="18" t="n"/>
+      <c r="I110" s="18" t="n"/>
+    </row>
+    <row r="111">
+      <c r="B111" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  Share capital</t>
         </is>
       </c>
-      <c r="C109" s="10" t="n">
+      <c r="C111" s="10" t="n">
         <v>1000</v>
       </c>
-      <c r="D109" s="10" t="n">
+      <c r="D111" s="10" t="n">
         <v>1000</v>
       </c>
-      <c r="E109" s="10" t="n">
+      <c r="E111" s="10" t="n">
         <v>1000</v>
       </c>
-      <c r="F109" s="10" t="n">
+      <c r="F111" s="10" t="n">
         <v>1000</v>
       </c>
-      <c r="G109" s="10" t="n">
+      <c r="G111" s="10" t="n">
         <v>1000</v>
       </c>
     </row>
-    <row r="110">
-      <c r="B110" s="9" t="inlineStr">
+    <row r="112">
+      <c r="B112" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  Retained earnings</t>
         </is>
       </c>
-      <c r="C110" s="13">
-        <f>C53</f>
-        <v/>
-      </c>
-      <c r="D110" s="13">
-        <f>D53</f>
-        <v/>
-      </c>
-      <c r="E110" s="13">
-        <f>E53</f>
-        <v/>
-      </c>
-      <c r="F110" s="13">
-        <f>F53</f>
-        <v/>
-      </c>
-      <c r="G110" s="13">
-        <f>G53</f>
-        <v/>
-      </c>
-      <c r="I110" s="12" t="inlineStr">
+      <c r="C112" s="13">
+        <f>C55</f>
+        <v/>
+      </c>
+      <c r="D112" s="13">
+        <f>D55</f>
+        <v/>
+      </c>
+      <c r="E112" s="13">
+        <f>E55</f>
+        <v/>
+      </c>
+      <c r="F112" s="13">
+        <f>F55</f>
+        <v/>
+      </c>
+      <c r="G112" s="13">
+        <f>G55</f>
+        <v/>
+      </c>
+      <c r="I112" s="12" t="inlineStr">
         <is>
           <t>Links to retained earnings, end of year (Income Statement).</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="B111" s="14" t="inlineStr">
+    <row r="113">
+      <c r="B113" s="14" t="inlineStr">
         <is>
           <t>Total shareholders' equity</t>
         </is>
       </c>
-      <c r="C111" s="15">
-        <f>C109+C110</f>
-        <v/>
-      </c>
-      <c r="D111" s="15">
-        <f>D109+D110</f>
-        <v/>
-      </c>
-      <c r="E111" s="15">
-        <f>E109+E110</f>
-        <v/>
-      </c>
-      <c r="F111" s="15">
-        <f>F109+F110</f>
-        <v/>
-      </c>
-      <c r="G111" s="15">
-        <f>G109+G110</f>
-        <v/>
-      </c>
-    </row>
-    <row r="112">
-      <c r="B112" s="23" t="inlineStr">
+      <c r="C113" s="15">
+        <f>C111+C112</f>
+        <v/>
+      </c>
+      <c r="D113" s="15">
+        <f>D111+D112</f>
+        <v/>
+      </c>
+      <c r="E113" s="15">
+        <f>E111+E112</f>
+        <v/>
+      </c>
+      <c r="F113" s="15">
+        <f>F111+F112</f>
+        <v/>
+      </c>
+      <c r="G113" s="15">
+        <f>G111+G112</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="23" t="inlineStr">
         <is>
           <t>TOTAL LIABILITIES AND EQUITY</t>
         </is>
       </c>
-      <c r="C112" s="24">
-        <f>C107+C111</f>
-        <v/>
-      </c>
-      <c r="D112" s="24">
-        <f>D107+D111</f>
-        <v/>
-      </c>
-      <c r="E112" s="24">
-        <f>E107+E111</f>
-        <v/>
-      </c>
-      <c r="F112" s="24">
-        <f>F107+F111</f>
-        <v/>
-      </c>
-      <c r="G112" s="24">
-        <f>G107+G111</f>
-        <v/>
-      </c>
-    </row>
-    <row r="113">
-      <c r="B113" s="9" t="inlineStr">
+      <c r="C114" s="24">
+        <f>C109+C113</f>
+        <v/>
+      </c>
+      <c r="D114" s="24">
+        <f>D109+D113</f>
+        <v/>
+      </c>
+      <c r="E114" s="24">
+        <f>E109+E113</f>
+        <v/>
+      </c>
+      <c r="F114" s="24">
+        <f>F109+F113</f>
+        <v/>
+      </c>
+      <c r="G114" s="24">
+        <f>G109+G113</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="9" t="inlineStr">
         <is>
           <t>Balance check (Total assets − Total liabilities &amp; equity)</t>
         </is>
       </c>
-      <c r="C113" s="13">
-        <f>C96-C112</f>
-        <v/>
-      </c>
-      <c r="D113" s="13">
-        <f>D96-D112</f>
-        <v/>
-      </c>
-      <c r="E113" s="13">
-        <f>E96-E112</f>
-        <v/>
-      </c>
-      <c r="F113" s="13">
-        <f>F96-F112</f>
-        <v/>
-      </c>
-      <c r="G113" s="13">
-        <f>G96-G112</f>
-        <v/>
-      </c>
-    </row>
-    <row r="115" ht="18" customHeight="1">
-      <c r="A115" s="8" t="n"/>
-      <c r="B115" s="8" t="inlineStr">
+      <c r="C115" s="13">
+        <f>C98-C114</f>
+        <v/>
+      </c>
+      <c r="D115" s="13">
+        <f>D98-D114</f>
+        <v/>
+      </c>
+      <c r="E115" s="13">
+        <f>E98-E114</f>
+        <v/>
+      </c>
+      <c r="F115" s="13">
+        <f>F98-F114</f>
+        <v/>
+      </c>
+      <c r="G115" s="13">
+        <f>G98-G114</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117" ht="18" customHeight="1">
+      <c r="A117" s="8" t="n"/>
+      <c r="B117" s="8" t="inlineStr">
         <is>
           <t>CASH FLOW STATEMENT (implied from balance sheet &amp; income statement)</t>
         </is>
       </c>
-      <c r="C115" s="8" t="n"/>
-      <c r="D115" s="8" t="n"/>
-      <c r="E115" s="8" t="n"/>
-      <c r="F115" s="8" t="n"/>
-      <c r="G115" s="8" t="n"/>
-      <c r="H115" s="8" t="n"/>
-      <c r="I115" s="8" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="18" t="n"/>
-      <c r="B116" s="18" t="inlineStr">
+      <c r="C117" s="8" t="n"/>
+      <c r="D117" s="8" t="n"/>
+      <c r="E117" s="8" t="n"/>
+      <c r="F117" s="8" t="n"/>
+      <c r="G117" s="8" t="n"/>
+      <c r="H117" s="8" t="n"/>
+      <c r="I117" s="8" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="18" t="n"/>
+      <c r="B118" s="18" t="inlineStr">
         <is>
           <t>Operating activities</t>
         </is>
       </c>
-      <c r="C116" s="18" t="n"/>
-      <c r="D116" s="18" t="n"/>
-      <c r="E116" s="18" t="n"/>
-      <c r="F116" s="18" t="n"/>
-      <c r="G116" s="18" t="n"/>
-      <c r="H116" s="18" t="n"/>
-      <c r="I116" s="18" t="n"/>
-    </row>
-    <row r="117">
-      <c r="B117" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Net income for the year</t>
-        </is>
-      </c>
-      <c r="C117" s="13" t="n"/>
-      <c r="D117" s="13">
-        <f>D36</f>
-        <v/>
-      </c>
-      <c r="E117" s="13">
-        <f>E36</f>
-        <v/>
-      </c>
-      <c r="F117" s="13">
-        <f>F36</f>
-        <v/>
-      </c>
-      <c r="G117" s="13">
-        <f>G36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="118">
-      <c r="B118" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Add: amortization — office equipment</t>
-        </is>
-      </c>
-      <c r="C118" s="13" t="n"/>
-      <c r="D118" s="13">
-        <f>D19</f>
-        <v/>
-      </c>
-      <c r="E118" s="13">
-        <f>E19</f>
-        <v/>
-      </c>
-      <c r="F118" s="13">
-        <f>F19</f>
-        <v/>
-      </c>
-      <c r="G118" s="13">
-        <f>G19</f>
-        <v/>
-      </c>
+      <c r="C118" s="18" t="n"/>
+      <c r="D118" s="18" t="n"/>
+      <c r="E118" s="18" t="n"/>
+      <c r="F118" s="18" t="n"/>
+      <c r="G118" s="18" t="n"/>
+      <c r="H118" s="18" t="n"/>
+      <c r="I118" s="18" t="n"/>
     </row>
     <row r="119">
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Add: amortization — building and shop equipment</t>
+          <t xml:space="preserve">  Net income for the year</t>
         </is>
       </c>
       <c r="C119" s="13" t="n"/>
       <c r="D119" s="13">
-        <f>D82</f>
+        <f>D36</f>
         <v/>
       </c>
       <c r="E119" s="13">
-        <f>E82</f>
+        <f>E36</f>
         <v/>
       </c>
       <c r="F119" s="13">
-        <f>F82</f>
+        <f>F36</f>
         <v/>
       </c>
       <c r="G119" s="13">
-        <f>G82</f>
+        <f>G36</f>
         <v/>
       </c>
     </row>
     <row r="120">
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Increase / (decrease) in future income tax liability</t>
+          <t xml:space="preserve">  Add: amortization — office equipment</t>
         </is>
       </c>
       <c r="C120" s="13" t="n"/>
       <c r="D120" s="13">
-        <f>D106-C106</f>
+        <f>D19</f>
         <v/>
       </c>
       <c r="E120" s="13">
-        <f>E106-D106</f>
+        <f>E19</f>
         <v/>
       </c>
       <c r="F120" s="13">
-        <f>F106-E106</f>
+        <f>F19</f>
         <v/>
       </c>
       <c r="G120" s="13">
-        <f>G106-F106</f>
+        <f>G19</f>
         <v/>
       </c>
     </row>
     <row r="121">
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (Increase) / decrease in accounts receivable</t>
+          <t xml:space="preserve">  Add: amortization — building and shop equipment</t>
         </is>
       </c>
       <c r="C121" s="13" t="n"/>
       <c r="D121" s="13">
-        <f>-(D89-C89)</f>
+        <f>D84</f>
         <v/>
       </c>
       <c r="E121" s="13">
-        <f>-(E89-D89)</f>
+        <f>E84</f>
         <v/>
       </c>
       <c r="F121" s="13">
-        <f>-(F89-E89)</f>
+        <f>F84</f>
         <v/>
       </c>
       <c r="G121" s="13">
-        <f>-(G89-F89)</f>
+        <f>G84</f>
         <v/>
       </c>
     </row>
     <row r="122">
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (Increase) / decrease in government sales tax recoverable</t>
+          <t xml:space="preserve">  Increase / (decrease) in future income tax liability</t>
         </is>
       </c>
       <c r="C122" s="13" t="n"/>
       <c r="D122" s="13">
-        <f>-(D90-C90)</f>
+        <f>D108-C108</f>
         <v/>
       </c>
       <c r="E122" s="13">
-        <f>-(E90-D90)</f>
+        <f>E108-D108</f>
         <v/>
       </c>
       <c r="F122" s="13">
-        <f>-(F90-E90)</f>
+        <f>F108-E108</f>
         <v/>
       </c>
       <c r="G122" s="13">
-        <f>-(G90-F90)</f>
+        <f>G108-F108</f>
         <v/>
       </c>
     </row>
     <row r="123">
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Increase / (decrease) in accounts payable and accrued liabilities</t>
+          <t xml:space="preserve">  (Increase) / decrease in accounts receivable</t>
         </is>
       </c>
       <c r="C123" s="13" t="n"/>
       <c r="D123" s="13">
-        <f>D100-C100</f>
+        <f>-(D91-C91)</f>
         <v/>
       </c>
       <c r="E123" s="13">
-        <f>E100-D100</f>
+        <f>-(E91-D91)</f>
         <v/>
       </c>
       <c r="F123" s="13">
-        <f>F100-E100</f>
+        <f>-(F91-E91)</f>
         <v/>
       </c>
       <c r="G123" s="13">
-        <f>G100-F100</f>
+        <f>-(G91-F91)</f>
         <v/>
       </c>
     </row>
     <row r="124">
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Increase / (decrease) in payroll deductions payable</t>
+          <t xml:space="preserve">  (Increase) / decrease in government sales tax recoverable</t>
         </is>
       </c>
       <c r="C124" s="13" t="n"/>
       <c r="D124" s="13">
-        <f>D101-C101</f>
+        <f>-(D92-C92)</f>
         <v/>
       </c>
       <c r="E124" s="13">
-        <f>E101-D101</f>
+        <f>-(E92-D92)</f>
         <v/>
       </c>
       <c r="F124" s="13">
-        <f>F101-E101</f>
+        <f>-(F92-E92)</f>
         <v/>
       </c>
       <c r="G124" s="13">
-        <f>G101-F101</f>
+        <f>-(G92-F92)</f>
         <v/>
       </c>
     </row>
     <row r="125">
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Increase / (decrease) in income tax payable</t>
+          <t xml:space="preserve">  Increase / (decrease) in accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="C125" s="13" t="n"/>
@@ -3226,1917 +3234,1965 @@
       </c>
     </row>
     <row r="126">
-      <c r="B126" s="14" t="inlineStr">
+      <c r="B126" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Increase / (decrease) in payroll deductions payable</t>
+        </is>
+      </c>
+      <c r="C126" s="13" t="n"/>
+      <c r="D126" s="13">
+        <f>D103-C103</f>
+        <v/>
+      </c>
+      <c r="E126" s="13">
+        <f>E103-D103</f>
+        <v/>
+      </c>
+      <c r="F126" s="13">
+        <f>F103-E103</f>
+        <v/>
+      </c>
+      <c r="G126" s="13">
+        <f>G103-F103</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Increase / (decrease) in income tax payable</t>
+        </is>
+      </c>
+      <c r="C127" s="13" t="n"/>
+      <c r="D127" s="13">
+        <f>D104-C104</f>
+        <v/>
+      </c>
+      <c r="E127" s="13">
+        <f>E104-D104</f>
+        <v/>
+      </c>
+      <c r="F127" s="13">
+        <f>F104-E104</f>
+        <v/>
+      </c>
+      <c r="G127" s="13">
+        <f>G104-F104</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" s="14" t="inlineStr">
         <is>
           <t>Net cash from operating activities</t>
         </is>
       </c>
-      <c r="C126" s="15" t="n"/>
-      <c r="D126" s="15">
-        <f>SUM(D117:D125)</f>
-        <v/>
-      </c>
-      <c r="E126" s="15">
-        <f>SUM(E117:E125)</f>
-        <v/>
-      </c>
-      <c r="F126" s="15">
-        <f>SUM(F117:F125)</f>
-        <v/>
-      </c>
-      <c r="G126" s="15">
-        <f>SUM(G117:G125)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="18" t="n"/>
-      <c r="B127" s="18" t="inlineStr">
+      <c r="C128" s="15" t="n"/>
+      <c r="D128" s="15">
+        <f>SUM(D119:D127)</f>
+        <v/>
+      </c>
+      <c r="E128" s="15">
+        <f>SUM(E119:E127)</f>
+        <v/>
+      </c>
+      <c r="F128" s="15">
+        <f>SUM(F119:F127)</f>
+        <v/>
+      </c>
+      <c r="G128" s="15">
+        <f>SUM(G119:G127)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="18" t="n"/>
+      <c r="B129" s="18" t="inlineStr">
         <is>
           <t>Investing activities</t>
         </is>
       </c>
-      <c r="C127" s="18" t="n"/>
-      <c r="D127" s="18" t="n"/>
-      <c r="E127" s="18" t="n"/>
-      <c r="F127" s="18" t="n"/>
-      <c r="G127" s="18" t="n"/>
-      <c r="H127" s="18" t="n"/>
-      <c r="I127" s="18" t="n"/>
-    </row>
-    <row r="128">
-      <c r="B128" s="9" t="inlineStr">
+      <c r="C129" s="18" t="n"/>
+      <c r="D129" s="18" t="n"/>
+      <c r="E129" s="18" t="n"/>
+      <c r="F129" s="18" t="n"/>
+      <c r="G129" s="18" t="n"/>
+      <c r="H129" s="18" t="n"/>
+      <c r="I129" s="18" t="n"/>
+    </row>
+    <row r="130">
+      <c r="B130" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  Purchase of land, buildings and equipment (implied)</t>
         </is>
       </c>
-      <c r="C128" s="13" t="n"/>
-      <c r="D128" s="13">
-        <f>-((D95-C95)+D19+D82)</f>
-        <v/>
-      </c>
-      <c r="E128" s="13">
-        <f>-((E95-D95)+E19+E82)</f>
-        <v/>
-      </c>
-      <c r="F128" s="13">
-        <f>-((F95-E95)+F19+F82)</f>
-        <v/>
-      </c>
-      <c r="G128" s="13">
-        <f>-((G95-F95)+G19+G82)</f>
-        <v/>
-      </c>
-      <c r="I128" s="12" t="inlineStr">
+      <c r="C130" s="13" t="n"/>
+      <c r="D130" s="13">
+        <f>-((D97-C97)+D19+D84)</f>
+        <v/>
+      </c>
+      <c r="E130" s="13">
+        <f>-((E97-D97)+E19+E84)</f>
+        <v/>
+      </c>
+      <c r="F130" s="13">
+        <f>-((F97-E97)+F19+F84)</f>
+        <v/>
+      </c>
+      <c r="G130" s="13">
+        <f>-((G97-F97)+G19+G84)</f>
+        <v/>
+      </c>
+      <c r="I130" s="12" t="inlineStr">
         <is>
           <t>Implied capex = Δ net PP&amp;E + total amortization. A positive figure here is a cash inflow (net disposals &gt; additions), as in FY2023.</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="B129" s="14" t="inlineStr">
+    <row r="131">
+      <c r="B131" s="14" t="inlineStr">
         <is>
           <t>Net cash from investing activities</t>
         </is>
       </c>
-      <c r="C129" s="15" t="n"/>
-      <c r="D129" s="15">
-        <f>SUM(D128:D128)</f>
-        <v/>
-      </c>
-      <c r="E129" s="15">
-        <f>SUM(E128:E128)</f>
-        <v/>
-      </c>
-      <c r="F129" s="15">
-        <f>SUM(F128:F128)</f>
-        <v/>
-      </c>
-      <c r="G129" s="15">
-        <f>SUM(G128:G128)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="18" t="n"/>
-      <c r="B130" s="18" t="inlineStr">
+      <c r="C131" s="15" t="n"/>
+      <c r="D131" s="15">
+        <f>SUM(D130:D130)</f>
+        <v/>
+      </c>
+      <c r="E131" s="15">
+        <f>SUM(E130:E130)</f>
+        <v/>
+      </c>
+      <c r="F131" s="15">
+        <f>SUM(F130:F130)</f>
+        <v/>
+      </c>
+      <c r="G131" s="15">
+        <f>SUM(G130:G130)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="18" t="n"/>
+      <c r="B132" s="18" t="inlineStr">
         <is>
           <t>Financing activities</t>
         </is>
       </c>
-      <c r="C130" s="18" t="n"/>
-      <c r="D130" s="18" t="n"/>
-      <c r="E130" s="18" t="n"/>
-      <c r="F130" s="18" t="n"/>
-      <c r="G130" s="18" t="n"/>
-      <c r="H130" s="18" t="n"/>
-      <c r="I130" s="18" t="n"/>
-    </row>
-    <row r="131">
-      <c r="B131" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Increase / (decrease) in bank loan</t>
-        </is>
-      </c>
-      <c r="C131" s="13" t="n"/>
-      <c r="D131" s="13">
-        <f>D99-C99</f>
-        <v/>
-      </c>
-      <c r="E131" s="13">
-        <f>E99-D99</f>
-        <v/>
-      </c>
-      <c r="F131" s="13">
-        <f>F99-E99</f>
-        <v/>
-      </c>
-      <c r="G131" s="13">
-        <f>G99-F99</f>
-        <v/>
-      </c>
-    </row>
-    <row r="132">
-      <c r="B132" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Increase / (decrease) in due to director</t>
-        </is>
-      </c>
-      <c r="C132" s="13" t="n"/>
-      <c r="D132" s="13">
-        <f>D104-C104</f>
-        <v/>
-      </c>
-      <c r="E132" s="13">
-        <f>E104-D104</f>
-        <v/>
-      </c>
-      <c r="F132" s="13">
-        <f>F104-E104</f>
-        <v/>
-      </c>
-      <c r="G132" s="13">
-        <f>G104-F104</f>
-        <v/>
-      </c>
+      <c r="C132" s="18" t="n"/>
+      <c r="D132" s="18" t="n"/>
+      <c r="E132" s="18" t="n"/>
+      <c r="F132" s="18" t="n"/>
+      <c r="G132" s="18" t="n"/>
+      <c r="H132" s="18" t="n"/>
+      <c r="I132" s="18" t="n"/>
     </row>
     <row r="133">
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Increase / (decrease) in due to KEL Tooling</t>
+          <t xml:space="preserve">  Increase / (decrease) in bank loan</t>
         </is>
       </c>
       <c r="C133" s="13" t="n"/>
       <c r="D133" s="13">
-        <f>D103-C103</f>
+        <f>D101-C101</f>
         <v/>
       </c>
       <c r="E133" s="13">
-        <f>E103-D103</f>
+        <f>E101-D101</f>
         <v/>
       </c>
       <c r="F133" s="13">
-        <f>F103-E103</f>
+        <f>F101-E101</f>
         <v/>
       </c>
       <c r="G133" s="13">
-        <f>G103-F103</f>
+        <f>G101-F101</f>
         <v/>
       </c>
     </row>
     <row r="134">
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (Increase) / decrease in due from Related Group of Companies</t>
+          <t xml:space="preserve">  Increase / (decrease) in due to director</t>
         </is>
       </c>
       <c r="C134" s="13" t="n"/>
       <c r="D134" s="13">
-        <f>-(D94-C94)</f>
+        <f>D106-C106</f>
         <v/>
       </c>
       <c r="E134" s="13">
-        <f>-(E94-D94)</f>
+        <f>E106-D106</f>
         <v/>
       </c>
       <c r="F134" s="13">
-        <f>-(F94-E94)</f>
+        <f>F106-E106</f>
         <v/>
       </c>
       <c r="G134" s="13">
-        <f>-(G94-F94)</f>
-        <v/>
-      </c>
-      <c r="I134" s="12" t="inlineStr">
-        <is>
-          <t>Related-party advances — reclassified to financing.</t>
-        </is>
+        <f>G106-F106</f>
+        <v/>
       </c>
     </row>
     <row r="135">
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (Increase) / decrease in due from director</t>
+          <t xml:space="preserve">  Increase / (decrease) in due to KEL Tooling</t>
         </is>
       </c>
       <c r="C135" s="13" t="n"/>
       <c r="D135" s="13">
-        <f>-(D91-C91)</f>
+        <f>D105-C105</f>
         <v/>
       </c>
       <c r="E135" s="13">
-        <f>-(E91-D91)</f>
+        <f>E105-D105</f>
         <v/>
       </c>
       <c r="F135" s="13">
-        <f>-(F91-E91)</f>
+        <f>F105-E105</f>
         <v/>
       </c>
       <c r="G135" s="13">
-        <f>-(G91-F91)</f>
+        <f>G105-F105</f>
         <v/>
       </c>
     </row>
     <row r="136">
       <c r="B136" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (Increase) / decrease in due from KEL Tooling</t>
+          <t xml:space="preserve">  (Increase) / decrease in due from Related Group of Companies</t>
         </is>
       </c>
       <c r="C136" s="13" t="n"/>
       <c r="D136" s="13">
-        <f>-(D92-C92)</f>
+        <f>-(D96-C96)</f>
         <v/>
       </c>
       <c r="E136" s="13">
-        <f>-(E92-D92)</f>
+        <f>-(E96-D96)</f>
         <v/>
       </c>
       <c r="F136" s="13">
-        <f>-(F92-E92)</f>
+        <f>-(F96-E96)</f>
         <v/>
       </c>
       <c r="G136" s="13">
-        <f>-(G92-F92)</f>
-        <v/>
+        <f>-(G96-F96)</f>
+        <v/>
+      </c>
+      <c r="I136" s="12" t="inlineStr">
+        <is>
+          <t>Related-party advances — reclassified to financing.</t>
+        </is>
       </c>
     </row>
     <row r="137">
       <c r="B137" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Dividends paid</t>
+          <t xml:space="preserve">  (Increase) / decrease in due from director</t>
         </is>
       </c>
       <c r="C137" s="13" t="n"/>
       <c r="D137" s="13">
-        <f>-D52</f>
+        <f>-(D93-C93)</f>
         <v/>
       </c>
       <c r="E137" s="13">
-        <f>-E52</f>
+        <f>-(E93-D93)</f>
         <v/>
       </c>
       <c r="F137" s="13">
-        <f>-F52</f>
+        <f>-(F93-E93)</f>
         <v/>
       </c>
       <c r="G137" s="13">
-        <f>-G52</f>
+        <f>-(G93-F93)</f>
         <v/>
       </c>
     </row>
     <row r="138">
       <c r="B138" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Issuance of share capital</t>
+          <t xml:space="preserve">  (Increase) / decrease in due from KEL Tooling</t>
         </is>
       </c>
       <c r="C138" s="13" t="n"/>
       <c r="D138" s="13">
-        <f>D109-C109</f>
+        <f>-(D94-C94)</f>
         <v/>
       </c>
       <c r="E138" s="13">
-        <f>E109-D109</f>
+        <f>-(E94-D94)</f>
         <v/>
       </c>
       <c r="F138" s="13">
-        <f>F109-E109</f>
+        <f>-(F94-E94)</f>
         <v/>
       </c>
       <c r="G138" s="13">
-        <f>G109-F109</f>
+        <f>-(G94-F94)</f>
         <v/>
       </c>
     </row>
     <row r="139">
-      <c r="B139" s="14" t="inlineStr">
+      <c r="B139" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Dividends paid</t>
+        </is>
+      </c>
+      <c r="C139" s="13" t="n"/>
+      <c r="D139" s="13">
+        <f>-D54</f>
+        <v/>
+      </c>
+      <c r="E139" s="13">
+        <f>-E54</f>
+        <v/>
+      </c>
+      <c r="F139" s="13">
+        <f>-F54</f>
+        <v/>
+      </c>
+      <c r="G139" s="13">
+        <f>-G54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Issuance of share capital</t>
+        </is>
+      </c>
+      <c r="C140" s="13" t="n"/>
+      <c r="D140" s="13">
+        <f>D111-C111</f>
+        <v/>
+      </c>
+      <c r="E140" s="13">
+        <f>E111-D111</f>
+        <v/>
+      </c>
+      <c r="F140" s="13">
+        <f>F111-E111</f>
+        <v/>
+      </c>
+      <c r="G140" s="13">
+        <f>G111-F111</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" s="14" t="inlineStr">
         <is>
           <t>Net cash from financing activities</t>
         </is>
       </c>
-      <c r="C139" s="15" t="n"/>
-      <c r="D139" s="15">
-        <f>SUM(D131:D138)</f>
-        <v/>
-      </c>
-      <c r="E139" s="15">
-        <f>SUM(E131:E138)</f>
-        <v/>
-      </c>
-      <c r="F139" s="15">
-        <f>SUM(F131:F138)</f>
-        <v/>
-      </c>
-      <c r="G139" s="15">
-        <f>SUM(G131:G138)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="140">
-      <c r="B140" s="19" t="inlineStr">
+      <c r="C141" s="15" t="n"/>
+      <c r="D141" s="15">
+        <f>SUM(D133:D140)</f>
+        <v/>
+      </c>
+      <c r="E141" s="15">
+        <f>SUM(E133:E140)</f>
+        <v/>
+      </c>
+      <c r="F141" s="15">
+        <f>SUM(F133:F140)</f>
+        <v/>
+      </c>
+      <c r="G141" s="15">
+        <f>SUM(G133:G140)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" s="19" t="inlineStr">
         <is>
           <t>Net change in cash</t>
         </is>
       </c>
-      <c r="C140" s="20">
-        <f>C126+C129+C139</f>
-        <v/>
-      </c>
-      <c r="D140" s="20">
-        <f>D126+D129+D139</f>
-        <v/>
-      </c>
-      <c r="E140" s="20">
-        <f>E126+E129+E139</f>
-        <v/>
-      </c>
-      <c r="F140" s="20">
-        <f>F126+F129+F139</f>
-        <v/>
-      </c>
-      <c r="G140" s="20">
-        <f>G126+G129+G139</f>
-        <v/>
-      </c>
-    </row>
-    <row r="141">
-      <c r="B141" s="9" t="inlineStr">
-        <is>
-          <t>Cash, beginning of year</t>
-        </is>
-      </c>
-      <c r="C141" s="13" t="n"/>
-      <c r="D141" s="13">
-        <f>C88</f>
-        <v/>
-      </c>
-      <c r="E141" s="13">
-        <f>D88</f>
-        <v/>
-      </c>
-      <c r="F141" s="13">
-        <f>E88</f>
-        <v/>
-      </c>
-      <c r="G141" s="13">
-        <f>F88</f>
-        <v/>
-      </c>
-    </row>
-    <row r="142">
-      <c r="B142" s="14" t="inlineStr">
-        <is>
-          <t>Cash, end of year</t>
-        </is>
-      </c>
-      <c r="C142" s="15" t="n"/>
-      <c r="D142" s="15">
-        <f>D141+D140</f>
-        <v/>
-      </c>
-      <c r="E142" s="15">
-        <f>E141+E140</f>
-        <v/>
-      </c>
-      <c r="F142" s="15">
-        <f>F141+F140</f>
-        <v/>
-      </c>
-      <c r="G142" s="15">
-        <f>G141+G140</f>
+      <c r="C142" s="20">
+        <f>C128+C131+C141</f>
+        <v/>
+      </c>
+      <c r="D142" s="20">
+        <f>D128+D131+D141</f>
+        <v/>
+      </c>
+      <c r="E142" s="20">
+        <f>E128+E131+E141</f>
+        <v/>
+      </c>
+      <c r="F142" s="20">
+        <f>F128+F131+F141</f>
+        <v/>
+      </c>
+      <c r="G142" s="20">
+        <f>G128+G131+G141</f>
         <v/>
       </c>
     </row>
     <row r="143">
       <c r="B143" s="9" t="inlineStr">
         <is>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="C143" s="13" t="n"/>
+      <c r="D143" s="13">
+        <f>C90</f>
+        <v/>
+      </c>
+      <c r="E143" s="13">
+        <f>D90</f>
+        <v/>
+      </c>
+      <c r="F143" s="13">
+        <f>E90</f>
+        <v/>
+      </c>
+      <c r="G143" s="13">
+        <f>F90</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" s="14" t="inlineStr">
+        <is>
+          <t>Cash, end of year</t>
+        </is>
+      </c>
+      <c r="C144" s="15" t="n"/>
+      <c r="D144" s="15">
+        <f>D143+D142</f>
+        <v/>
+      </c>
+      <c r="E144" s="15">
+        <f>E143+E142</f>
+        <v/>
+      </c>
+      <c r="F144" s="15">
+        <f>F143+F142</f>
+        <v/>
+      </c>
+      <c r="G144" s="15">
+        <f>G143+G142</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" s="9" t="inlineStr">
+        <is>
           <t>Tie-out check (implied ending cash − balance sheet cash)</t>
         </is>
       </c>
-      <c r="C143" s="13">
-        <f>C142-C88</f>
-        <v/>
-      </c>
-      <c r="D143" s="13">
-        <f>D142-D88</f>
-        <v/>
-      </c>
-      <c r="E143" s="13">
-        <f>E142-E88</f>
-        <v/>
-      </c>
-      <c r="F143" s="13">
-        <f>F142-F88</f>
-        <v/>
-      </c>
-      <c r="G143" s="13">
-        <f>G142-G88</f>
-        <v/>
-      </c>
-    </row>
-    <row r="145" ht="18" customHeight="1">
-      <c r="A145" s="8" t="n"/>
-      <c r="B145" s="8" t="inlineStr">
+      <c r="C145" s="13">
+        <f>C144-C90</f>
+        <v/>
+      </c>
+      <c r="D145" s="13">
+        <f>D144-D90</f>
+        <v/>
+      </c>
+      <c r="E145" s="13">
+        <f>E144-E90</f>
+        <v/>
+      </c>
+      <c r="F145" s="13">
+        <f>F144-F90</f>
+        <v/>
+      </c>
+      <c r="G145" s="13">
+        <f>G144-G90</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147" ht="18" customHeight="1">
+      <c r="A147" s="8" t="n"/>
+      <c r="B147" s="8" t="inlineStr">
         <is>
           <t>AMORTIZATION &amp; PP&amp;E SCHEDULE</t>
         </is>
       </c>
-      <c r="C145" s="8" t="n"/>
-      <c r="D145" s="8" t="n"/>
-      <c r="E145" s="8" t="n"/>
-      <c r="F145" s="8" t="n"/>
-      <c r="G145" s="8" t="n"/>
-      <c r="H145" s="8" t="n"/>
-      <c r="I145" s="8" t="n"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="18" t="n"/>
-      <c r="B146" s="18" t="inlineStr">
+      <c r="C147" s="8" t="n"/>
+      <c r="D147" s="8" t="n"/>
+      <c r="E147" s="8" t="n"/>
+      <c r="F147" s="8" t="n"/>
+      <c r="G147" s="8" t="n"/>
+      <c r="H147" s="8" t="n"/>
+      <c r="I147" s="8" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="18" t="n"/>
+      <c r="B148" s="18" t="inlineStr">
         <is>
           <t>Amortization (depreciation) by category</t>
         </is>
       </c>
-      <c r="C146" s="18" t="n"/>
-      <c r="D146" s="18" t="n"/>
-      <c r="E146" s="18" t="n"/>
-      <c r="F146" s="18" t="n"/>
-      <c r="G146" s="18" t="n"/>
-      <c r="H146" s="18" t="n"/>
-      <c r="I146" s="18" t="n"/>
-    </row>
-    <row r="147">
-      <c r="B147" s="9" t="inlineStr">
+      <c r="C148" s="18" t="n"/>
+      <c r="D148" s="18" t="n"/>
+      <c r="E148" s="18" t="n"/>
+      <c r="F148" s="18" t="n"/>
+      <c r="G148" s="18" t="n"/>
+      <c r="H148" s="18" t="n"/>
+      <c r="I148" s="18" t="n"/>
+    </row>
+    <row r="149">
+      <c r="B149" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  Amortization — office equipment (G&amp;A)</t>
         </is>
       </c>
-      <c r="C147" s="13">
+      <c r="C149" s="13">
         <f>C19</f>
         <v/>
       </c>
-      <c r="D147" s="13">
+      <c r="D149" s="13">
         <f>D19</f>
         <v/>
       </c>
-      <c r="E147" s="13">
+      <c r="E149" s="13">
         <f>E19</f>
         <v/>
       </c>
-      <c r="F147" s="13">
+      <c r="F149" s="13">
         <f>F19</f>
         <v/>
       </c>
-      <c r="G147" s="13">
+      <c r="G149" s="13">
         <f>G19</f>
         <v/>
       </c>
     </row>
-    <row r="148">
-      <c r="B148" s="9" t="inlineStr">
+    <row r="150">
+      <c r="B150" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  Amortization — building and shop equipment (COGS)</t>
         </is>
       </c>
-      <c r="C148" s="13">
-        <f>C82</f>
-        <v/>
-      </c>
-      <c r="D148" s="13">
-        <f>D82</f>
-        <v/>
-      </c>
-      <c r="E148" s="13">
-        <f>E82</f>
-        <v/>
-      </c>
-      <c r="F148" s="13">
-        <f>F82</f>
-        <v/>
-      </c>
-      <c r="G148" s="13">
-        <f>G82</f>
-        <v/>
-      </c>
-    </row>
-    <row r="149">
-      <c r="B149" s="14" t="inlineStr">
+      <c r="C150" s="13">
+        <f>C84</f>
+        <v/>
+      </c>
+      <c r="D150" s="13">
+        <f>D84</f>
+        <v/>
+      </c>
+      <c r="E150" s="13">
+        <f>E84</f>
+        <v/>
+      </c>
+      <c r="F150" s="13">
+        <f>F84</f>
+        <v/>
+      </c>
+      <c r="G150" s="13">
+        <f>G84</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" s="14" t="inlineStr">
         <is>
           <t>Total amortization (D&amp;A)</t>
         </is>
       </c>
-      <c r="C149" s="15">
-        <f>C19+C82</f>
-        <v/>
-      </c>
-      <c r="D149" s="15">
-        <f>D19+D82</f>
-        <v/>
-      </c>
-      <c r="E149" s="15">
-        <f>E19+E82</f>
-        <v/>
-      </c>
-      <c r="F149" s="15">
-        <f>F19+F82</f>
-        <v/>
-      </c>
-      <c r="G149" s="15">
-        <f>G19+G82</f>
-        <v/>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="18" t="n"/>
-      <c r="B150" s="18" t="inlineStr">
+      <c r="C151" s="15">
+        <f>C19+C84</f>
+        <v/>
+      </c>
+      <c r="D151" s="15">
+        <f>D19+D84</f>
+        <v/>
+      </c>
+      <c r="E151" s="15">
+        <f>E19+E84</f>
+        <v/>
+      </c>
+      <c r="F151" s="15">
+        <f>F19+F84</f>
+        <v/>
+      </c>
+      <c r="G151" s="15">
+        <f>G19+G84</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="18" t="n"/>
+      <c r="B152" s="18" t="inlineStr">
         <is>
           <t>PP&amp;E rollforward (net book value)</t>
         </is>
       </c>
-      <c r="C150" s="18" t="n"/>
-      <c r="D150" s="18" t="n"/>
-      <c r="E150" s="18" t="n"/>
-      <c r="F150" s="18" t="n"/>
-      <c r="G150" s="18" t="n"/>
-      <c r="H150" s="18" t="n"/>
-      <c r="I150" s="18" t="n"/>
-    </row>
-    <row r="151">
-      <c r="B151" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  PP&amp;E, beginning of year</t>
-        </is>
-      </c>
-      <c r="C151" s="13" t="n"/>
-      <c r="D151" s="13">
-        <f>C95</f>
-        <v/>
-      </c>
-      <c r="E151" s="13">
-        <f>D95</f>
-        <v/>
-      </c>
-      <c r="F151" s="13">
-        <f>E95</f>
-        <v/>
-      </c>
-      <c r="G151" s="13">
-        <f>F95</f>
-        <v/>
-      </c>
-    </row>
-    <row r="152">
-      <c r="B152" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Add: capital expenditures (implied)</t>
-        </is>
-      </c>
-      <c r="C152" s="13" t="n"/>
-      <c r="D152" s="13">
-        <f>-D128</f>
-        <v/>
-      </c>
-      <c r="E152" s="13">
-        <f>-E128</f>
-        <v/>
-      </c>
-      <c r="F152" s="13">
-        <f>-F128</f>
-        <v/>
-      </c>
-      <c r="G152" s="13">
-        <f>-G128</f>
-        <v/>
-      </c>
+      <c r="C152" s="18" t="n"/>
+      <c r="D152" s="18" t="n"/>
+      <c r="E152" s="18" t="n"/>
+      <c r="F152" s="18" t="n"/>
+      <c r="G152" s="18" t="n"/>
+      <c r="H152" s="18" t="n"/>
+      <c r="I152" s="18" t="n"/>
     </row>
     <row r="153">
       <c r="B153" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Less: total amortization</t>
+          <t xml:space="preserve">  PP&amp;E, beginning of year</t>
         </is>
       </c>
       <c r="C153" s="13" t="n"/>
       <c r="D153" s="13">
-        <f>-(D19+D82)</f>
+        <f>C97</f>
         <v/>
       </c>
       <c r="E153" s="13">
-        <f>-(E19+E82)</f>
+        <f>D97</f>
         <v/>
       </c>
       <c r="F153" s="13">
-        <f>-(F19+F82)</f>
+        <f>E97</f>
         <v/>
       </c>
       <c r="G153" s="13">
-        <f>-(G19+G82)</f>
+        <f>F97</f>
         <v/>
       </c>
     </row>
     <row r="154">
-      <c r="B154" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  PP&amp;E, end of year</t>
-        </is>
-      </c>
-      <c r="C154" s="15" t="n"/>
-      <c r="D154" s="15">
-        <f>D151+D152+D153</f>
-        <v/>
-      </c>
-      <c r="E154" s="15">
-        <f>E151+E152+E153</f>
-        <v/>
-      </c>
-      <c r="F154" s="15">
-        <f>F151+F152+F153</f>
-        <v/>
-      </c>
-      <c r="G154" s="15">
-        <f>G151+G152+G153</f>
+      <c r="B154" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Add: capital expenditures (implied)</t>
+        </is>
+      </c>
+      <c r="C154" s="13" t="n"/>
+      <c r="D154" s="13">
+        <f>-D130</f>
+        <v/>
+      </c>
+      <c r="E154" s="13">
+        <f>-E130</f>
+        <v/>
+      </c>
+      <c r="F154" s="13">
+        <f>-F130</f>
+        <v/>
+      </c>
+      <c r="G154" s="13">
+        <f>-G130</f>
         <v/>
       </c>
     </row>
     <row r="155">
       <c r="B155" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Check (rollforward − balance sheet PP&amp;E)</t>
+          <t xml:space="preserve">  Less: total amortization</t>
         </is>
       </c>
       <c r="C155" s="13" t="n"/>
       <c r="D155" s="13">
-        <f>D154-D95</f>
+        <f>-(D19+D84)</f>
         <v/>
       </c>
       <c r="E155" s="13">
-        <f>E154-E95</f>
+        <f>-(E19+E84)</f>
         <v/>
       </c>
       <c r="F155" s="13">
-        <f>F154-F95</f>
+        <f>-(F19+F84)</f>
         <v/>
       </c>
       <c r="G155" s="13">
-        <f>G154-G95</f>
+        <f>-(G19+G84)</f>
         <v/>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="18" t="n"/>
-      <c r="B156" s="18" t="inlineStr">
-        <is>
-          <t>Implied useful-life analysis</t>
-        </is>
-      </c>
-      <c r="C156" s="18" t="n"/>
-      <c r="D156" s="18" t="n"/>
-      <c r="E156" s="18" t="n"/>
-      <c r="F156" s="18" t="n"/>
-      <c r="G156" s="18" t="n"/>
-      <c r="H156" s="18" t="n"/>
-      <c r="I156" s="18" t="n"/>
+      <c r="B156" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PP&amp;E, end of year</t>
+        </is>
+      </c>
+      <c r="C156" s="15" t="n"/>
+      <c r="D156" s="15">
+        <f>D153+D154+D155</f>
+        <v/>
+      </c>
+      <c r="E156" s="15">
+        <f>E153+E154+E155</f>
+        <v/>
+      </c>
+      <c r="F156" s="15">
+        <f>F153+F154+F155</f>
+        <v/>
+      </c>
+      <c r="G156" s="15">
+        <f>G153+G154+G155</f>
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="B157" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Check (rollforward − balance sheet PP&amp;E)</t>
+        </is>
+      </c>
+      <c r="C157" s="13" t="n"/>
+      <c r="D157" s="13">
+        <f>D156-D97</f>
+        <v/>
+      </c>
+      <c r="E157" s="13">
+        <f>E156-E97</f>
+        <v/>
+      </c>
+      <c r="F157" s="13">
+        <f>F156-F97</f>
+        <v/>
+      </c>
+      <c r="G157" s="13">
+        <f>G156-G97</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="18" t="n"/>
+      <c r="B158" s="18" t="inlineStr">
+        <is>
+          <t>Implied useful-life analysis</t>
+        </is>
+      </c>
+      <c r="C158" s="18" t="n"/>
+      <c r="D158" s="18" t="n"/>
+      <c r="E158" s="18" t="n"/>
+      <c r="F158" s="18" t="n"/>
+      <c r="G158" s="18" t="n"/>
+      <c r="H158" s="18" t="n"/>
+      <c r="I158" s="18" t="n"/>
+    </row>
+    <row r="159">
+      <c r="B159" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Net PP&amp;E, end of year</t>
         </is>
       </c>
-      <c r="C157" s="13">
-        <f>C95</f>
-        <v/>
-      </c>
-      <c r="D157" s="13">
-        <f>D95</f>
-        <v/>
-      </c>
-      <c r="E157" s="13">
-        <f>E95</f>
-        <v/>
-      </c>
-      <c r="F157" s="13">
-        <f>F95</f>
-        <v/>
-      </c>
-      <c r="G157" s="13">
-        <f>G95</f>
-        <v/>
-      </c>
-    </row>
-    <row r="158">
-      <c r="B158" s="9" t="inlineStr">
+      <c r="C159" s="13">
+        <f>C97</f>
+        <v/>
+      </c>
+      <c r="D159" s="13">
+        <f>D97</f>
+        <v/>
+      </c>
+      <c r="E159" s="13">
+        <f>E97</f>
+        <v/>
+      </c>
+      <c r="F159" s="13">
+        <f>F97</f>
+        <v/>
+      </c>
+      <c r="G159" s="13">
+        <f>G97</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  Total amortization (D&amp;A)</t>
         </is>
       </c>
-      <c r="C158" s="13">
-        <f>C149</f>
-        <v/>
-      </c>
-      <c r="D158" s="13">
-        <f>D149</f>
-        <v/>
-      </c>
-      <c r="E158" s="13">
-        <f>E149</f>
-        <v/>
-      </c>
-      <c r="F158" s="13">
-        <f>F149</f>
-        <v/>
-      </c>
-      <c r="G158" s="13">
-        <f>G149</f>
-        <v/>
-      </c>
-    </row>
-    <row r="159">
-      <c r="B159" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Implied depreciation rate (D&amp;A / beginning net PP&amp;E)</t>
-        </is>
-      </c>
-      <c r="C159" s="17" t="n"/>
-      <c r="D159" s="17">
-        <f>IFERROR(D149/C95,"")</f>
-        <v/>
-      </c>
-      <c r="E159" s="17">
-        <f>IFERROR(E149/D95,"")</f>
-        <v/>
-      </c>
-      <c r="F159" s="17">
-        <f>IFERROR(F149/E95,"")</f>
-        <v/>
-      </c>
-      <c r="G159" s="17">
-        <f>IFERROR(G149/F95,"")</f>
-        <v/>
-      </c>
-      <c r="I159" s="12" t="inlineStr">
-        <is>
-          <t>Annual amortization as a % of opening net book value.</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="B160" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Implied remaining useful life (net PP&amp;E / D&amp;A)</t>
-        </is>
-      </c>
-      <c r="C160" s="25">
-        <f>IFERROR(C95/C149,"")</f>
-        <v/>
-      </c>
-      <c r="D160" s="25">
-        <f>IFERROR(D95/D149,"")</f>
-        <v/>
-      </c>
-      <c r="E160" s="25">
-        <f>IFERROR(E95/E149,"")</f>
-        <v/>
-      </c>
-      <c r="F160" s="25">
-        <f>IFERROR(F95/F149,"")</f>
-        <v/>
-      </c>
-      <c r="G160" s="25">
-        <f>IFERROR(G95/G149,"")</f>
-        <v/>
-      </c>
-      <c r="I160" s="12" t="inlineStr">
-        <is>
-          <t>Years of amortization remaining at the current run-rate on the net book value.</t>
-        </is>
+      <c r="C160" s="13">
+        <f>C151</f>
+        <v/>
+      </c>
+      <c r="D160" s="13">
+        <f>D151</f>
+        <v/>
+      </c>
+      <c r="E160" s="13">
+        <f>E151</f>
+        <v/>
+      </c>
+      <c r="F160" s="13">
+        <f>F151</f>
+        <v/>
+      </c>
+      <c r="G160" s="13">
+        <f>G151</f>
+        <v/>
       </c>
     </row>
     <row r="161">
       <c r="B161" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Capex intensity (implied capex / D&amp;A)</t>
-        </is>
-      </c>
-      <c r="C161" s="26" t="n"/>
-      <c r="D161" s="26">
-        <f>IFERROR(-D128/D149,"")</f>
-        <v/>
-      </c>
-      <c r="E161" s="26">
-        <f>IFERROR(-E128/E149,"")</f>
-        <v/>
-      </c>
-      <c r="F161" s="26">
-        <f>IFERROR(-F128/F149,"")</f>
-        <v/>
-      </c>
-      <c r="G161" s="26">
-        <f>IFERROR(-G128/G149,"")</f>
+          <t xml:space="preserve">  Implied depreciation rate (D&amp;A / beginning net PP&amp;E)</t>
+        </is>
+      </c>
+      <c r="C161" s="17" t="n"/>
+      <c r="D161" s="17">
+        <f>IFERROR(D151/C97,"")</f>
+        <v/>
+      </c>
+      <c r="E161" s="17">
+        <f>IFERROR(E151/D97,"")</f>
+        <v/>
+      </c>
+      <c r="F161" s="17">
+        <f>IFERROR(F151/E97,"")</f>
+        <v/>
+      </c>
+      <c r="G161" s="17">
+        <f>IFERROR(G151/F97,"")</f>
         <v/>
       </c>
       <c r="I161" s="12" t="inlineStr">
         <is>
-          <t>Reinvestment ratio: &gt;1x grows the asset base, &lt;1x shrinks it.</t>
+          <t>Annual amortization as a % of opening net book value.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="B162" s="16" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Implied remaining useful life (net PP&amp;E / D&amp;A)</t>
+        </is>
+      </c>
+      <c r="C162" s="25">
+        <f>IFERROR(C97/C151,"")</f>
+        <v/>
+      </c>
+      <c r="D162" s="25">
+        <f>IFERROR(D97/D151,"")</f>
+        <v/>
+      </c>
+      <c r="E162" s="25">
+        <f>IFERROR(E97/E151,"")</f>
+        <v/>
+      </c>
+      <c r="F162" s="25">
+        <f>IFERROR(F97/F151,"")</f>
+        <v/>
+      </c>
+      <c r="G162" s="25">
+        <f>IFERROR(G97/G151,"")</f>
+        <v/>
+      </c>
+      <c r="I162" s="12" t="inlineStr">
+        <is>
+          <t>Years of amortization remaining at the current run-rate on the net book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Capex intensity (implied capex / D&amp;A)</t>
+        </is>
+      </c>
+      <c r="C163" s="26" t="n"/>
+      <c r="D163" s="26">
+        <f>IFERROR(-D130/D151,"")</f>
+        <v/>
+      </c>
+      <c r="E163" s="26">
+        <f>IFERROR(-E130/E151,"")</f>
+        <v/>
+      </c>
+      <c r="F163" s="26">
+        <f>IFERROR(-F130/F151,"")</f>
+        <v/>
+      </c>
+      <c r="G163" s="26">
+        <f>IFERROR(-G130/G151,"")</f>
+        <v/>
+      </c>
+      <c r="I163" s="12" t="inlineStr">
+        <is>
+          <t>Reinvestment ratio: &gt;1x grows the asset base, &lt;1x shrinks it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" s="16" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Capex % of revenue</t>
         </is>
       </c>
-      <c r="C162" s="17" t="n"/>
-      <c r="D162" s="17">
-        <f>IFERROR(-D128/D9,"")</f>
-        <v/>
-      </c>
-      <c r="E162" s="17">
-        <f>IFERROR(-E128/E9,"")</f>
-        <v/>
-      </c>
-      <c r="F162" s="17">
-        <f>IFERROR(-F128/F9,"")</f>
-        <v/>
-      </c>
-      <c r="G162" s="17">
-        <f>IFERROR(-G128/G9,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="164" ht="18" customHeight="1">
-      <c r="A164" s="8" t="n"/>
-      <c r="B164" s="8" t="inlineStr">
+      <c r="C164" s="17" t="n"/>
+      <c r="D164" s="17">
+        <f>IFERROR(-D130/D9,"")</f>
+        <v/>
+      </c>
+      <c r="E164" s="17">
+        <f>IFERROR(-E130/E9,"")</f>
+        <v/>
+      </c>
+      <c r="F164" s="17">
+        <f>IFERROR(-F130/F9,"")</f>
+        <v/>
+      </c>
+      <c r="G164" s="17">
+        <f>IFERROR(-G130/G9,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166" ht="18" customHeight="1">
+      <c r="A166" s="8" t="n"/>
+      <c r="B166" s="8" t="inlineStr">
         <is>
           <t>RATIO ANALYSIS &amp; FREE CASH FLOW</t>
         </is>
       </c>
-      <c r="C164" s="8" t="n"/>
-      <c r="D164" s="8" t="n"/>
-      <c r="E164" s="8" t="n"/>
-      <c r="F164" s="8" t="n"/>
-      <c r="G164" s="8" t="n"/>
-      <c r="H164" s="8" t="n"/>
-      <c r="I164" s="8" t="n"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="18" t="n"/>
-      <c r="B165" s="18" t="inlineStr">
+      <c r="C166" s="8" t="n"/>
+      <c r="D166" s="8" t="n"/>
+      <c r="E166" s="8" t="n"/>
+      <c r="F166" s="8" t="n"/>
+      <c r="G166" s="8" t="n"/>
+      <c r="H166" s="8" t="n"/>
+      <c r="I166" s="8" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="18" t="n"/>
+      <c r="B167" s="18" t="inlineStr">
         <is>
           <t>Cash generation</t>
         </is>
       </c>
-      <c r="C165" s="18" t="n"/>
-      <c r="D165" s="18" t="n"/>
-      <c r="E165" s="18" t="n"/>
-      <c r="F165" s="18" t="n"/>
-      <c r="G165" s="18" t="n"/>
-      <c r="H165" s="18" t="n"/>
-      <c r="I165" s="18" t="n"/>
-    </row>
-    <row r="166">
-      <c r="B166" s="9" t="inlineStr">
+      <c r="C167" s="18" t="n"/>
+      <c r="D167" s="18" t="n"/>
+      <c r="E167" s="18" t="n"/>
+      <c r="F167" s="18" t="n"/>
+      <c r="G167" s="18" t="n"/>
+      <c r="H167" s="18" t="n"/>
+      <c r="I167" s="18" t="n"/>
+    </row>
+    <row r="168">
+      <c r="B168" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  Free cash flow (CFO − capex)</t>
         </is>
       </c>
-      <c r="C166" s="13">
-        <f>C126+C128</f>
-        <v/>
-      </c>
-      <c r="D166" s="13">
-        <f>D126+D128</f>
-        <v/>
-      </c>
-      <c r="E166" s="13">
-        <f>E126+E128</f>
-        <v/>
-      </c>
-      <c r="F166" s="13">
-        <f>F126+F128</f>
-        <v/>
-      </c>
-      <c r="G166" s="13">
-        <f>G126+G128</f>
-        <v/>
-      </c>
-    </row>
-    <row r="167">
-      <c r="B167" s="16" t="inlineStr">
+      <c r="C168" s="13">
+        <f>C128+C130</f>
+        <v/>
+      </c>
+      <c r="D168" s="13">
+        <f>D128+D130</f>
+        <v/>
+      </c>
+      <c r="E168" s="13">
+        <f>E128+E130</f>
+        <v/>
+      </c>
+      <c r="F168" s="13">
+        <f>F128+F130</f>
+        <v/>
+      </c>
+      <c r="G168" s="13">
+        <f>G128+G130</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  FCF conversion (FCF / net income)</t>
         </is>
       </c>
-      <c r="C167" s="26" t="n"/>
-      <c r="D167" s="26">
-        <f>IFERROR((D126+D128)/D36,"")</f>
-        <v/>
-      </c>
-      <c r="E167" s="26">
-        <f>IFERROR((E126+E128)/E36,"")</f>
-        <v/>
-      </c>
-      <c r="F167" s="26">
-        <f>IFERROR((F126+F128)/F36,"")</f>
-        <v/>
-      </c>
-      <c r="G167" s="26">
-        <f>IFERROR((G126+G128)/G36,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="168">
-      <c r="B168" s="16" t="inlineStr">
+      <c r="C169" s="26" t="n"/>
+      <c r="D169" s="26">
+        <f>IFERROR((D128+D130)/D36,"")</f>
+        <v/>
+      </c>
+      <c r="E169" s="26">
+        <f>IFERROR((E128+E130)/E36,"")</f>
+        <v/>
+      </c>
+      <c r="F169" s="26">
+        <f>IFERROR((F128+F130)/F36,"")</f>
+        <v/>
+      </c>
+      <c r="G169" s="26">
+        <f>IFERROR((G128+G130)/G36,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex % of revenue</t>
         </is>
       </c>
-      <c r="C168" s="17" t="n"/>
-      <c r="D168" s="17">
-        <f>IFERROR(-D128/D9,"")</f>
-        <v/>
-      </c>
-      <c r="E168" s="17">
-        <f>IFERROR(-E128/E9,"")</f>
-        <v/>
-      </c>
-      <c r="F168" s="17">
-        <f>IFERROR(-F128/F9,"")</f>
-        <v/>
-      </c>
-      <c r="G168" s="17">
-        <f>IFERROR(-G128/G9,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="18" t="n"/>
-      <c r="B169" s="18" t="inlineStr">
+      <c r="C170" s="17" t="n"/>
+      <c r="D170" s="17">
+        <f>IFERROR(-D130/D9,"")</f>
+        <v/>
+      </c>
+      <c r="E170" s="17">
+        <f>IFERROR(-E130/E9,"")</f>
+        <v/>
+      </c>
+      <c r="F170" s="17">
+        <f>IFERROR(-F130/F9,"")</f>
+        <v/>
+      </c>
+      <c r="G170" s="17">
+        <f>IFERROR(-G130/G9,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="18" t="n"/>
+      <c r="B171" s="18" t="inlineStr">
         <is>
           <t>Returns</t>
         </is>
       </c>
-      <c r="C169" s="18" t="n"/>
-      <c r="D169" s="18" t="n"/>
-      <c r="E169" s="18" t="n"/>
-      <c r="F169" s="18" t="n"/>
-      <c r="G169" s="18" t="n"/>
-      <c r="H169" s="18" t="n"/>
-      <c r="I169" s="18" t="n"/>
-    </row>
-    <row r="170">
-      <c r="B170" s="9" t="inlineStr">
-        <is>
-          <t>Operating earnings (EBIT)</t>
-        </is>
-      </c>
-      <c r="C170" s="13">
-        <f>C31+C18</f>
-        <v/>
-      </c>
-      <c r="D170" s="13">
-        <f>D31+D18</f>
-        <v/>
-      </c>
-      <c r="E170" s="13">
-        <f>E31+E18</f>
-        <v/>
-      </c>
-      <c r="F170" s="13">
-        <f>F31+F18</f>
-        <v/>
-      </c>
-      <c r="G170" s="13">
-        <f>G31+G18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="171">
-      <c r="B171" s="9" t="inlineStr">
-        <is>
-          <t>Normalised tax rate</t>
-        </is>
-      </c>
-      <c r="C171" s="17">
-        <f>C35</f>
-        <v/>
-      </c>
-      <c r="D171" s="17">
-        <f>D35</f>
-        <v/>
-      </c>
-      <c r="E171" s="17">
-        <f>E35</f>
-        <v/>
-      </c>
-      <c r="F171" s="17">
-        <f>F35</f>
-        <v/>
-      </c>
-      <c r="G171" s="17">
-        <f>G35</f>
-        <v/>
-      </c>
+      <c r="C171" s="18" t="n"/>
+      <c r="D171" s="18" t="n"/>
+      <c r="E171" s="18" t="n"/>
+      <c r="F171" s="18" t="n"/>
+      <c r="G171" s="18" t="n"/>
+      <c r="H171" s="18" t="n"/>
+      <c r="I171" s="18" t="n"/>
     </row>
     <row r="172">
       <c r="B172" s="9" t="inlineStr">
         <is>
-          <t>NOPAT = EBIT × (1 − tax rate)</t>
+          <t>Operating earnings (EBIT)</t>
         </is>
       </c>
       <c r="C172" s="13">
-        <f>C170*(1-C171)</f>
+        <f>C31+C18</f>
         <v/>
       </c>
       <c r="D172" s="13">
-        <f>D170*(1-D171)</f>
+        <f>D31+D18</f>
         <v/>
       </c>
       <c r="E172" s="13">
-        <f>E170*(1-E171)</f>
+        <f>E31+E18</f>
         <v/>
       </c>
       <c r="F172" s="13">
-        <f>F170*(1-F171)</f>
+        <f>F31+F18</f>
         <v/>
       </c>
       <c r="G172" s="13">
-        <f>G170*(1-G171)</f>
+        <f>G31+G18</f>
         <v/>
       </c>
     </row>
     <row r="173">
       <c r="B173" s="9" t="inlineStr">
         <is>
-          <t>Invested capital (Equity + Net debt)</t>
-        </is>
-      </c>
-      <c r="C173" s="13">
-        <f>C174+C175</f>
-        <v/>
-      </c>
-      <c r="D173" s="13">
-        <f>D174+D175</f>
-        <v/>
-      </c>
-      <c r="E173" s="13">
-        <f>E174+E175</f>
-        <v/>
-      </c>
-      <c r="F173" s="13">
-        <f>F174+F175</f>
-        <v/>
-      </c>
-      <c r="G173" s="13">
-        <f>G174+G175</f>
+          <t>Normalised tax rate</t>
+        </is>
+      </c>
+      <c r="C173" s="17">
+        <f>C35</f>
+        <v/>
+      </c>
+      <c r="D173" s="17">
+        <f>D35</f>
+        <v/>
+      </c>
+      <c r="E173" s="17">
+        <f>E35</f>
+        <v/>
+      </c>
+      <c r="F173" s="17">
+        <f>F35</f>
+        <v/>
+      </c>
+      <c r="G173" s="17">
+        <f>G35</f>
         <v/>
       </c>
     </row>
     <row r="174">
       <c r="B174" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Total equity</t>
+          <t>NOPAT = EBIT × (1 − tax rate)</t>
         </is>
       </c>
       <c r="C174" s="13">
-        <f>C111</f>
+        <f>C172*(1-C173)</f>
         <v/>
       </c>
       <c r="D174" s="13">
-        <f>D111</f>
+        <f>D172*(1-D173)</f>
         <v/>
       </c>
       <c r="E174" s="13">
-        <f>E111</f>
+        <f>E172*(1-E173)</f>
         <v/>
       </c>
       <c r="F174" s="13">
-        <f>F111</f>
+        <f>F172*(1-F173)</f>
         <v/>
       </c>
       <c r="G174" s="13">
-        <f>G111</f>
+        <f>G172*(1-G173)</f>
         <v/>
       </c>
     </row>
     <row r="175">
       <c r="B175" s="9" t="inlineStr">
         <is>
+          <t>Invested capital (Equity + Net debt)</t>
+        </is>
+      </c>
+      <c r="C175" s="13">
+        <f>C176+C177</f>
+        <v/>
+      </c>
+      <c r="D175" s="13">
+        <f>D176+D177</f>
+        <v/>
+      </c>
+      <c r="E175" s="13">
+        <f>E176+E177</f>
+        <v/>
+      </c>
+      <c r="F175" s="13">
+        <f>F176+F177</f>
+        <v/>
+      </c>
+      <c r="G175" s="13">
+        <f>G176+G177</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Total equity</t>
+        </is>
+      </c>
+      <c r="C176" s="13">
+        <f>C113</f>
+        <v/>
+      </c>
+      <c r="D176" s="13">
+        <f>D113</f>
+        <v/>
+      </c>
+      <c r="E176" s="13">
+        <f>E113</f>
+        <v/>
+      </c>
+      <c r="F176" s="13">
+        <f>F113</f>
+        <v/>
+      </c>
+      <c r="G176" s="13">
+        <f>G113</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Net debt (bank loan − cash)</t>
         </is>
       </c>
-      <c r="C175" s="13">
-        <f>C99-C88</f>
-        <v/>
-      </c>
-      <c r="D175" s="13">
-        <f>D99-D88</f>
-        <v/>
-      </c>
-      <c r="E175" s="13">
-        <f>E99-E88</f>
-        <v/>
-      </c>
-      <c r="F175" s="13">
-        <f>F99-F88</f>
-        <v/>
-      </c>
-      <c r="G175" s="13">
-        <f>G99-G88</f>
-        <v/>
-      </c>
-    </row>
-    <row r="176">
-      <c r="B176" s="14" t="inlineStr">
+      <c r="C177" s="13">
+        <f>C101-C90</f>
+        <v/>
+      </c>
+      <c r="D177" s="13">
+        <f>D101-D90</f>
+        <v/>
+      </c>
+      <c r="E177" s="13">
+        <f>E101-E90</f>
+        <v/>
+      </c>
+      <c r="F177" s="13">
+        <f>F101-F90</f>
+        <v/>
+      </c>
+      <c r="G177" s="13">
+        <f>G101-G90</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" s="14" t="inlineStr">
         <is>
           <t>ROIC = NOPAT / Invested capital</t>
         </is>
       </c>
-      <c r="C176" s="27">
-        <f>IFERROR(C172/C173,0)</f>
-        <v/>
-      </c>
-      <c r="D176" s="27">
-        <f>IFERROR(D172/D173,0)</f>
-        <v/>
-      </c>
-      <c r="E176" s="27">
-        <f>IFERROR(E172/E173,0)</f>
-        <v/>
-      </c>
-      <c r="F176" s="27">
-        <f>IFERROR(F172/F173,0)</f>
-        <v/>
-      </c>
-      <c r="G176" s="27">
-        <f>IFERROR(G172/G173,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="177">
-      <c r="B177" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Operating margin</t>
-        </is>
-      </c>
-      <c r="C177" s="17">
-        <f>IFERROR(C170/C9,0)</f>
-        <v/>
-      </c>
-      <c r="D177" s="17">
-        <f>IFERROR(D170/D9,0)</f>
-        <v/>
-      </c>
-      <c r="E177" s="17">
-        <f>IFERROR(E170/E9,0)</f>
-        <v/>
-      </c>
-      <c r="F177" s="17">
-        <f>IFERROR(F170/F9,0)</f>
-        <v/>
-      </c>
-      <c r="G177" s="17">
-        <f>IFERROR(G170/G9,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="178">
-      <c r="B178" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Capital turnover (Sales / IC)</t>
-        </is>
-      </c>
-      <c r="C178" s="26">
-        <f>IFERROR(C9/C173,0)</f>
-        <v/>
-      </c>
-      <c r="D178" s="26">
-        <f>IFERROR(D9/D173,0)</f>
-        <v/>
-      </c>
-      <c r="E178" s="26">
-        <f>IFERROR(E9/E173,0)</f>
-        <v/>
-      </c>
-      <c r="F178" s="26">
-        <f>IFERROR(F9/F173,0)</f>
-        <v/>
-      </c>
-      <c r="G178" s="26">
-        <f>IFERROR(G9/G173,0)</f>
+      <c r="C178" s="27">
+        <f>IFERROR(C174/C175,0)</f>
+        <v/>
+      </c>
+      <c r="D178" s="27">
+        <f>IFERROR(D174/D175,0)</f>
+        <v/>
+      </c>
+      <c r="E178" s="27">
+        <f>IFERROR(E174/E175,0)</f>
+        <v/>
+      </c>
+      <c r="F178" s="27">
+        <f>IFERROR(F174/F175,0)</f>
+        <v/>
+      </c>
+      <c r="G178" s="27">
+        <f>IFERROR(G174/G175,0)</f>
         <v/>
       </c>
     </row>
     <row r="179">
       <c r="B179" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Tax burden (1 − tax rate)</t>
+          <t xml:space="preserve">  Operating margin</t>
         </is>
       </c>
       <c r="C179" s="17">
-        <f>1-C171</f>
+        <f>IFERROR(C172/C9,0)</f>
         <v/>
       </c>
       <c r="D179" s="17">
-        <f>1-D171</f>
+        <f>IFERROR(D172/D9,0)</f>
         <v/>
       </c>
       <c r="E179" s="17">
-        <f>1-E171</f>
+        <f>IFERROR(E172/E9,0)</f>
         <v/>
       </c>
       <c r="F179" s="17">
-        <f>1-F171</f>
+        <f>IFERROR(F172/F9,0)</f>
         <v/>
       </c>
       <c r="G179" s="17">
-        <f>1-G171</f>
+        <f>IFERROR(G172/G9,0)</f>
         <v/>
       </c>
     </row>
     <row r="180">
       <c r="B180" s="16" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Capital turnover (Sales / IC)</t>
+        </is>
+      </c>
+      <c r="C180" s="26">
+        <f>IFERROR(C9/C175,0)</f>
+        <v/>
+      </c>
+      <c r="D180" s="26">
+        <f>IFERROR(D9/D175,0)</f>
+        <v/>
+      </c>
+      <c r="E180" s="26">
+        <f>IFERROR(E9/E175,0)</f>
+        <v/>
+      </c>
+      <c r="F180" s="26">
+        <f>IFERROR(F9/F175,0)</f>
+        <v/>
+      </c>
+      <c r="G180" s="26">
+        <f>IFERROR(G9/G175,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Tax burden (1 − tax rate)</t>
+        </is>
+      </c>
+      <c r="C181" s="17">
+        <f>1-C173</f>
+        <v/>
+      </c>
+      <c r="D181" s="17">
+        <f>1-D173</f>
+        <v/>
+      </c>
+      <c r="E181" s="17">
+        <f>1-E173</f>
+        <v/>
+      </c>
+      <c r="F181" s="17">
+        <f>1-F173</f>
+        <v/>
+      </c>
+      <c r="G181" s="17">
+        <f>1-G173</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" s="16" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Check: Margin × Turnover × Tax burden</t>
         </is>
       </c>
-      <c r="C180" s="17">
-        <f>C177*C178*C179</f>
-        <v/>
-      </c>
-      <c r="D180" s="17">
-        <f>D177*D178*D179</f>
-        <v/>
-      </c>
-      <c r="E180" s="17">
-        <f>E177*E178*E179</f>
-        <v/>
-      </c>
-      <c r="F180" s="17">
-        <f>F177*F178*F179</f>
-        <v/>
-      </c>
-      <c r="G180" s="17">
-        <f>G177*G178*G179</f>
-        <v/>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="18" t="n"/>
-      <c r="B181" s="18" t="inlineStr">
+      <c r="C182" s="17">
+        <f>C179*C180*C181</f>
+        <v/>
+      </c>
+      <c r="D182" s="17">
+        <f>D179*D180*D181</f>
+        <v/>
+      </c>
+      <c r="E182" s="17">
+        <f>E179*E180*E181</f>
+        <v/>
+      </c>
+      <c r="F182" s="17">
+        <f>F179*F180*F181</f>
+        <v/>
+      </c>
+      <c r="G182" s="17">
+        <f>G179*G180*G181</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="18" t="n"/>
+      <c r="B183" s="18" t="inlineStr">
         <is>
           <t>RONTA decomposition</t>
         </is>
       </c>
-      <c r="C181" s="18" t="n"/>
-      <c r="D181" s="18" t="n"/>
-      <c r="E181" s="18" t="n"/>
-      <c r="F181" s="18" t="n"/>
-      <c r="G181" s="18" t="n"/>
-      <c r="H181" s="18" t="n"/>
-      <c r="I181" s="18" t="n"/>
-    </row>
-    <row r="182">
-      <c r="B182" s="9" t="inlineStr">
+      <c r="C183" s="18" t="n"/>
+      <c r="D183" s="18" t="n"/>
+      <c r="E183" s="18" t="n"/>
+      <c r="F183" s="18" t="n"/>
+      <c r="G183" s="18" t="n"/>
+      <c r="H183" s="18" t="n"/>
+      <c r="I183" s="18" t="n"/>
+    </row>
+    <row r="184">
+      <c r="B184" s="9" t="inlineStr">
         <is>
           <t>EBIT before special items</t>
         </is>
       </c>
-      <c r="C182" s="13">
-        <f>C170</f>
-        <v/>
-      </c>
-      <c r="D182" s="13">
-        <f>D170</f>
-        <v/>
-      </c>
-      <c r="E182" s="13">
-        <f>E170</f>
-        <v/>
-      </c>
-      <c r="F182" s="13">
-        <f>F170</f>
-        <v/>
-      </c>
-      <c r="G182" s="13">
-        <f>G170</f>
-        <v/>
-      </c>
-    </row>
-    <row r="183">
-      <c r="B183" s="9" t="inlineStr">
-        <is>
-          <t>NOPAT = EBIT × (1 − tax rate)</t>
-        </is>
-      </c>
-      <c r="C183" s="13">
-        <f>C182*(1-C171)</f>
-        <v/>
-      </c>
-      <c r="D183" s="13">
-        <f>D182*(1-D171)</f>
-        <v/>
-      </c>
-      <c r="E183" s="13">
-        <f>E182*(1-E171)</f>
-        <v/>
-      </c>
-      <c r="F183" s="13">
-        <f>F182*(1-F171)</f>
-        <v/>
-      </c>
-      <c r="G183" s="13">
-        <f>G182*(1-G171)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="184">
-      <c r="B184" s="28" t="inlineStr">
-        <is>
-          <t>Net tangible assets (NTA):</t>
-        </is>
+      <c r="C184" s="13">
+        <f>C172</f>
+        <v/>
+      </c>
+      <c r="D184" s="13">
+        <f>D172</f>
+        <v/>
+      </c>
+      <c r="E184" s="13">
+        <f>E172</f>
+        <v/>
+      </c>
+      <c r="F184" s="13">
+        <f>F172</f>
+        <v/>
+      </c>
+      <c r="G184" s="13">
+        <f>G172</f>
+        <v/>
       </c>
     </row>
     <row r="185">
       <c r="B185" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Total assets</t>
+          <t>NOPAT = EBIT × (1 − tax rate)</t>
         </is>
       </c>
       <c r="C185" s="13">
-        <f>C96</f>
+        <f>C184*(1-C173)</f>
         <v/>
       </c>
       <c r="D185" s="13">
-        <f>D96</f>
+        <f>D184*(1-D173)</f>
         <v/>
       </c>
       <c r="E185" s="13">
-        <f>E96</f>
+        <f>E184*(1-E173)</f>
         <v/>
       </c>
       <c r="F185" s="13">
-        <f>F96</f>
+        <f>F184*(1-F173)</f>
         <v/>
       </c>
       <c r="G185" s="13">
-        <f>G96</f>
+        <f>G184*(1-G173)</f>
         <v/>
       </c>
     </row>
     <row r="186">
-      <c r="B186" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  − Intangible assets (none)</t>
-        </is>
-      </c>
-      <c r="C186" s="13">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D186" s="13">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E186" s="13">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F186" s="13">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G186" s="13">
-        <f>0</f>
-        <v/>
+      <c r="B186" s="28" t="inlineStr">
+        <is>
+          <t>Net tangible assets (NTA):</t>
+        </is>
       </c>
     </row>
     <row r="187">
       <c r="B187" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  − Non-interest-bearing current liabilities</t>
+          <t xml:space="preserve">  Total assets</t>
         </is>
       </c>
       <c r="C187" s="13">
-        <f>-(C105-C99)</f>
+        <f>C98</f>
         <v/>
       </c>
       <c r="D187" s="13">
-        <f>-(D105-D99)</f>
+        <f>D98</f>
         <v/>
       </c>
       <c r="E187" s="13">
-        <f>-(E105-E99)</f>
+        <f>E98</f>
         <v/>
       </c>
       <c r="F187" s="13">
-        <f>-(F105-F99)</f>
+        <f>F98</f>
         <v/>
       </c>
       <c r="G187" s="13">
-        <f>-(G105-G99)</f>
-        <v/>
-      </c>
-      <c r="I187" s="12" t="inlineStr">
-        <is>
-          <t>Current liabilities excluding the interest-bearing bank loan.</t>
-        </is>
+        <f>G98</f>
+        <v/>
       </c>
     </row>
     <row r="188">
       <c r="B188" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">  − Intangible assets (none)</t>
+        </is>
+      </c>
+      <c r="C188" s="13">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D188" s="13">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E188" s="13">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F188" s="13">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G188" s="13">
+        <f>0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  − Non-interest-bearing current liabilities</t>
+        </is>
+      </c>
+      <c r="C189" s="13">
+        <f>-(C107-C101)</f>
+        <v/>
+      </c>
+      <c r="D189" s="13">
+        <f>-(D107-D101)</f>
+        <v/>
+      </c>
+      <c r="E189" s="13">
+        <f>-(E107-E101)</f>
+        <v/>
+      </c>
+      <c r="F189" s="13">
+        <f>-(F107-F101)</f>
+        <v/>
+      </c>
+      <c r="G189" s="13">
+        <f>-(G107-G101)</f>
+        <v/>
+      </c>
+      <c r="I189" s="12" t="inlineStr">
+        <is>
+          <t>Current liabilities excluding the interest-bearing bank loan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">  − Cash</t>
         </is>
       </c>
-      <c r="C188" s="13">
-        <f>-C88</f>
-        <v/>
-      </c>
-      <c r="D188" s="13">
-        <f>-D88</f>
-        <v/>
-      </c>
-      <c r="E188" s="13">
-        <f>-E88</f>
-        <v/>
-      </c>
-      <c r="F188" s="13">
-        <f>-F88</f>
-        <v/>
-      </c>
-      <c r="G188" s="13">
-        <f>-G88</f>
-        <v/>
-      </c>
-    </row>
-    <row r="189">
-      <c r="B189" s="14" t="inlineStr">
+      <c r="C190" s="13">
+        <f>-C90</f>
+        <v/>
+      </c>
+      <c r="D190" s="13">
+        <f>-D90</f>
+        <v/>
+      </c>
+      <c r="E190" s="13">
+        <f>-E90</f>
+        <v/>
+      </c>
+      <c r="F190" s="13">
+        <f>-F90</f>
+        <v/>
+      </c>
+      <c r="G190" s="13">
+        <f>-G90</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  = Net tangible assets</t>
         </is>
       </c>
-      <c r="C189" s="15">
-        <f>C185+C186+C187+C188</f>
-        <v/>
-      </c>
-      <c r="D189" s="15">
-        <f>D185+D186+D187+D188</f>
-        <v/>
-      </c>
-      <c r="E189" s="15">
-        <f>E185+E186+E187+E188</f>
-        <v/>
-      </c>
-      <c r="F189" s="15">
-        <f>F185+F186+F187+F188</f>
-        <v/>
-      </c>
-      <c r="G189" s="15">
-        <f>G185+G186+G187+G188</f>
-        <v/>
-      </c>
-    </row>
-    <row r="190">
-      <c r="B190" s="28" t="inlineStr">
+      <c r="C191" s="15">
+        <f>C187+C188+C189+C190</f>
+        <v/>
+      </c>
+      <c r="D191" s="15">
+        <f>D187+D188+D189+D190</f>
+        <v/>
+      </c>
+      <c r="E191" s="15">
+        <f>E187+E188+E189+E190</f>
+        <v/>
+      </c>
+      <c r="F191" s="15">
+        <f>F187+F188+F189+F190</f>
+        <v/>
+      </c>
+      <c r="G191" s="15">
+        <f>G187+G188+G189+G190</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" s="28" t="inlineStr">
         <is>
           <t>RONTA = NOPAT / NTA</t>
         </is>
       </c>
-      <c r="C190" s="22">
-        <f>IFERROR(C183/C189,0)</f>
-        <v/>
-      </c>
-      <c r="D190" s="22">
-        <f>IFERROR(D183/D189,0)</f>
-        <v/>
-      </c>
-      <c r="E190" s="22">
-        <f>IFERROR(E183/E189,0)</f>
-        <v/>
-      </c>
-      <c r="F190" s="22">
-        <f>IFERROR(F183/F189,0)</f>
-        <v/>
-      </c>
-      <c r="G190" s="22">
-        <f>IFERROR(G183/G189,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="18" t="n"/>
-      <c r="B191" s="18" t="inlineStr">
+      <c r="C192" s="22">
+        <f>IFERROR(C185/C191,0)</f>
+        <v/>
+      </c>
+      <c r="D192" s="22">
+        <f>IFERROR(D185/D191,0)</f>
+        <v/>
+      </c>
+      <c r="E192" s="22">
+        <f>IFERROR(E185/E191,0)</f>
+        <v/>
+      </c>
+      <c r="F192" s="22">
+        <f>IFERROR(F185/F191,0)</f>
+        <v/>
+      </c>
+      <c r="G192" s="22">
+        <f>IFERROR(G185/G191,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="18" t="n"/>
+      <c r="B193" s="18" t="inlineStr">
         <is>
           <t>Return on Equity (ROE)</t>
         </is>
       </c>
-      <c r="C191" s="18" t="n"/>
-      <c r="D191" s="18" t="n"/>
-      <c r="E191" s="18" t="n"/>
-      <c r="F191" s="18" t="n"/>
-      <c r="G191" s="18" t="n"/>
-      <c r="H191" s="18" t="n"/>
-      <c r="I191" s="18" t="n"/>
-    </row>
-    <row r="192">
-      <c r="B192" s="9" t="inlineStr">
+      <c r="C193" s="18" t="n"/>
+      <c r="D193" s="18" t="n"/>
+      <c r="E193" s="18" t="n"/>
+      <c r="F193" s="18" t="n"/>
+      <c r="G193" s="18" t="n"/>
+      <c r="H193" s="18" t="n"/>
+      <c r="I193" s="18" t="n"/>
+    </row>
+    <row r="194">
+      <c r="B194" s="9" t="inlineStr">
         <is>
           <t>Net income (profit for the year)</t>
         </is>
       </c>
-      <c r="C192" s="13">
+      <c r="C194" s="13">
         <f>C36</f>
         <v/>
       </c>
-      <c r="D192" s="13">
+      <c r="D194" s="13">
         <f>D36</f>
         <v/>
       </c>
-      <c r="E192" s="13">
+      <c r="E194" s="13">
         <f>E36</f>
         <v/>
       </c>
-      <c r="F192" s="13">
+      <c r="F194" s="13">
         <f>F36</f>
         <v/>
       </c>
-      <c r="G192" s="13">
+      <c r="G194" s="13">
         <f>G36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="193">
-      <c r="B193" s="9" t="inlineStr">
-        <is>
-          <t>Total equity</t>
-        </is>
-      </c>
-      <c r="C193" s="13">
-        <f>C111</f>
-        <v/>
-      </c>
-      <c r="D193" s="13">
-        <f>D111</f>
-        <v/>
-      </c>
-      <c r="E193" s="13">
-        <f>E111</f>
-        <v/>
-      </c>
-      <c r="F193" s="13">
-        <f>F111</f>
-        <v/>
-      </c>
-      <c r="G193" s="13">
-        <f>G111</f>
-        <v/>
-      </c>
-    </row>
-    <row r="194">
-      <c r="B194" s="28" t="inlineStr">
-        <is>
-          <t>ROE = Net income / Equity</t>
-        </is>
-      </c>
-      <c r="C194" s="22">
-        <f>IFERROR(C192/C193,0)</f>
-        <v/>
-      </c>
-      <c r="D194" s="22">
-        <f>IFERROR(D192/D193,0)</f>
-        <v/>
-      </c>
-      <c r="E194" s="22">
-        <f>IFERROR(E192/E193,0)</f>
-        <v/>
-      </c>
-      <c r="F194" s="22">
-        <f>IFERROR(F192/F193,0)</f>
-        <v/>
-      </c>
-      <c r="G194" s="22">
-        <f>IFERROR(G192/G193,0)</f>
         <v/>
       </c>
     </row>
     <row r="195">
       <c r="B195" s="9" t="inlineStr">
         <is>
-          <t>Return on assets (NI / total assets)</t>
-        </is>
-      </c>
-      <c r="C195" s="17">
-        <f>IFERROR(C36/C96,0)</f>
-        <v/>
-      </c>
-      <c r="D195" s="17">
-        <f>IFERROR(D36/D96,0)</f>
-        <v/>
-      </c>
-      <c r="E195" s="17">
-        <f>IFERROR(E36/E96,0)</f>
-        <v/>
-      </c>
-      <c r="F195" s="17">
-        <f>IFERROR(F36/F96,0)</f>
-        <v/>
-      </c>
-      <c r="G195" s="17">
-        <f>IFERROR(G36/G96,0)</f>
+          <t>Total equity</t>
+        </is>
+      </c>
+      <c r="C195" s="13">
+        <f>C113</f>
+        <v/>
+      </c>
+      <c r="D195" s="13">
+        <f>D113</f>
+        <v/>
+      </c>
+      <c r="E195" s="13">
+        <f>E113</f>
+        <v/>
+      </c>
+      <c r="F195" s="13">
+        <f>F113</f>
+        <v/>
+      </c>
+      <c r="G195" s="13">
+        <f>G113</f>
         <v/>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="18" t="n"/>
-      <c r="B196" s="18" t="inlineStr">
-        <is>
-          <t>Leverage</t>
-        </is>
-      </c>
-      <c r="C196" s="18" t="n"/>
-      <c r="D196" s="18" t="n"/>
-      <c r="E196" s="18" t="n"/>
-      <c r="F196" s="18" t="n"/>
-      <c r="G196" s="18" t="n"/>
-      <c r="H196" s="18" t="n"/>
-      <c r="I196" s="18" t="n"/>
+      <c r="B196" s="28" t="inlineStr">
+        <is>
+          <t>ROE = Net income / Equity</t>
+        </is>
+      </c>
+      <c r="C196" s="22">
+        <f>IFERROR(C194/C195,0)</f>
+        <v/>
+      </c>
+      <c r="D196" s="22">
+        <f>IFERROR(D194/D195,0)</f>
+        <v/>
+      </c>
+      <c r="E196" s="22">
+        <f>IFERROR(E194/E195,0)</f>
+        <v/>
+      </c>
+      <c r="F196" s="22">
+        <f>IFERROR(F194/F195,0)</f>
+        <v/>
+      </c>
+      <c r="G196" s="22">
+        <f>IFERROR(G194/G195,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="B197" s="9" t="inlineStr">
         <is>
-          <t>Net debt (bank loan − cash)</t>
-        </is>
-      </c>
-      <c r="C197" s="13">
-        <f>C99-C88</f>
-        <v/>
-      </c>
-      <c r="D197" s="13">
-        <f>D99-D88</f>
-        <v/>
-      </c>
-      <c r="E197" s="13">
-        <f>E99-E88</f>
-        <v/>
-      </c>
-      <c r="F197" s="13">
-        <f>F99-F88</f>
-        <v/>
-      </c>
-      <c r="G197" s="13">
-        <f>G99-G88</f>
+          <t>Return on assets (NI / total assets)</t>
+        </is>
+      </c>
+      <c r="C197" s="17">
+        <f>IFERROR(C36/C98,0)</f>
+        <v/>
+      </c>
+      <c r="D197" s="17">
+        <f>IFERROR(D36/D98,0)</f>
+        <v/>
+      </c>
+      <c r="E197" s="17">
+        <f>IFERROR(E36/E98,0)</f>
+        <v/>
+      </c>
+      <c r="F197" s="17">
+        <f>IFERROR(F36/F98,0)</f>
+        <v/>
+      </c>
+      <c r="G197" s="17">
+        <f>IFERROR(G36/G98,0)</f>
         <v/>
       </c>
     </row>
     <row r="198">
-      <c r="B198" s="9" t="inlineStr">
-        <is>
-          <t>EBITDA (Operating earnings + D&amp;A)</t>
-        </is>
-      </c>
-      <c r="C198" s="13">
-        <f>C170+C19+C82</f>
-        <v/>
-      </c>
-      <c r="D198" s="13">
-        <f>D170+D19+D82</f>
-        <v/>
-      </c>
-      <c r="E198" s="13">
-        <f>E170+E19+E82</f>
-        <v/>
-      </c>
-      <c r="F198" s="13">
-        <f>F170+F19+F82</f>
-        <v/>
-      </c>
-      <c r="G198" s="13">
-        <f>G170+G19+G82</f>
-        <v/>
-      </c>
+      <c r="A198" s="18" t="n"/>
+      <c r="B198" s="18" t="inlineStr">
+        <is>
+          <t>Leverage</t>
+        </is>
+      </c>
+      <c r="C198" s="18" t="n"/>
+      <c r="D198" s="18" t="n"/>
+      <c r="E198" s="18" t="n"/>
+      <c r="F198" s="18" t="n"/>
+      <c r="G198" s="18" t="n"/>
+      <c r="H198" s="18" t="n"/>
+      <c r="I198" s="18" t="n"/>
     </row>
     <row r="199">
       <c r="B199" s="9" t="inlineStr">
         <is>
-          <t>Net debt / EBITDA  (x)</t>
-        </is>
-      </c>
-      <c r="C199" s="26">
-        <f>IFERROR(C197/C198,"")</f>
-        <v/>
-      </c>
-      <c r="D199" s="26">
-        <f>IFERROR(D197/D198,"")</f>
-        <v/>
-      </c>
-      <c r="E199" s="26">
-        <f>IFERROR(E197/E198,"")</f>
-        <v/>
-      </c>
-      <c r="F199" s="26">
-        <f>IFERROR(F197/F198,"")</f>
-        <v/>
-      </c>
-      <c r="G199" s="26">
-        <f>IFERROR(G197/G198,"")</f>
+          <t>Net debt (bank loan − cash)</t>
+        </is>
+      </c>
+      <c r="C199" s="13">
+        <f>C101-C90</f>
+        <v/>
+      </c>
+      <c r="D199" s="13">
+        <f>D101-D90</f>
+        <v/>
+      </c>
+      <c r="E199" s="13">
+        <f>E101-E90</f>
+        <v/>
+      </c>
+      <c r="F199" s="13">
+        <f>F101-F90</f>
+        <v/>
+      </c>
+      <c r="G199" s="13">
+        <f>G101-G90</f>
         <v/>
       </c>
     </row>
     <row r="200">
       <c r="B200" s="9" t="inlineStr">
         <is>
-          <t>Interest coverage (EBIT / interest expense)</t>
-        </is>
-      </c>
-      <c r="C200" s="26">
-        <f>IFERROR(C170/C18,"")</f>
-        <v/>
-      </c>
-      <c r="D200" s="26">
-        <f>IFERROR(D170/D18,"")</f>
-        <v/>
-      </c>
-      <c r="E200" s="26">
-        <f>IFERROR(E170/E18,"")</f>
-        <v/>
-      </c>
-      <c r="F200" s="26">
-        <f>IFERROR(F170/F18,"")</f>
-        <v/>
-      </c>
-      <c r="G200" s="26">
-        <f>IFERROR(G170/G18,"")</f>
+          <t>EBITDA (Operating earnings + D&amp;A)</t>
+        </is>
+      </c>
+      <c r="C200" s="13">
+        <f>C172+C19+C84</f>
+        <v/>
+      </c>
+      <c r="D200" s="13">
+        <f>D172+D19+D84</f>
+        <v/>
+      </c>
+      <c r="E200" s="13">
+        <f>E172+E19+E84</f>
+        <v/>
+      </c>
+      <c r="F200" s="13">
+        <f>F172+F19+F84</f>
+        <v/>
+      </c>
+      <c r="G200" s="13">
+        <f>G172+G19+G84</f>
         <v/>
       </c>
     </row>
     <row r="201">
       <c r="B201" s="9" t="inlineStr">
         <is>
-          <t>Debt / equity (bank loan / equity)</t>
+          <t>Net debt / EBITDA  (x)</t>
         </is>
       </c>
       <c r="C201" s="26">
-        <f>IFERROR(C99/C111,0)</f>
+        <f>IFERROR(C199/C200,"")</f>
         <v/>
       </c>
       <c r="D201" s="26">
-        <f>IFERROR(D99/D111,0)</f>
+        <f>IFERROR(D199/D200,"")</f>
         <v/>
       </c>
       <c r="E201" s="26">
-        <f>IFERROR(E99/E111,0)</f>
+        <f>IFERROR(E199/E200,"")</f>
         <v/>
       </c>
       <c r="F201" s="26">
-        <f>IFERROR(F99/F111,0)</f>
+        <f>IFERROR(F199/F200,"")</f>
         <v/>
       </c>
       <c r="G201" s="26">
-        <f>IFERROR(G99/G111,0)</f>
+        <f>IFERROR(G199/G200,"")</f>
         <v/>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="18" t="n"/>
-      <c r="B202" s="18" t="inlineStr">
-        <is>
-          <t>Liquidity &amp; working capital</t>
-        </is>
-      </c>
-      <c r="C202" s="18" t="n"/>
-      <c r="D202" s="18" t="n"/>
-      <c r="E202" s="18" t="n"/>
-      <c r="F202" s="18" t="n"/>
-      <c r="G202" s="18" t="n"/>
-      <c r="H202" s="18" t="n"/>
-      <c r="I202" s="18" t="n"/>
+      <c r="B202" s="9" t="inlineStr">
+        <is>
+          <t>Interest coverage (EBIT / interest expense)</t>
+        </is>
+      </c>
+      <c r="C202" s="26">
+        <f>IFERROR(C172/C18,"")</f>
+        <v/>
+      </c>
+      <c r="D202" s="26">
+        <f>IFERROR(D172/D18,"")</f>
+        <v/>
+      </c>
+      <c r="E202" s="26">
+        <f>IFERROR(E172/E18,"")</f>
+        <v/>
+      </c>
+      <c r="F202" s="26">
+        <f>IFERROR(F172/F18,"")</f>
+        <v/>
+      </c>
+      <c r="G202" s="26">
+        <f>IFERROR(G172/G18,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="B203" s="9" t="inlineStr">
         <is>
-          <t>Current ratio (CA / CL)</t>
+          <t>Debt / equity (bank loan / equity)</t>
         </is>
       </c>
       <c r="C203" s="26">
-        <f>IFERROR(C93/C105,"")</f>
+        <f>IFERROR(C101/C113,0)</f>
         <v/>
       </c>
       <c r="D203" s="26">
-        <f>IFERROR(D93/D105,"")</f>
+        <f>IFERROR(D101/D113,0)</f>
         <v/>
       </c>
       <c r="E203" s="26">
-        <f>IFERROR(E93/E105,"")</f>
+        <f>IFERROR(E101/E113,0)</f>
         <v/>
       </c>
       <c r="F203" s="26">
-        <f>IFERROR(F93/F105,"")</f>
+        <f>IFERROR(F101/F113,0)</f>
         <v/>
       </c>
       <c r="G203" s="26">
-        <f>IFERROR(G93/G105,"")</f>
+        <f>IFERROR(G101/G113,0)</f>
         <v/>
       </c>
     </row>
     <row r="204">
-      <c r="B204" s="9" t="inlineStr">
-        <is>
-          <t>Quick ratio ((cash + A/R) / CL)</t>
-        </is>
-      </c>
-      <c r="C204" s="26">
-        <f>IFERROR((C88+C89)/C105,"")</f>
-        <v/>
-      </c>
-      <c r="D204" s="26">
-        <f>IFERROR((D88+D89)/D105,"")</f>
-        <v/>
-      </c>
-      <c r="E204" s="26">
-        <f>IFERROR((E88+E89)/E105,"")</f>
-        <v/>
-      </c>
-      <c r="F204" s="26">
-        <f>IFERROR((F88+F89)/F105,"")</f>
-        <v/>
-      </c>
-      <c r="G204" s="26">
-        <f>IFERROR((G88+G89)/G105,"")</f>
-        <v/>
-      </c>
+      <c r="A204" s="18" t="n"/>
+      <c r="B204" s="18" t="inlineStr">
+        <is>
+          <t>Liquidity &amp; working capital</t>
+        </is>
+      </c>
+      <c r="C204" s="18" t="n"/>
+      <c r="D204" s="18" t="n"/>
+      <c r="E204" s="18" t="n"/>
+      <c r="F204" s="18" t="n"/>
+      <c r="G204" s="18" t="n"/>
+      <c r="H204" s="18" t="n"/>
+      <c r="I204" s="18" t="n"/>
     </row>
     <row r="205">
       <c r="B205" s="9" t="inlineStr">
         <is>
-          <t>DSO (A/R / revenue × 365)</t>
-        </is>
-      </c>
-      <c r="C205" s="29">
-        <f>IFERROR(C89/C9*365,"")</f>
-        <v/>
-      </c>
-      <c r="D205" s="29">
-        <f>IFERROR(D89/D9*365,"")</f>
-        <v/>
-      </c>
-      <c r="E205" s="29">
-        <f>IFERROR(E89/E9*365,"")</f>
-        <v/>
-      </c>
-      <c r="F205" s="29">
-        <f>IFERROR(F89/F9*365,"")</f>
-        <v/>
-      </c>
-      <c r="G205" s="29">
-        <f>IFERROR(G89/G9*365,"")</f>
+          <t>Current ratio (CA / CL)</t>
+        </is>
+      </c>
+      <c r="C205" s="26">
+        <f>IFERROR(C95/C107,"")</f>
+        <v/>
+      </c>
+      <c r="D205" s="26">
+        <f>IFERROR(D95/D107,"")</f>
+        <v/>
+      </c>
+      <c r="E205" s="26">
+        <f>IFERROR(E95/E107,"")</f>
+        <v/>
+      </c>
+      <c r="F205" s="26">
+        <f>IFERROR(F95/F107,"")</f>
+        <v/>
+      </c>
+      <c r="G205" s="26">
+        <f>IFERROR(G95/G107,"")</f>
         <v/>
       </c>
     </row>
     <row r="206">
       <c r="B206" s="9" t="inlineStr">
         <is>
+          <t>Quick ratio ((cash + A/R) / CL)</t>
+        </is>
+      </c>
+      <c r="C206" s="26">
+        <f>IFERROR((C90+C91)/C107,"")</f>
+        <v/>
+      </c>
+      <c r="D206" s="26">
+        <f>IFERROR((D90+D91)/D107,"")</f>
+        <v/>
+      </c>
+      <c r="E206" s="26">
+        <f>IFERROR((E90+E91)/E107,"")</f>
+        <v/>
+      </c>
+      <c r="F206" s="26">
+        <f>IFERROR((F90+F91)/F107,"")</f>
+        <v/>
+      </c>
+      <c r="G206" s="26">
+        <f>IFERROR((G90+G91)/G107,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" s="9" t="inlineStr">
+        <is>
+          <t>DSO (A/R / revenue × 365)</t>
+        </is>
+      </c>
+      <c r="C207" s="29">
+        <f>IFERROR(C91/C9*365,"")</f>
+        <v/>
+      </c>
+      <c r="D207" s="29">
+        <f>IFERROR(D91/D9*365,"")</f>
+        <v/>
+      </c>
+      <c r="E207" s="29">
+        <f>IFERROR(E91/E9*365,"")</f>
+        <v/>
+      </c>
+      <c r="F207" s="29">
+        <f>IFERROR(F91/F9*365,"")</f>
+        <v/>
+      </c>
+      <c r="G207" s="29">
+        <f>IFERROR(G91/G9*365,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="208">
+      <c r="B208" s="9" t="inlineStr">
+        <is>
           <t>DPO (A/P / cost of sales × 365)</t>
         </is>
       </c>
-      <c r="C206" s="29">
-        <f>IFERROR(C100/C10*365,"")</f>
-        <v/>
-      </c>
-      <c r="D206" s="29">
-        <f>IFERROR(D100/D10*365,"")</f>
-        <v/>
-      </c>
-      <c r="E206" s="29">
-        <f>IFERROR(E100/E10*365,"")</f>
-        <v/>
-      </c>
-      <c r="F206" s="29">
-        <f>IFERROR(F100/F10*365,"")</f>
-        <v/>
-      </c>
-      <c r="G206" s="29">
-        <f>IFERROR(G100/G10*365,"")</f>
+      <c r="C208" s="29">
+        <f>IFERROR(C102/C10*365,"")</f>
+        <v/>
+      </c>
+      <c r="D208" s="29">
+        <f>IFERROR(D102/D10*365,"")</f>
+        <v/>
+      </c>
+      <c r="E208" s="29">
+        <f>IFERROR(E102/E10*365,"")</f>
+        <v/>
+      </c>
+      <c r="F208" s="29">
+        <f>IFERROR(F102/F10*365,"")</f>
+        <v/>
+      </c>
+      <c r="G208" s="29">
+        <f>IFERROR(G102/G10*365,"")</f>
         <v/>
       </c>
     </row>

--- a/models/RY_Tool_3_Statement_Model.xlsx
+++ b/models/RY_Tool_3_Statement_Model.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Model" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="LBO" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +24,7 @@
     <numFmt numFmtId="167" formatCode="0.00&quot;x&quot;;(0.00&quot;x&quot;);\-"/>
     <numFmt numFmtId="168" formatCode="0&quot; days&quot;;(0);\-"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -91,8 +92,48 @@
       <color rgb="FF404040"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="FF595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="FF595959"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -112,6 +153,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCAD2C5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -140,7 +186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -210,6 +256,113 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5199,4 +5352,2016 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:L108"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="1.4" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="12.5" customWidth="1" min="3" max="3"/>
+    <col width="12.5" customWidth="1" min="4" max="4"/>
+    <col width="12.5" customWidth="1" min="5" max="5"/>
+    <col width="12.5" customWidth="1" min="6" max="6"/>
+    <col width="12.5" customWidth="1" min="7" max="7"/>
+    <col width="12.5" customWidth="1" min="8" max="8"/>
+    <col width="12.5" customWidth="1" min="9" max="9"/>
+    <col width="12.5" customWidth="1" min="10" max="10"/>
+    <col width="12.5" customWidth="1" min="11" max="11"/>
+    <col width="12.5" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="30" t="inlineStr">
+        <is>
+          <t>R. &amp; Y. Tool and Die Co. Limited — LBO / IRR Model</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="31" t="inlineStr">
+        <is>
+          <t>Owner-earnings LBO built off the FY2021–FY2025 financials (Model tab). Canadian dollars, whole $. Gold cells are toggles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="31" t="inlineStr">
+        <is>
+          <t>Interest accrues on beginning-of-year debt (no circularity). Excess free cash sweeps to debt paydown; no interim distributions, so equity is entry-in / exit-out. Base-case operating assumptions default to FY21–25 history.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="32" t="inlineStr">
+        <is>
+          <t>SCENARIO  (Base / Bull / Bear):</t>
+        </is>
+      </c>
+      <c r="C5" s="33" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="H5" s="34" t="inlineStr">
+        <is>
+          <t>SCENARIO INPUTS</t>
+        </is>
+      </c>
+      <c r="J5" s="35" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="K5" s="35" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="L5" s="35" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="H6" s="36" t="inlineStr">
+        <is>
+          <t>Revenue growth (%/yr)</t>
+        </is>
+      </c>
+      <c r="J6" s="37" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K6" s="37" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L6" s="37" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="38" t="inlineStr">
+        <is>
+          <t>ENTRY, FINANCING &amp; OPERATING ASSUMPTIONS</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>EBITDA margin (%)</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="39" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K7" s="39" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="L7" s="39" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="40" t="n"/>
+      <c r="B8" s="41" t="inlineStr">
+        <is>
+          <t>Entry (base year = FY2025)</t>
+        </is>
+      </c>
+      <c r="C8" s="40" t="n"/>
+      <c r="D8" s="40" t="n"/>
+      <c r="E8" s="40" t="n"/>
+      <c r="F8" s="40" t="n"/>
+      <c r="G8" s="40" t="n"/>
+      <c r="H8" s="18" t="inlineStr">
+        <is>
+          <t>Capex (% of revenue)</t>
+        </is>
+      </c>
+      <c r="I8" s="40" t="n"/>
+      <c r="J8" s="42" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K8" s="42" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L8" s="42" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="36" t="inlineStr">
+        <is>
+          <t>Entry LTM EBITDA (FY2025)</t>
+        </is>
+      </c>
+      <c r="C9" s="43">
+        <f>'Model'!G45</f>
+        <v/>
+      </c>
+      <c r="D9" s="44" t="inlineStr">
+        <is>
+          <t>Linked from Model — EBITDA bridge.</t>
+        </is>
+      </c>
+      <c r="H9" s="45" t="inlineStr">
+        <is>
+          <t>Historical FY21–25 anchor:</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="36" t="inlineStr">
+        <is>
+          <t>Entry LTM revenue (FY2025)</t>
+        </is>
+      </c>
+      <c r="C10" s="43">
+        <f>'Model'!G9</f>
+        <v/>
+      </c>
+      <c r="H10" s="45" t="inlineStr">
+        <is>
+          <t>rev CAGR ~10% · avg EBITDA margin ~17% · avg capex ~3–4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="36" t="inlineStr">
+        <is>
+          <t>Entry EV / EBITDA multiple  (x)</t>
+        </is>
+      </c>
+      <c r="C11" s="46" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" s="44" t="inlineStr">
+        <is>
+          <t>Purchase multiple.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="36" t="inlineStr">
+        <is>
+          <t>Enterprise value at entry</t>
+        </is>
+      </c>
+      <c r="C12" s="43">
+        <f>C9*C11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="40" t="n"/>
+      <c r="B13" s="41" t="inlineStr">
+        <is>
+          <t>Financing (toggles)</t>
+        </is>
+      </c>
+      <c r="C13" s="40" t="n"/>
+      <c r="D13" s="40" t="n"/>
+      <c r="E13" s="40" t="n"/>
+      <c r="F13" s="40" t="n"/>
+      <c r="G13" s="40" t="n"/>
+      <c r="H13" s="40" t="n"/>
+      <c r="I13" s="40" t="n"/>
+      <c r="J13" s="40" t="n"/>
+      <c r="K13" s="40" t="n"/>
+      <c r="L13" s="40" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="36" t="inlineStr">
+        <is>
+          <t>Entry leverage — Debt / EBITDA (x)</t>
+        </is>
+      </c>
+      <c r="C14" s="46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D14" s="44" t="inlineStr">
+        <is>
+          <t>DEBT toggle — turns of EBITDA financed with debt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="36" t="inlineStr">
+        <is>
+          <t>New debt raised at entry</t>
+        </is>
+      </c>
+      <c r="C15" s="43">
+        <f>C14*C9</f>
+        <v/>
+      </c>
+      <c r="D15" s="44">
+        <f> leverage × entry EBITDA.</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="36" t="inlineStr">
+        <is>
+          <t>Interest rate on debt  (%)</t>
+        </is>
+      </c>
+      <c r="C16" s="47" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D16" s="44" t="inlineStr">
+        <is>
+          <t>INTEREST toggle — accrues on opening debt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="36" t="inlineStr">
+        <is>
+          <t>Mandatory amortization (% opening debt/yr)</t>
+        </is>
+      </c>
+      <c r="C17" s="47" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="36" t="inlineStr">
+        <is>
+          <t>Cash sweep (% of FCF after mandatory)</t>
+        </is>
+      </c>
+      <c r="C18" s="47" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="36" t="inlineStr">
+        <is>
+          <t>Minimum / opening cash on balance sheet</t>
+        </is>
+      </c>
+      <c r="C19" s="48" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D19" s="44" t="inlineStr">
+        <is>
+          <t>CASH toggle — cash funded onto the B/S at close and held as a floor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="36" t="inlineStr">
+        <is>
+          <t>Transaction &amp; financing fees (% of EV)</t>
+        </is>
+      </c>
+      <c r="C20" s="47" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="40" t="n"/>
+      <c r="B21" s="41" t="inlineStr">
+        <is>
+          <t>Operating (scenario-driven; base = FY21–25 history)</t>
+        </is>
+      </c>
+      <c r="C21" s="40" t="n"/>
+      <c r="D21" s="40" t="n"/>
+      <c r="E21" s="40" t="n"/>
+      <c r="F21" s="40" t="n"/>
+      <c r="G21" s="40" t="n"/>
+      <c r="H21" s="40" t="n"/>
+      <c r="I21" s="40" t="n"/>
+      <c r="J21" s="40" t="n"/>
+      <c r="K21" s="40" t="n"/>
+      <c r="L21" s="40" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="36" t="inlineStr">
+        <is>
+          <t>Revenue growth  (%/yr)</t>
+        </is>
+      </c>
+      <c r="C22" s="49">
+        <f>INDEX($J6:$L6,MATCH($C$5,$J$5:$L$5,0))</f>
+        <v/>
+      </c>
+      <c r="D22" s="44" t="inlineStr">
+        <is>
+          <t>Driven by the scenario selector (C5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="36" t="inlineStr">
+        <is>
+          <t>EBITDA margin  (%)</t>
+        </is>
+      </c>
+      <c r="C23" s="49">
+        <f>INDEX($J7:$L7,MATCH($C$5,$J$5:$L$5,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="36" t="inlineStr">
+        <is>
+          <t>Capex  (% of revenue)</t>
+        </is>
+      </c>
+      <c r="C24" s="49">
+        <f>INDEX($J8:$L8,MATCH($C$5,$J$5:$L$5,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="36" t="inlineStr">
+        <is>
+          <t>D&amp;A  (% of revenue)</t>
+        </is>
+      </c>
+      <c r="C25" s="47" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D25" s="44" t="inlineStr">
+        <is>
+          <t>Roughly the FY25 run-rate; drives the tax shield.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="36" t="inlineStr">
+        <is>
+          <t>Cash tax rate  (%)</t>
+        </is>
+      </c>
+      <c r="C26" s="47" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D26" s="44" t="inlineStr">
+        <is>
+          <t>≈ FY25 effective rate / CDN small-business rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="36" t="inlineStr">
+        <is>
+          <t>Δ Net working capital (% of Δrevenue)</t>
+        </is>
+      </c>
+      <c r="C27" s="47" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="36" t="inlineStr">
+        <is>
+          <t>Exit year  (1–5)</t>
+        </is>
+      </c>
+      <c r="C28" s="50" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="36" t="inlineStr">
+        <is>
+          <t>Exit EV / EBITDA multiple  (x)</t>
+        </is>
+      </c>
+      <c r="C29" s="46" t="n">
+        <v>6</v>
+      </c>
+      <c r="D29" s="44" t="inlineStr">
+        <is>
+          <t>Default = entry multiple (no multiple expansion).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n"/>
+      <c r="B31" s="38" t="inlineStr">
+        <is>
+          <t>SOURCES &amp; USES OF FUNDS</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n"/>
+      <c r="L31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="40" t="n"/>
+      <c r="B32" s="41" t="inlineStr">
+        <is>
+          <t>Uses</t>
+        </is>
+      </c>
+      <c r="C32" s="40" t="n"/>
+      <c r="D32" s="40" t="n"/>
+      <c r="E32" s="40" t="n"/>
+      <c r="F32" s="40" t="n"/>
+      <c r="G32" s="40" t="n"/>
+      <c r="H32" s="40" t="n"/>
+      <c r="I32" s="40" t="n"/>
+      <c r="J32" s="40" t="n"/>
+      <c r="K32" s="40" t="n"/>
+      <c r="L32" s="40" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="36" t="inlineStr">
+        <is>
+          <t>Purchase of enterprise value</t>
+        </is>
+      </c>
+      <c r="C33" s="43">
+        <f>C12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="36" t="inlineStr">
+        <is>
+          <t>Cash funded to balance sheet</t>
+        </is>
+      </c>
+      <c r="C34" s="43">
+        <f>C19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="36" t="inlineStr">
+        <is>
+          <t>Transaction &amp; financing fees</t>
+        </is>
+      </c>
+      <c r="C35" s="43">
+        <f>C20*C12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="32" t="inlineStr">
+        <is>
+          <t>Total uses</t>
+        </is>
+      </c>
+      <c r="C36" s="51">
+        <f>SUM(C33:C35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="40" t="n"/>
+      <c r="B37" s="41" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+      <c r="C37" s="40" t="n"/>
+      <c r="D37" s="40" t="n"/>
+      <c r="E37" s="40" t="n"/>
+      <c r="F37" s="40" t="n"/>
+      <c r="G37" s="40" t="n"/>
+      <c r="H37" s="40" t="n"/>
+      <c r="I37" s="40" t="n"/>
+      <c r="J37" s="40" t="n"/>
+      <c r="K37" s="40" t="n"/>
+      <c r="L37" s="40" t="n"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="36" t="inlineStr">
+        <is>
+          <t>New debt raised</t>
+        </is>
+      </c>
+      <c r="C38" s="43">
+        <f>C15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="32" t="inlineStr">
+        <is>
+          <t>Sponsor equity (plug)</t>
+        </is>
+      </c>
+      <c r="C39" s="52">
+        <f>C36-C38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="32" t="inlineStr">
+        <is>
+          <t>Total sources</t>
+        </is>
+      </c>
+      <c r="C40" s="51">
+        <f>C38+C39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="36" t="inlineStr">
+        <is>
+          <t>Check (sources − uses)</t>
+        </is>
+      </c>
+      <c r="C41" s="43">
+        <f>C40-C36</f>
+        <v/>
+      </c>
+      <c r="D41" s="44" t="inlineStr">
+        <is>
+          <t>Must be 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="36" t="inlineStr">
+        <is>
+          <t>Entry net debt (debt − opening cash)</t>
+        </is>
+      </c>
+      <c r="C42" s="43">
+        <f>C38-C34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n"/>
+      <c r="B45" s="38" t="inlineStr">
+        <is>
+          <t>OWNER-EARNINGS PROJECTION, DEBT SCHEDULE &amp; FREE CASH FLOW</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
+      <c r="H45" s="4" t="n"/>
+      <c r="I45" s="4" t="n"/>
+      <c r="J45" s="4" t="n"/>
+      <c r="K45" s="4" t="n"/>
+      <c r="L45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="53" t="n"/>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>($)</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>FY2025  (entry)</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>FY2026E</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>FY2027E</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>FY2028E</t>
+        </is>
+      </c>
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>FY2029E</t>
+        </is>
+      </c>
+      <c r="L46" s="6" t="inlineStr">
+        <is>
+          <t>FY2030E</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="54" t="inlineStr">
+        <is>
+          <t>Hold year (0 = entry)</t>
+        </is>
+      </c>
+      <c r="G47" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="J47" s="55" t="n">
+        <v>3</v>
+      </c>
+      <c r="K47" s="55" t="n">
+        <v>4</v>
+      </c>
+      <c r="L47" s="55" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="32" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C48" s="52">
+        <f>'Model'!C9</f>
+        <v/>
+      </c>
+      <c r="D48" s="52">
+        <f>'Model'!D9</f>
+        <v/>
+      </c>
+      <c r="E48" s="52">
+        <f>'Model'!E9</f>
+        <v/>
+      </c>
+      <c r="F48" s="52">
+        <f>'Model'!F9</f>
+        <v/>
+      </c>
+      <c r="G48" s="52">
+        <f>'Model'!G9</f>
+        <v/>
+      </c>
+      <c r="H48" s="52">
+        <f>G48*(1+$C$22)</f>
+        <v/>
+      </c>
+      <c r="I48" s="52">
+        <f>H48*(1+$C$22)</f>
+        <v/>
+      </c>
+      <c r="J48" s="52">
+        <f>I48*(1+$C$22)</f>
+        <v/>
+      </c>
+      <c r="K48" s="52">
+        <f>J48*(1+$C$22)</f>
+        <v/>
+      </c>
+      <c r="L48" s="52">
+        <f>K48*(1+$C$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Revenue growth %</t>
+        </is>
+      </c>
+      <c r="D49" s="56">
+        <f>IFERROR(D48/C48-1,"")</f>
+        <v/>
+      </c>
+      <c r="E49" s="56">
+        <f>IFERROR(E48/D48-1,"")</f>
+        <v/>
+      </c>
+      <c r="F49" s="56">
+        <f>IFERROR(F48/E48-1,"")</f>
+        <v/>
+      </c>
+      <c r="G49" s="56">
+        <f>IFERROR(G48/F48-1,"")</f>
+        <v/>
+      </c>
+      <c r="H49" s="56">
+        <f>IFERROR(H48/G48-1,"")</f>
+        <v/>
+      </c>
+      <c r="I49" s="56">
+        <f>IFERROR(I48/H48-1,"")</f>
+        <v/>
+      </c>
+      <c r="J49" s="56">
+        <f>IFERROR(J48/I48-1,"")</f>
+        <v/>
+      </c>
+      <c r="K49" s="56">
+        <f>IFERROR(K48/J48-1,"")</f>
+        <v/>
+      </c>
+      <c r="L49" s="56">
+        <f>IFERROR(L48/K48-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="32" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="C50" s="51">
+        <f>'Model'!C45</f>
+        <v/>
+      </c>
+      <c r="D50" s="51">
+        <f>'Model'!D45</f>
+        <v/>
+      </c>
+      <c r="E50" s="51">
+        <f>'Model'!E45</f>
+        <v/>
+      </c>
+      <c r="F50" s="51">
+        <f>'Model'!F45</f>
+        <v/>
+      </c>
+      <c r="G50" s="51">
+        <f>'Model'!G45</f>
+        <v/>
+      </c>
+      <c r="H50" s="51">
+        <f>H48*$C$23</f>
+        <v/>
+      </c>
+      <c r="I50" s="51">
+        <f>I48*$C$23</f>
+        <v/>
+      </c>
+      <c r="J50" s="51">
+        <f>J48*$C$23</f>
+        <v/>
+      </c>
+      <c r="K50" s="51">
+        <f>K48*$C$23</f>
+        <v/>
+      </c>
+      <c r="L50" s="51">
+        <f>L48*$C$23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   EBITDA margin %</t>
+        </is>
+      </c>
+      <c r="C51" s="56">
+        <f>IFERROR(C50/C48,"")</f>
+        <v/>
+      </c>
+      <c r="D51" s="56">
+        <f>IFERROR(D50/D48,"")</f>
+        <v/>
+      </c>
+      <c r="E51" s="56">
+        <f>IFERROR(E50/E48,"")</f>
+        <v/>
+      </c>
+      <c r="F51" s="56">
+        <f>IFERROR(F50/F48,"")</f>
+        <v/>
+      </c>
+      <c r="G51" s="56">
+        <f>IFERROR(G50/G48,"")</f>
+        <v/>
+      </c>
+      <c r="H51" s="56">
+        <f>IFERROR(H50/H48,"")</f>
+        <v/>
+      </c>
+      <c r="I51" s="56">
+        <f>IFERROR(I50/I48,"")</f>
+        <v/>
+      </c>
+      <c r="J51" s="56">
+        <f>IFERROR(J50/J48,"")</f>
+        <v/>
+      </c>
+      <c r="K51" s="56">
+        <f>IFERROR(K50/K48,"")</f>
+        <v/>
+      </c>
+      <c r="L51" s="56">
+        <f>IFERROR(L50/L48,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="36" t="inlineStr">
+        <is>
+          <t>Depreciation &amp; amortization</t>
+        </is>
+      </c>
+      <c r="C52" s="43">
+        <f>'Model'!C151</f>
+        <v/>
+      </c>
+      <c r="D52" s="43">
+        <f>'Model'!D151</f>
+        <v/>
+      </c>
+      <c r="E52" s="43">
+        <f>'Model'!E151</f>
+        <v/>
+      </c>
+      <c r="F52" s="43">
+        <f>'Model'!F151</f>
+        <v/>
+      </c>
+      <c r="G52" s="43">
+        <f>'Model'!G151</f>
+        <v/>
+      </c>
+      <c r="H52" s="43">
+        <f>H48*$C$25</f>
+        <v/>
+      </c>
+      <c r="I52" s="43">
+        <f>I48*$C$25</f>
+        <v/>
+      </c>
+      <c r="J52" s="43">
+        <f>J48*$C$25</f>
+        <v/>
+      </c>
+      <c r="K52" s="43">
+        <f>K48*$C$25</f>
+        <v/>
+      </c>
+      <c r="L52" s="43">
+        <f>L48*$C$25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="32" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="C53" s="51">
+        <f>C50-C52</f>
+        <v/>
+      </c>
+      <c r="D53" s="51">
+        <f>D50-D52</f>
+        <v/>
+      </c>
+      <c r="E53" s="51">
+        <f>E50-E52</f>
+        <v/>
+      </c>
+      <c r="F53" s="51">
+        <f>F50-F52</f>
+        <v/>
+      </c>
+      <c r="G53" s="51">
+        <f>G50-G52</f>
+        <v/>
+      </c>
+      <c r="H53" s="51">
+        <f>H50-H52</f>
+        <v/>
+      </c>
+      <c r="I53" s="51">
+        <f>I50-I52</f>
+        <v/>
+      </c>
+      <c r="J53" s="51">
+        <f>J50-J52</f>
+        <v/>
+      </c>
+      <c r="K53" s="51">
+        <f>K50-K52</f>
+        <v/>
+      </c>
+      <c r="L53" s="51">
+        <f>L50-L52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="36" t="inlineStr">
+        <is>
+          <t>Interest expense (on opening debt)</t>
+        </is>
+      </c>
+      <c r="H54" s="43">
+        <f>$C$16*H64</f>
+        <v/>
+      </c>
+      <c r="I54" s="43">
+        <f>$C$16*I64</f>
+        <v/>
+      </c>
+      <c r="J54" s="43">
+        <f>$C$16*J64</f>
+        <v/>
+      </c>
+      <c r="K54" s="43">
+        <f>$C$16*K64</f>
+        <v/>
+      </c>
+      <c r="L54" s="43">
+        <f>$C$16*L64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="32" t="inlineStr">
+        <is>
+          <t>Pre-tax profit (EBT)</t>
+        </is>
+      </c>
+      <c r="H55" s="51">
+        <f>H53-H54</f>
+        <v/>
+      </c>
+      <c r="I55" s="51">
+        <f>I53-I54</f>
+        <v/>
+      </c>
+      <c r="J55" s="51">
+        <f>J53-J54</f>
+        <v/>
+      </c>
+      <c r="K55" s="51">
+        <f>K53-K54</f>
+        <v/>
+      </c>
+      <c r="L55" s="51">
+        <f>L53-L54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="36" t="inlineStr">
+        <is>
+          <t>Cash taxes</t>
+        </is>
+      </c>
+      <c r="H56" s="43">
+        <f>-MAX(H55*$C$26,0)</f>
+        <v/>
+      </c>
+      <c r="I56" s="43">
+        <f>-MAX(I55*$C$26,0)</f>
+        <v/>
+      </c>
+      <c r="J56" s="43">
+        <f>-MAX(J55*$C$26,0)</f>
+        <v/>
+      </c>
+      <c r="K56" s="43">
+        <f>-MAX(K55*$C$26,0)</f>
+        <v/>
+      </c>
+      <c r="L56" s="43">
+        <f>-MAX(L55*$C$26,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="32" t="inlineStr">
+        <is>
+          <t>Net profit after tax</t>
+        </is>
+      </c>
+      <c r="H57" s="51">
+        <f>H55+H56</f>
+        <v/>
+      </c>
+      <c r="I57" s="51">
+        <f>I55+I56</f>
+        <v/>
+      </c>
+      <c r="J57" s="51">
+        <f>J55+J56</f>
+        <v/>
+      </c>
+      <c r="K57" s="51">
+        <f>K55+K56</f>
+        <v/>
+      </c>
+      <c r="L57" s="51">
+        <f>L55+L56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   (+) D&amp;A</t>
+        </is>
+      </c>
+      <c r="H58" s="43">
+        <f>H52</f>
+        <v/>
+      </c>
+      <c r="I58" s="43">
+        <f>I52</f>
+        <v/>
+      </c>
+      <c r="J58" s="43">
+        <f>J52</f>
+        <v/>
+      </c>
+      <c r="K58" s="43">
+        <f>K52</f>
+        <v/>
+      </c>
+      <c r="L58" s="43">
+        <f>L52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   (−) Capex</t>
+        </is>
+      </c>
+      <c r="H59" s="43">
+        <f>-H48*$C$24</f>
+        <v/>
+      </c>
+      <c r="I59" s="43">
+        <f>-I48*$C$24</f>
+        <v/>
+      </c>
+      <c r="J59" s="43">
+        <f>-J48*$C$24</f>
+        <v/>
+      </c>
+      <c r="K59" s="43">
+        <f>-K48*$C$24</f>
+        <v/>
+      </c>
+      <c r="L59" s="43">
+        <f>-L48*$C$24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   (−) Δ Net working capital</t>
+        </is>
+      </c>
+      <c r="H60" s="43">
+        <f>-(H48-G48)*$C$27</f>
+        <v/>
+      </c>
+      <c r="I60" s="43">
+        <f>-(I48-H48)*$C$27</f>
+        <v/>
+      </c>
+      <c r="J60" s="43">
+        <f>-(J48-I48)*$C$27</f>
+        <v/>
+      </c>
+      <c r="K60" s="43">
+        <f>-(K48-J48)*$C$27</f>
+        <v/>
+      </c>
+      <c r="L60" s="43">
+        <f>-(L48-K48)*$C$27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="32" t="inlineStr">
+        <is>
+          <t>Levered free cash flow (owner earnings)</t>
+        </is>
+      </c>
+      <c r="H61" s="51">
+        <f>H57+H58+H59+H60</f>
+        <v/>
+      </c>
+      <c r="I61" s="51">
+        <f>I57+I58+I59+I60</f>
+        <v/>
+      </c>
+      <c r="J61" s="51">
+        <f>J57+J58+J59+J60</f>
+        <v/>
+      </c>
+      <c r="K61" s="51">
+        <f>K57+K58+K59+K60</f>
+        <v/>
+      </c>
+      <c r="L61" s="51">
+        <f>L57+L58+L59+L60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="40" t="n"/>
+      <c r="B63" s="41" t="inlineStr">
+        <is>
+          <t>Debt schedule</t>
+        </is>
+      </c>
+      <c r="C63" s="40" t="n"/>
+      <c r="D63" s="40" t="n"/>
+      <c r="E63" s="40" t="n"/>
+      <c r="F63" s="40" t="n"/>
+      <c r="G63" s="40" t="n"/>
+      <c r="H63" s="40" t="n"/>
+      <c r="I63" s="40" t="n"/>
+      <c r="J63" s="40" t="n"/>
+      <c r="K63" s="40" t="n"/>
+      <c r="L63" s="40" t="n"/>
+    </row>
+    <row r="64">
+      <c r="B64" s="36" t="inlineStr">
+        <is>
+          <t>Beginning debt</t>
+        </is>
+      </c>
+      <c r="H64" s="43">
+        <f>G67</f>
+        <v/>
+      </c>
+      <c r="I64" s="43">
+        <f>H67</f>
+        <v/>
+      </c>
+      <c r="J64" s="43">
+        <f>I67</f>
+        <v/>
+      </c>
+      <c r="K64" s="43">
+        <f>J67</f>
+        <v/>
+      </c>
+      <c r="L64" s="43">
+        <f>K67</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   (−) Mandatory amortization</t>
+        </is>
+      </c>
+      <c r="H65" s="43">
+        <f>-MIN(H64,$C$17*$C$15)</f>
+        <v/>
+      </c>
+      <c r="I65" s="43">
+        <f>-MIN(I64,$C$17*$C$15)</f>
+        <v/>
+      </c>
+      <c r="J65" s="43">
+        <f>-MIN(J64,$C$17*$C$15)</f>
+        <v/>
+      </c>
+      <c r="K65" s="43">
+        <f>-MIN(K64,$C$17*$C$15)</f>
+        <v/>
+      </c>
+      <c r="L65" s="43">
+        <f>-MIN(L64,$C$17*$C$15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   (−) Cash sweep</t>
+        </is>
+      </c>
+      <c r="H66" s="43">
+        <f>-MIN(MAX(H61+H65,0)*$C$18,H64+H65)</f>
+        <v/>
+      </c>
+      <c r="I66" s="43">
+        <f>-MIN(MAX(I61+I65,0)*$C$18,I64+I65)</f>
+        <v/>
+      </c>
+      <c r="J66" s="43">
+        <f>-MIN(MAX(J61+J65,0)*$C$18,J64+J65)</f>
+        <v/>
+      </c>
+      <c r="K66" s="43">
+        <f>-MIN(MAX(K61+K65,0)*$C$18,K64+K65)</f>
+        <v/>
+      </c>
+      <c r="L66" s="43">
+        <f>-MIN(MAX(L61+L65,0)*$C$18,L64+L65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="32" t="inlineStr">
+        <is>
+          <t>Ending debt</t>
+        </is>
+      </c>
+      <c r="G67" s="43">
+        <f>$C$15</f>
+        <v/>
+      </c>
+      <c r="H67" s="51">
+        <f>H64+H65+H66</f>
+        <v/>
+      </c>
+      <c r="I67" s="51">
+        <f>I64+I65+I66</f>
+        <v/>
+      </c>
+      <c r="J67" s="51">
+        <f>J64+J65+J66</f>
+        <v/>
+      </c>
+      <c r="K67" s="51">
+        <f>K64+K65+K66</f>
+        <v/>
+      </c>
+      <c r="L67" s="51">
+        <f>L64+L65+L66</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="40" t="n"/>
+      <c r="B69" s="41" t="inlineStr">
+        <is>
+          <t>Cash &amp; leverage</t>
+        </is>
+      </c>
+      <c r="C69" s="40" t="n"/>
+      <c r="D69" s="40" t="n"/>
+      <c r="E69" s="40" t="n"/>
+      <c r="F69" s="40" t="n"/>
+      <c r="G69" s="40" t="n"/>
+      <c r="H69" s="40" t="n"/>
+      <c r="I69" s="40" t="n"/>
+      <c r="J69" s="40" t="n"/>
+      <c r="K69" s="40" t="n"/>
+      <c r="L69" s="40" t="n"/>
+    </row>
+    <row r="70">
+      <c r="B70" s="36" t="inlineStr">
+        <is>
+          <t>Beginning cash</t>
+        </is>
+      </c>
+      <c r="H70" s="43">
+        <f>G72</f>
+        <v/>
+      </c>
+      <c r="I70" s="43">
+        <f>H72</f>
+        <v/>
+      </c>
+      <c r="J70" s="43">
+        <f>I72</f>
+        <v/>
+      </c>
+      <c r="K70" s="43">
+        <f>J72</f>
+        <v/>
+      </c>
+      <c r="L70" s="43">
+        <f>K72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   (+) FCF after debt paydown</t>
+        </is>
+      </c>
+      <c r="H71" s="43">
+        <f>H61+H65+H66</f>
+        <v/>
+      </c>
+      <c r="I71" s="43">
+        <f>I61+I65+I66</f>
+        <v/>
+      </c>
+      <c r="J71" s="43">
+        <f>J61+J65+J66</f>
+        <v/>
+      </c>
+      <c r="K71" s="43">
+        <f>K61+K65+K66</f>
+        <v/>
+      </c>
+      <c r="L71" s="43">
+        <f>L61+L65+L66</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="32" t="inlineStr">
+        <is>
+          <t>Ending cash</t>
+        </is>
+      </c>
+      <c r="G72" s="43">
+        <f>$C$19</f>
+        <v/>
+      </c>
+      <c r="H72" s="51">
+        <f>H70+H71</f>
+        <v/>
+      </c>
+      <c r="I72" s="51">
+        <f>I70+I71</f>
+        <v/>
+      </c>
+      <c r="J72" s="51">
+        <f>J70+J71</f>
+        <v/>
+      </c>
+      <c r="K72" s="51">
+        <f>K70+K71</f>
+        <v/>
+      </c>
+      <c r="L72" s="51">
+        <f>L70+L71</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="36" t="inlineStr">
+        <is>
+          <t>Net debt (debt − cash)</t>
+        </is>
+      </c>
+      <c r="G73" s="43">
+        <f>G67-G72</f>
+        <v/>
+      </c>
+      <c r="H73" s="43">
+        <f>H67-H72</f>
+        <v/>
+      </c>
+      <c r="I73" s="43">
+        <f>I67-I72</f>
+        <v/>
+      </c>
+      <c r="J73" s="43">
+        <f>J67-J72</f>
+        <v/>
+      </c>
+      <c r="K73" s="43">
+        <f>K67-K72</f>
+        <v/>
+      </c>
+      <c r="L73" s="43">
+        <f>L67-L72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Net debt / EBITDA  (x)</t>
+        </is>
+      </c>
+      <c r="G74" s="57">
+        <f>IFERROR(G73/G50,"")</f>
+        <v/>
+      </c>
+      <c r="H74" s="57">
+        <f>IFERROR(H73/H50,"")</f>
+        <v/>
+      </c>
+      <c r="I74" s="57">
+        <f>IFERROR(I73/I50,"")</f>
+        <v/>
+      </c>
+      <c r="J74" s="57">
+        <f>IFERROR(J73/J50,"")</f>
+        <v/>
+      </c>
+      <c r="K74" s="57">
+        <f>IFERROR(K73/K50,"")</f>
+        <v/>
+      </c>
+      <c r="L74" s="57">
+        <f>IFERROR(L73/L50,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n"/>
+      <c r="B76" s="38" t="inlineStr">
+        <is>
+          <t>RETURNS — EXIT &amp; IRR</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="n"/>
+      <c r="D76" s="4" t="n"/>
+      <c r="E76" s="4" t="n"/>
+      <c r="F76" s="4" t="n"/>
+      <c r="G76" s="4" t="n"/>
+      <c r="H76" s="4" t="n"/>
+      <c r="I76" s="4" t="n"/>
+      <c r="J76" s="4" t="n"/>
+      <c r="K76" s="4" t="n"/>
+      <c r="L76" s="4" t="n"/>
+    </row>
+    <row r="77">
+      <c r="B77" s="36" t="inlineStr">
+        <is>
+          <t>Hold period (years)</t>
+        </is>
+      </c>
+      <c r="C77" s="58">
+        <f>C28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="36" t="inlineStr">
+        <is>
+          <t>Exit-year EBITDA</t>
+        </is>
+      </c>
+      <c r="C78" s="43">
+        <f>INDEX($G50:$L50,1,$C$28+1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="36" t="inlineStr">
+        <is>
+          <t>Exit EV / EBITDA multiple  (x)</t>
+        </is>
+      </c>
+      <c r="C79" s="59">
+        <f>C29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="36" t="inlineStr">
+        <is>
+          <t>Exit enterprise value</t>
+        </is>
+      </c>
+      <c r="C80" s="43">
+        <f>C78*C79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="36" t="inlineStr">
+        <is>
+          <t>(−) Net debt at exit</t>
+        </is>
+      </c>
+      <c r="C81" s="43">
+        <f>INDEX($G73:$L73,1,$C$28+1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="32" t="inlineStr">
+        <is>
+          <t>Exit equity value</t>
+        </is>
+      </c>
+      <c r="C82" s="51">
+        <f>C80-C81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="36" t="inlineStr">
+        <is>
+          <t>Entry sponsor equity</t>
+        </is>
+      </c>
+      <c r="C83" s="43">
+        <f>C39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="32" t="inlineStr">
+        <is>
+          <t>MOIC  (x)</t>
+        </is>
+      </c>
+      <c r="C84" s="60">
+        <f>IFERROR(C82/C83,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="32" t="inlineStr">
+        <is>
+          <t>IRR  (equity, closed form)</t>
+        </is>
+      </c>
+      <c r="C85" s="61">
+        <f>IFERROR((C82/C83)^(1/C77)-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="40" t="n"/>
+      <c r="B87" s="41" t="inlineStr">
+        <is>
+          <t>Equity cash flows (Year 0 → exit)   —   live =IRR()</t>
+        </is>
+      </c>
+      <c r="C87" s="40" t="n"/>
+      <c r="D87" s="40" t="n"/>
+      <c r="E87" s="40" t="n"/>
+      <c r="F87" s="40" t="n"/>
+      <c r="G87" s="40" t="n"/>
+      <c r="H87" s="40" t="n"/>
+      <c r="I87" s="40" t="n"/>
+      <c r="J87" s="40" t="n"/>
+      <c r="K87" s="40" t="n"/>
+      <c r="L87" s="40" t="n"/>
+    </row>
+    <row r="88">
+      <c r="B88" s="36" t="inlineStr">
+        <is>
+          <t>Sponsor equity cash flow</t>
+        </is>
+      </c>
+      <c r="G88" s="43">
+        <f>-C39</f>
+        <v/>
+      </c>
+      <c r="H88" s="43">
+        <f>IF($C$28=1,$C$82,0)</f>
+        <v/>
+      </c>
+      <c r="I88" s="43">
+        <f>IF($C$28=2,$C$82,0)</f>
+        <v/>
+      </c>
+      <c r="J88" s="43">
+        <f>IF($C$28=3,$C$82,0)</f>
+        <v/>
+      </c>
+      <c r="K88" s="43">
+        <f>IF($C$28=4,$C$82,0)</f>
+        <v/>
+      </c>
+      <c r="L88" s="43">
+        <f>IF($C$28=5,$C$82,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="32" t="inlineStr">
+        <is>
+          <t>IRR  =IRR(equity cash flows)</t>
+        </is>
+      </c>
+      <c r="C89" s="61">
+        <f>IFERROR(IRR(G88:L88),"")</f>
+        <v/>
+      </c>
+      <c r="D89" s="62" t="inlineStr">
+        <is>
+          <t>Matches the closed-form IRR above; add interim dividends to G88:L88 to extend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="n"/>
+      <c r="B92" s="38" t="inlineStr">
+        <is>
+          <t>IRR SENSITIVITY — ENTRY (down) × EXIT (across) EV/EBITDA MULTIPLE</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="n"/>
+      <c r="D92" s="4" t="n"/>
+      <c r="E92" s="4" t="n"/>
+      <c r="F92" s="4" t="n"/>
+      <c r="G92" s="4" t="n"/>
+      <c r="H92" s="4" t="n"/>
+      <c r="I92" s="4" t="n"/>
+      <c r="J92" s="4" t="n"/>
+      <c r="K92" s="4" t="n"/>
+      <c r="L92" s="4" t="n"/>
+    </row>
+    <row r="93">
+      <c r="B93" s="62" t="inlineStr">
+        <is>
+          <t>Holds the current operating scenario, leverage, interest and cash fixed; only the multiples vary. Live case is highlighted by your C11 / C29 inputs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="C94" s="63" t="inlineStr">
+        <is>
+          <t>Entry ↓ / Exit →</t>
+        </is>
+      </c>
+      <c r="D94" s="64" t="n">
+        <v>5</v>
+      </c>
+      <c r="E94" s="64" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F94" s="64" t="n">
+        <v>6</v>
+      </c>
+      <c r="G94" s="64" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H94" s="64" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="C95" s="64" t="n">
+        <v>5</v>
+      </c>
+      <c r="D95" s="65">
+        <f>IFERROR(((D$94*$C$78-$C$81)/($C95*$C$9*(1+$C$20)+$C$19-$C$15))^(1/$C$28)-1,"")</f>
+        <v/>
+      </c>
+      <c r="E95" s="65">
+        <f>IFERROR(((E$94*$C$78-$C$81)/($C95*$C$9*(1+$C$20)+$C$19-$C$15))^(1/$C$28)-1,"")</f>
+        <v/>
+      </c>
+      <c r="F95" s="65">
+        <f>IFERROR(((F$94*$C$78-$C$81)/($C95*$C$9*(1+$C$20)+$C$19-$C$15))^(1/$C$28)-1,"")</f>
+        <v/>
+      </c>
+      <c r="G95" s="65">
+        <f>IFERROR(((G$94*$C$78-$C$81)/($C95*$C$9*(1+$C$20)+$C$19-$C$15))^(1/$C$28)-1,"")</f>
+        <v/>
+      </c>
+      <c r="H95" s="65">
+        <f>IFERROR(((H$94*$C$78-$C$81)/($C95*$C$9*(1+$C$20)+$C$19-$C$15))^(1/$C$28)-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="C96" s="64" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D96" s="65">
+        <f>IFERROR(((D$94*$C$78-$C$81)/($C96*$C$9*(1+$C$20)+$C$19-$C$15))^(1/$C$28)-1,"")</f>
+        <v/>
+      </c>
+      <c r="E96" s="65">
+        <f>IFERROR(((E$94*$C$78-$C$81)/($C96*$C$9*(1+$C$20)+$C$19-$C$15))^(1/$C$28)-1,"")</f>
+        <v/>
+      </c>
+      <c r="F96" s="65">
+        <f>IFERROR(((F$94*$C$78-$C$81)/($C96*$C$9*(1+$C$20)+$C$19-$C$15))^(1/$C$28)-1,"")</f>
+        <v/>
+      </c>
+      <c r="G96" s="65">
+        <f>IFERROR(((G$94*$C$78-$C$81)/($C96*$C$9*(1+$C$20)+$C$19-$C$15))^(1/$C$28)-1,"")</f>
+        <v/>
+      </c>
+      <c r="H96" s="65">
+        <f>IFERROR(((H$94*$C$78-$C$81)/($C96*$C$9*(1+$C$20)+$C$19-$C$15))^(1/$C$28)-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="C97" s="64" t="n">
+        <v>6</v>
+      </c>
+      <c r="D97" s="65">
+        <f>IFERROR(((D$94*$C$78-$C$81)/($C97*$C$9*(1+$C$20)+$C$19-$C$15))^(1/$C$28)-1,"")</f>
+        <v/>
+      </c>
+      <c r="E97" s="65">
+        <f>IFERROR(((E$94*$C$78-$C$81)/($C97*$C$9*(1+$C$20)+$C$19-$C$15))^(1/$C$28)-1,"")</f>
+        <v/>
+      </c>
+      <c r="F97" s="65">
+        <f>IFERROR(((F$94*$C$78-$C$81)/($C97*$C$9*(1+$C$20)+$C$19-$C$15))^(1/$C$28)-1,"")</f>
+        <v/>
+      </c>
+      <c r="G97" s="65">
+        <f>IFERROR(((G$94*$C$78-$C$81)/($C97*$C$9*(1+$C$20)+$C$19-$C$15))^(1/$C$28)-1,"")</f>
+        <v/>
+      </c>
+      <c r="H97" s="65">
+        <f>IFERROR(((H$94*$C$78-$C$81)/($C97*$C$9*(1+$C$20)+$C$19-$C$15))^(1/$C$28)-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="C98" s="64" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D98" s="65">
+        <f>IFERROR(((D$94*$C$78-$C$81)/($C98*$C$9*(1+$C$20)+$C$19-$C$15))^(1/$C$28)-1,"")</f>
+        <v/>
+      </c>
+      <c r="E98" s="65">
+        <f>IFERROR(((E$94*$C$78-$C$81)/($C98*$C$9*(1+$C$20)+$C$19-$C$15))^(1/$C$28)-1,"")</f>
+        <v/>
+      </c>
+      <c r="F98" s="65">
+        <f>IFERROR(((F$94*$C$78-$C$81)/($C98*$C$9*(1+$C$20)+$C$19-$C$15))^(1/$C$28)-1,"")</f>
+        <v/>
+      </c>
+      <c r="G98" s="65">
+        <f>IFERROR(((G$94*$C$78-$C$81)/($C98*$C$9*(1+$C$20)+$C$19-$C$15))^(1/$C$28)-1,"")</f>
+        <v/>
+      </c>
+      <c r="H98" s="65">
+        <f>IFERROR(((H$94*$C$78-$C$81)/($C98*$C$9*(1+$C$20)+$C$19-$C$15))^(1/$C$28)-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="C99" s="64" t="n">
+        <v>7</v>
+      </c>
+      <c r="D99" s="65">
+        <f>IFERROR(((D$94*$C$78-$C$81)/($C99*$C$9*(1+$C$20)+$C$19-$C$15))^(1/$C$28)-1,"")</f>
+        <v/>
+      </c>
+      <c r="E99" s="65">
+        <f>IFERROR(((E$94*$C$78-$C$81)/($C99*$C$9*(1+$C$20)+$C$19-$C$15))^(1/$C$28)-1,"")</f>
+        <v/>
+      </c>
+      <c r="F99" s="65">
+        <f>IFERROR(((F$94*$C$78-$C$81)/($C99*$C$9*(1+$C$20)+$C$19-$C$15))^(1/$C$28)-1,"")</f>
+        <v/>
+      </c>
+      <c r="G99" s="65">
+        <f>IFERROR(((G$94*$C$78-$C$81)/($C99*$C$9*(1+$C$20)+$C$19-$C$15))^(1/$C$28)-1,"")</f>
+        <v/>
+      </c>
+      <c r="H99" s="65">
+        <f>IFERROR(((H$94*$C$78-$C$81)/($C99*$C$9*(1+$C$20)+$C$19-$C$15))^(1/$C$28)-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="n"/>
+      <c r="B102" s="38" t="inlineStr">
+        <is>
+          <t>MOIC SENSITIVITY — ENTRY (down) × EXIT (across) EV/EBITDA MULTIPLE</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="n"/>
+      <c r="D102" s="4" t="n"/>
+      <c r="E102" s="4" t="n"/>
+      <c r="F102" s="4" t="n"/>
+      <c r="G102" s="4" t="n"/>
+      <c r="H102" s="4" t="n"/>
+      <c r="I102" s="4" t="n"/>
+      <c r="J102" s="4" t="n"/>
+      <c r="K102" s="4" t="n"/>
+      <c r="L102" s="4" t="n"/>
+    </row>
+    <row r="103">
+      <c r="C103" s="63" t="inlineStr">
+        <is>
+          <t>Entry ↓ / Exit →</t>
+        </is>
+      </c>
+      <c r="D103" s="64" t="n">
+        <v>5</v>
+      </c>
+      <c r="E103" s="64" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F103" s="64" t="n">
+        <v>6</v>
+      </c>
+      <c r="G103" s="64" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H103" s="64" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="C104" s="64" t="n">
+        <v>5</v>
+      </c>
+      <c r="D104" s="66">
+        <f>IFERROR((D$103*$C$78-$C$81)/($C104*$C$9*(1+$C$20)+$C$19-$C$15),"")</f>
+        <v/>
+      </c>
+      <c r="E104" s="66">
+        <f>IFERROR((E$103*$C$78-$C$81)/($C104*$C$9*(1+$C$20)+$C$19-$C$15),"")</f>
+        <v/>
+      </c>
+      <c r="F104" s="66">
+        <f>IFERROR((F$103*$C$78-$C$81)/($C104*$C$9*(1+$C$20)+$C$19-$C$15),"")</f>
+        <v/>
+      </c>
+      <c r="G104" s="66">
+        <f>IFERROR((G$103*$C$78-$C$81)/($C104*$C$9*(1+$C$20)+$C$19-$C$15),"")</f>
+        <v/>
+      </c>
+      <c r="H104" s="66">
+        <f>IFERROR((H$103*$C$78-$C$81)/($C104*$C$9*(1+$C$20)+$C$19-$C$15),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="C105" s="64" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D105" s="66">
+        <f>IFERROR((D$103*$C$78-$C$81)/($C105*$C$9*(1+$C$20)+$C$19-$C$15),"")</f>
+        <v/>
+      </c>
+      <c r="E105" s="66">
+        <f>IFERROR((E$103*$C$78-$C$81)/($C105*$C$9*(1+$C$20)+$C$19-$C$15),"")</f>
+        <v/>
+      </c>
+      <c r="F105" s="66">
+        <f>IFERROR((F$103*$C$78-$C$81)/($C105*$C$9*(1+$C$20)+$C$19-$C$15),"")</f>
+        <v/>
+      </c>
+      <c r="G105" s="66">
+        <f>IFERROR((G$103*$C$78-$C$81)/($C105*$C$9*(1+$C$20)+$C$19-$C$15),"")</f>
+        <v/>
+      </c>
+      <c r="H105" s="66">
+        <f>IFERROR((H$103*$C$78-$C$81)/($C105*$C$9*(1+$C$20)+$C$19-$C$15),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="C106" s="64" t="n">
+        <v>6</v>
+      </c>
+      <c r="D106" s="66">
+        <f>IFERROR((D$103*$C$78-$C$81)/($C106*$C$9*(1+$C$20)+$C$19-$C$15),"")</f>
+        <v/>
+      </c>
+      <c r="E106" s="66">
+        <f>IFERROR((E$103*$C$78-$C$81)/($C106*$C$9*(1+$C$20)+$C$19-$C$15),"")</f>
+        <v/>
+      </c>
+      <c r="F106" s="66">
+        <f>IFERROR((F$103*$C$78-$C$81)/($C106*$C$9*(1+$C$20)+$C$19-$C$15),"")</f>
+        <v/>
+      </c>
+      <c r="G106" s="66">
+        <f>IFERROR((G$103*$C$78-$C$81)/($C106*$C$9*(1+$C$20)+$C$19-$C$15),"")</f>
+        <v/>
+      </c>
+      <c r="H106" s="66">
+        <f>IFERROR((H$103*$C$78-$C$81)/($C106*$C$9*(1+$C$20)+$C$19-$C$15),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="C107" s="64" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D107" s="66">
+        <f>IFERROR((D$103*$C$78-$C$81)/($C107*$C$9*(1+$C$20)+$C$19-$C$15),"")</f>
+        <v/>
+      </c>
+      <c r="E107" s="66">
+        <f>IFERROR((E$103*$C$78-$C$81)/($C107*$C$9*(1+$C$20)+$C$19-$C$15),"")</f>
+        <v/>
+      </c>
+      <c r="F107" s="66">
+        <f>IFERROR((F$103*$C$78-$C$81)/($C107*$C$9*(1+$C$20)+$C$19-$C$15),"")</f>
+        <v/>
+      </c>
+      <c r="G107" s="66">
+        <f>IFERROR((G$103*$C$78-$C$81)/($C107*$C$9*(1+$C$20)+$C$19-$C$15),"")</f>
+        <v/>
+      </c>
+      <c r="H107" s="66">
+        <f>IFERROR((H$103*$C$78-$C$81)/($C107*$C$9*(1+$C$20)+$C$19-$C$15),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="C108" s="64" t="n">
+        <v>7</v>
+      </c>
+      <c r="D108" s="66">
+        <f>IFERROR((D$103*$C$78-$C$81)/($C108*$C$9*(1+$C$20)+$C$19-$C$15),"")</f>
+        <v/>
+      </c>
+      <c r="E108" s="66">
+        <f>IFERROR((E$103*$C$78-$C$81)/($C108*$C$9*(1+$C$20)+$C$19-$C$15),"")</f>
+        <v/>
+      </c>
+      <c r="F108" s="66">
+        <f>IFERROR((F$103*$C$78-$C$81)/($C108*$C$9*(1+$C$20)+$C$19-$C$15),"")</f>
+        <v/>
+      </c>
+      <c r="G108" s="66">
+        <f>IFERROR((G$103*$C$78-$C$81)/($C108*$C$9*(1+$C$20)+$C$19-$C$15),"")</f>
+        <v/>
+      </c>
+      <c r="H108" s="66">
+        <f>IFERROR((H$103*$C$78-$C$81)/($C108*$C$9*(1+$C$20)+$C$19-$C$15),"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>